--- a/artfynd/A 48959-2025 artfynd.xlsx
+++ b/artfynd/A 48959-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129733690</v>
       </c>
       <c r="B2" t="n">
-        <v>91583</v>
+        <v>91584</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129733694</v>
       </c>
       <c r="B3" t="n">
-        <v>91583</v>
+        <v>91584</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129733684</v>
       </c>
       <c r="B4" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -990,7 +990,7 @@
         <v>129733680</v>
       </c>
       <c r="B5" t="n">
-        <v>91587</v>
+        <v>91588</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1087,7 +1087,7 @@
         <v>129733693</v>
       </c>
       <c r="B6" t="n">
-        <v>91583</v>
+        <v>91584</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1184,7 +1184,7 @@
         <v>129733695</v>
       </c>
       <c r="B7" t="n">
-        <v>91583</v>
+        <v>91584</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1281,7 +1281,7 @@
         <v>129733692</v>
       </c>
       <c r="B8" t="n">
-        <v>91583</v>
+        <v>91584</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1375,45 +1375,53 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129733689</v>
+        <v>129733686</v>
       </c>
       <c r="B9" t="n">
-        <v>91583</v>
+        <v>98769</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1108</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>473505</v>
+        <v>473562</v>
       </c>
       <c r="R9" t="n">
-        <v>6991422</v>
+        <v>6991360</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1454,6 +1462,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1475,7 +1484,7 @@
         <v>129733685</v>
       </c>
       <c r="B10" t="n">
-        <v>57732</v>
+        <v>57733</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1582,10 +1591,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129733696</v>
+        <v>129733689</v>
       </c>
       <c r="B11" t="n">
-        <v>91607</v>
+        <v>91584</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1593,19 +1602,23 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr"/>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1613,10 +1626,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>473472</v>
+        <v>473505</v>
       </c>
       <c r="R11" t="n">
-        <v>6991545</v>
+        <v>6991422</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1675,53 +1688,41 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129733686</v>
+        <v>129733696</v>
       </c>
       <c r="B12" t="n">
-        <v>98768</v>
+        <v>91608</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>473562</v>
+        <v>473472</v>
       </c>
       <c r="R12" t="n">
-        <v>6991360</v>
+        <v>6991545</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1762,7 +1763,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1784,7 +1784,7 @@
         <v>129733681</v>
       </c>
       <c r="B13" t="n">
-        <v>91587</v>
+        <v>91588</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1881,7 +1881,7 @@
         <v>129733687</v>
       </c>
       <c r="B14" t="n">
-        <v>91583</v>
+        <v>91584</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1978,7 +1978,7 @@
         <v>129733691</v>
       </c>
       <c r="B15" t="n">
-        <v>91583</v>
+        <v>91584</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         <v>129733683</v>
       </c>
       <c r="B16" t="n">
-        <v>92305</v>
+        <v>92306</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2172,7 +2172,7 @@
         <v>129733682</v>
       </c>
       <c r="B17" t="n">
-        <v>92305</v>
+        <v>92306</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2269,7 +2269,7 @@
         <v>129733688</v>
       </c>
       <c r="B18" t="n">
-        <v>91583</v>
+        <v>91584</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2363,32 +2363,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129762650</v>
+        <v>129762562</v>
       </c>
       <c r="B19" t="n">
-        <v>91583</v>
+        <v>92306</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1108</v>
+        <v>3298</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2405,10 +2405,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>473464</v>
+        <v>473408</v>
       </c>
       <c r="R19" t="n">
-        <v>6991416</v>
+        <v>6991459</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i stambasen av en stående döende grov gran.</t>
+          <t>Rikligt med fruktkroppar i stambasen av en hyfsat grov stående död gran med full längd.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2498,10 +2498,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129762639</v>
+        <v>129762650</v>
       </c>
       <c r="B20" t="n">
-        <v>91583</v>
+        <v>91584</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2540,10 +2540,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>473289</v>
+        <v>473464</v>
       </c>
       <c r="R20" t="n">
-        <v>6991144</v>
+        <v>6991416</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2580,7 +2580,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>I två stående döda granar.</t>
+          <t>Flera fruktkroppar i stambasen av en stående döende grov gran.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2595,7 +2595,7 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
@@ -2633,10 +2633,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129762642</v>
+        <v>129762643</v>
       </c>
       <c r="B21" t="n">
-        <v>91583</v>
+        <v>91584</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2663,7 +2663,11 @@
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2671,10 +2675,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>473243</v>
+        <v>473253</v>
       </c>
       <c r="R21" t="n">
-        <v>6991220</v>
+        <v>6991258</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2711,7 +2715,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>I stambasen av en döende gran.</t>
+          <t>Flera fruktkroppar i en stående döende gran.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2764,10 +2768,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129762643</v>
+        <v>129762642</v>
       </c>
       <c r="B22" t="n">
-        <v>91583</v>
+        <v>91584</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2794,11 +2798,7 @@
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2806,10 +2806,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>473253</v>
+        <v>473243</v>
       </c>
       <c r="R22" t="n">
-        <v>6991258</v>
+        <v>6991220</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2846,7 +2846,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en stående döende gran.</t>
+          <t>I stambasen av en döende gran.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2899,32 +2899,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129762562</v>
+        <v>129762639</v>
       </c>
       <c r="B23" t="n">
-        <v>92305</v>
+        <v>91584</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>3298</v>
+        <v>1108</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2941,10 +2941,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>473408</v>
+        <v>473289</v>
       </c>
       <c r="R23" t="n">
-        <v>6991459</v>
+        <v>6991144</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2981,7 +2981,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Rikligt med fruktkroppar i stambasen av en hyfsat grov stående död gran med full längd.</t>
+          <t>I två stående döda granar.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
@@ -3034,10 +3034,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129762654</v>
+        <v>129762652</v>
       </c>
       <c r="B24" t="n">
-        <v>91583</v>
+        <v>91584</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3064,7 +3064,11 @@
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3072,10 +3076,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>473668</v>
+        <v>473621</v>
       </c>
       <c r="R24" t="n">
-        <v>6991289</v>
+        <v>6991345</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3102,17 +3106,17 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en granstubbe.</t>
+          <t>Flera fruktkroppar i en stående död gran med full längd och 35 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3142,12 +3146,12 @@
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>Stubbe</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Stump # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3165,10 +3169,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129762652</v>
+        <v>129762654</v>
       </c>
       <c r="B25" t="n">
-        <v>91583</v>
+        <v>91584</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3195,11 +3199,7 @@
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3207,10 +3207,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>473621</v>
+        <v>473668</v>
       </c>
       <c r="R25" t="n">
-        <v>6991345</v>
+        <v>6991289</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3237,17 +3237,17 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en stående död gran med full längd och 35 cm i brösthöjdsdiameter.</t>
+          <t>Flera fruktkroppar i en granstubbe.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3277,12 +3277,12 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Stubbe</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3300,10 +3300,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129762641</v>
+        <v>129762649</v>
       </c>
       <c r="B26" t="n">
-        <v>91583</v>
+        <v>91584</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3342,10 +3342,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>473229</v>
+        <v>473475</v>
       </c>
       <c r="R26" t="n">
-        <v>6991116</v>
+        <v>6991471</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3382,7 +3382,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Gott om fruktkroppar i en stående död gran med full längd.</t>
+          <t>Flera fruktkroppar i stambasen av en stående död gran (24 cm BHD) med full längd. På fyndplatsen finns stående död ved i en volym som indikerar minst högt livsmiljövärde för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3435,10 +3435,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129762662</v>
+        <v>129762641</v>
       </c>
       <c r="B27" t="n">
-        <v>79075</v>
+        <v>91584</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3446,26 +3446,30 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3473,10 +3477,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>473631</v>
+        <v>473229</v>
       </c>
       <c r="R27" t="n">
-        <v>6991321</v>
+        <v>6991116</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3503,17 +3507,17 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>På gran i granskog.</t>
+          <t>Gott om fruktkroppar i en stående död gran med full längd.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3543,12 +3547,12 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3566,65 +3570,48 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129762632</v>
+        <v>129762662</v>
       </c>
       <c r="B28" t="n">
-        <v>98768</v>
+        <v>79076</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr"/>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>473644</v>
+        <v>473631</v>
       </c>
       <c r="R28" t="n">
-        <v>6991272</v>
+        <v>6991321</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3661,7 +3648,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Minst 54 plantor inom ca 2 m2 yta strax norr om ett dike.</t>
+          <t>På gran i granskog.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3677,6 +3664,26 @@
       <c r="AH28" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3694,52 +3701,65 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129762649</v>
+        <v>129762632</v>
       </c>
       <c r="B29" t="n">
-        <v>91583</v>
+        <v>98769</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1108</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>473475</v>
+        <v>473644</v>
       </c>
       <c r="R29" t="n">
-        <v>6991471</v>
+        <v>6991272</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3766,17 +3786,17 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i stambasen av en stående död gran (24 cm BHD) med full längd. På fyndplatsen finns stående död ved i en volym som indikerar minst högt livsmiljövärde för tretåig hackspett.</t>
+          <t>Minst 54 plantor inom ca 2 m2 yta strax norr om ett dike.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3792,26 +3812,6 @@
       <c r="AH29" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -3832,7 +3832,7 @@
         <v>129762647</v>
       </c>
       <c r="B30" t="n">
-        <v>91583</v>
+        <v>91584</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3967,7 +3967,7 @@
         <v>129762640</v>
       </c>
       <c r="B31" t="n">
-        <v>91583</v>
+        <v>91584</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4102,7 +4102,7 @@
         <v>129762663</v>
       </c>
       <c r="B32" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4230,10 +4230,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129762660</v>
+        <v>129762651</v>
       </c>
       <c r="B33" t="n">
-        <v>79075</v>
+        <v>91584</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4241,26 +4241,30 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4268,10 +4272,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>473564</v>
+        <v>473497</v>
       </c>
       <c r="R33" t="n">
-        <v>6991395</v>
+        <v>6991392</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4308,7 +4312,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>På bark av tall.</t>
+          <t>Flera fruktkroppar i en levande gran.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4328,22 +4332,22 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Pinus sylvestris</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4364,7 +4368,7 @@
         <v>129762630</v>
       </c>
       <c r="B34" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4492,7 +4496,7 @@
         <v>129762664</v>
       </c>
       <c r="B35" t="n">
-        <v>98685</v>
+        <v>98686</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4605,10 +4609,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129762651</v>
+        <v>129762660</v>
       </c>
       <c r="B36" t="n">
-        <v>91583</v>
+        <v>79076</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4616,30 +4620,26 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4647,10 +4647,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>473497</v>
+        <v>473564</v>
       </c>
       <c r="R36" t="n">
-        <v>6991392</v>
+        <v>6991395</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4687,7 +4687,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en levande gran.</t>
+          <t>På bark av tall.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4707,22 +4707,22 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4740,10 +4740,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129762644</v>
+        <v>129762593</v>
       </c>
       <c r="B37" t="n">
-        <v>91583</v>
+        <v>57736</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4751,41 +4751,46 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>473430</v>
+        <v>473284</v>
       </c>
       <c r="R37" t="n">
-        <v>6991442</v>
+        <v>6991191</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4822,7 +4827,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>I en granhögstubbe.</t>
+          <t>Ringhack, äldre, på stambasen av en gran i granskog.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4831,13 +4836,12 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ37" t="inlineStr">
@@ -4852,12 +4856,12 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -4875,10 +4879,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129762593</v>
+        <v>129762644</v>
       </c>
       <c r="B38" t="n">
-        <v>57735</v>
+        <v>91584</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4886,46 +4890,41 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>473284</v>
+        <v>473430</v>
       </c>
       <c r="R38" t="n">
-        <v>6991191</v>
+        <v>6991442</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4962,7 +4961,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en gran i granskog.</t>
+          <t>I en granhögstubbe.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4971,12 +4970,13 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ38" t="inlineStr">
@@ -4991,12 +4991,12 @@
       </c>
       <c r="AM38" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5017,7 +5017,7 @@
         <v>129762645</v>
       </c>
       <c r="B39" t="n">
-        <v>91583</v>
+        <v>91584</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5149,10 +5149,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129762603</v>
+        <v>129762655</v>
       </c>
       <c r="B40" t="n">
-        <v>57732</v>
+        <v>91608</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5160,46 +5160,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>473521</v>
+        <v>473666</v>
       </c>
       <c r="R40" t="n">
-        <v>6991419</v>
+        <v>6991307</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5236,7 +5227,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Rejäla hackspår i stambasen av en stående död gran med full längd.</t>
+          <t>Flera fruktkroppar i en levande gran.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5245,12 +5236,33 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM40" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5271,7 +5283,7 @@
         <v>129762597</v>
       </c>
       <c r="B41" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5410,7 +5422,7 @@
         <v>129762620</v>
       </c>
       <c r="B42" t="n">
-        <v>98672</v>
+        <v>98673</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5535,10 +5547,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129762655</v>
+        <v>129762603</v>
       </c>
       <c r="B43" t="n">
-        <v>91607</v>
+        <v>57733</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5546,37 +5558,46 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr"/>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>473666</v>
+        <v>473521</v>
       </c>
       <c r="R43" t="n">
-        <v>6991307</v>
+        <v>6991419</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5613,7 +5634,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en levande gran.</t>
+          <t>Rejäla hackspår i stambasen av en stående död gran med full längd.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5622,33 +5643,12 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -5669,7 +5669,7 @@
         <v>129762648</v>
       </c>
       <c r="B44" t="n">
-        <v>91583</v>
+        <v>91584</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5804,7 +5804,7 @@
         <v>129762659</v>
       </c>
       <c r="B45" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5935,7 +5935,7 @@
         <v>129762631</v>
       </c>
       <c r="B46" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6060,10 +6060,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129762658</v>
+        <v>129762646</v>
       </c>
       <c r="B47" t="n">
-        <v>79075</v>
+        <v>91584</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6071,26 +6071,30 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -6098,10 +6102,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>473495</v>
+        <v>473393</v>
       </c>
       <c r="R47" t="n">
-        <v>6991469</v>
+        <v>6991465</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6138,7 +6142,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>På flera både döda och levande granar.</t>
+          <t>I en stående död gran.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6153,7 +6157,7 @@
       </c>
       <c r="AH47" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ47" t="inlineStr">
@@ -6168,12 +6172,12 @@
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6191,10 +6195,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129762646</v>
+        <v>129762658</v>
       </c>
       <c r="B48" t="n">
-        <v>91583</v>
+        <v>79076</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6202,30 +6206,26 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K48" t="inlineStr"/>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -6233,10 +6233,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>473393</v>
+        <v>473495</v>
       </c>
       <c r="R48" t="n">
-        <v>6991465</v>
+        <v>6991469</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6273,7 +6273,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>I en stående död gran.</t>
+          <t>På flera både döda och levande granar.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6288,7 +6288,7 @@
       </c>
       <c r="AH48" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ48" t="inlineStr">
@@ -6303,12 +6303,12 @@
       </c>
       <c r="AM48" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6329,7 +6329,7 @@
         <v>129762595</v>
       </c>
       <c r="B49" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6468,7 +6468,7 @@
         <v>129762602</v>
       </c>
       <c r="B50" t="n">
-        <v>57732</v>
+        <v>57733</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6588,65 +6588,48 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129762627</v>
+        <v>129762656</v>
       </c>
       <c r="B51" t="n">
-        <v>98768</v>
+        <v>91608</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L51" t="inlineStr"/>
-      <c r="N51" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>473137</v>
+        <v>473615</v>
       </c>
       <c r="R51" t="n">
-        <v>6991201</v>
+        <v>6991356</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6673,17 +6656,17 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Minst 18 plantor och 1 vinterståndare inom ca 0,5 m2 yta söder om ett dike i barrblandskog.</t>
+          <t>Rikligt med fruktkroppar i en stående döende gran med full längd.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6698,7 +6681,27 @@
       </c>
       <c r="AH51" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM51" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -6716,10 +6719,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129762594</v>
+        <v>129762601</v>
       </c>
       <c r="B52" t="n">
-        <v>57735</v>
+        <v>57896</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6727,29 +6730,33 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -6763,10 +6770,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>473355</v>
+        <v>473628</v>
       </c>
       <c r="R52" t="n">
-        <v>6991512</v>
+        <v>6991288</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6803,7 +6810,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran vid hyggeskanten.</t>
+          <t>Minst 2 individer med lockläte i flerskiktad barrblandskog med inslag av klena björkar och björkhögstubbar.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6817,27 +6824,7 @@
       </c>
       <c r="AH52" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ52" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK52" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO52" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Barrträd</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -6855,46 +6842,50 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129762601</v>
+        <v>129762627</v>
       </c>
       <c r="B53" t="n">
-        <v>57895</v>
+        <v>98769</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr"/>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N53" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -6906,10 +6897,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>473628</v>
+        <v>473137</v>
       </c>
       <c r="R53" t="n">
-        <v>6991288</v>
+        <v>6991201</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6946,7 +6937,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Minst 2 individer med lockläte i flerskiktad barrblandskog med inslag av klena björkar och björkhögstubbar.</t>
+          <t>Minst 18 plantor och 1 vinterståndare inom ca 0,5 m2 yta söder om ett dike i barrblandskog.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6955,12 +6946,13 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
-          <t>Barrträd</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -6978,10 +6970,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129762656</v>
+        <v>129762594</v>
       </c>
       <c r="B54" t="n">
-        <v>91607</v>
+        <v>57736</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6989,37 +6981,46 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>473615</v>
+        <v>473355</v>
       </c>
       <c r="R54" t="n">
-        <v>6991356</v>
+        <v>6991512</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7046,17 +7047,17 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Rikligt med fruktkroppar i en stående döende gran med full längd.</t>
+          <t>Ringhack, färska, på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7065,7 +7066,6 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -7112,7 +7112,7 @@
         <v>129762653</v>
       </c>
       <c r="B55" t="n">
-        <v>91583</v>
+        <v>91584</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7244,10 +7244,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129762600</v>
+        <v>129762556</v>
       </c>
       <c r="B56" t="n">
-        <v>57895</v>
+        <v>91588</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7255,50 +7255,41 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>473307</v>
+        <v>473292</v>
       </c>
       <c r="R56" t="n">
-        <v>6991179</v>
+        <v>6991191</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7335,7 +7326,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Minst 1 talltita med lockläte. Ev. fans fler individer på fyndplatsen där det är flerskiktad barrskog.</t>
+          <t>Växer i en död granstam av en rotvälta.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7344,12 +7335,33 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ56" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK56" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM56" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO56" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -7367,10 +7379,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129762556</v>
+        <v>129762600</v>
       </c>
       <c r="B57" t="n">
-        <v>91587</v>
+        <v>57896</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7378,41 +7390,50 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>473292</v>
+        <v>473307</v>
       </c>
       <c r="R57" t="n">
-        <v>6991191</v>
+        <v>6991179</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7449,7 +7470,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Växer i en död granstam av en rotvälta.</t>
+          <t>Minst 1 talltita med lockläte. Ev. fans fler individer på fyndplatsen där det är flerskiktad barrskog.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7458,33 +7479,12 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ57" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK57" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM57" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO57" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -7505,7 +7505,7 @@
         <v>129762596</v>
       </c>
       <c r="B58" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7641,10 +7641,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129762661</v>
+        <v>129762557</v>
       </c>
       <c r="B59" t="n">
-        <v>79075</v>
+        <v>91588</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7652,26 +7652,30 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -7679,10 +7683,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>473612</v>
+        <v>473560</v>
       </c>
       <c r="R59" t="n">
-        <v>6991344</v>
+        <v>6991376</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7709,17 +7713,17 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Fruktkroppar längs flera meter i en granlåga.</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7734,7 +7738,7 @@
       </c>
       <c r="AH59" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ59" t="inlineStr">
@@ -7749,12 +7753,12 @@
       </c>
       <c r="AM59" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO59" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -7772,10 +7776,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129762557</v>
+        <v>129762661</v>
       </c>
       <c r="B60" t="n">
-        <v>91587</v>
+        <v>79076</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7783,30 +7787,26 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K60" t="inlineStr"/>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -7814,10 +7814,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>473560</v>
+        <v>473612</v>
       </c>
       <c r="R60" t="n">
-        <v>6991376</v>
+        <v>6991344</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7844,17 +7844,17 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Fruktkroppar längs flera meter i en granlåga.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7869,7 +7869,7 @@
       </c>
       <c r="AH60" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ60" t="inlineStr">
@@ -7884,12 +7884,12 @@
       </c>
       <c r="AM60" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO60" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
@@ -7910,7 +7910,7 @@
         <v>129762628</v>
       </c>
       <c r="B61" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -8038,7 +8038,7 @@
         <v>129762598</v>
       </c>
       <c r="B62" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8165,7 +8165,7 @@
         <v>129762629</v>
       </c>
       <c r="B63" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>

--- a/artfynd/A 48959-2025 artfynd.xlsx
+++ b/artfynd/A 48959-2025 artfynd.xlsx
@@ -1375,42 +1375,42 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129733686</v>
+        <v>129733685</v>
       </c>
       <c r="B9" t="n">
-        <v>98769</v>
+        <v>57733</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1418,10 +1418,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>473562</v>
+        <v>473633</v>
       </c>
       <c r="R9" t="n">
-        <v>6991360</v>
+        <v>6991388</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1456,13 +1456,17 @@
           <t>2025-11-05</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Färska hackspår.</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1481,42 +1485,42 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129733685</v>
+        <v>129733686</v>
       </c>
       <c r="B10" t="n">
-        <v>57733</v>
+        <v>98769</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1524,10 +1528,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>473633</v>
+        <v>473562</v>
       </c>
       <c r="R10" t="n">
-        <v>6991388</v>
+        <v>6991360</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1562,17 +1566,13 @@
           <t>2025-11-05</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Färska hackspår.</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -4365,65 +4365,48 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129762630</v>
+        <v>129762660</v>
       </c>
       <c r="B34" t="n">
-        <v>98769</v>
+        <v>79076</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr"/>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>473588</v>
+        <v>473564</v>
       </c>
       <c r="R34" t="n">
-        <v>6991340</v>
+        <v>6991395</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4460,7 +4443,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Minst 6 plantor och 1 vinterståndare inom ca 0,5 m2 yta precis intill korallrot i gammal barrblandskog.</t>
+          <t>På bark av tall.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4476,6 +4459,26 @@
       <c r="AH34" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM34" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4493,53 +4496,65 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129762664</v>
+        <v>129762630</v>
       </c>
       <c r="B35" t="n">
-        <v>98686</v>
+        <v>98769</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>473659</v>
+        <v>473588</v>
       </c>
       <c r="R35" t="n">
-        <v>6991313</v>
+        <v>6991340</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4566,17 +4581,17 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Minst 1 vinterståndare.</t>
+          <t>Minst 6 plantor och 1 vinterståndare inom ca 0,5 m2 yta precis intill korallrot i gammal barrblandskog.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4609,37 +4624,42 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129762660</v>
+        <v>129762664</v>
       </c>
       <c r="B36" t="n">
-        <v>79076</v>
+        <v>98686</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4647,10 +4667,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>473564</v>
+        <v>473659</v>
       </c>
       <c r="R36" t="n">
-        <v>6991395</v>
+        <v>6991313</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4677,17 +4697,17 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>På bark av tall.</t>
+          <t>Minst 1 vinterståndare.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4703,26 +4723,6 @@
       <c r="AH36" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>

--- a/artfynd/A 48959-2025 artfynd.xlsx
+++ b/artfynd/A 48959-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129733690</v>
       </c>
       <c r="B2" t="n">
-        <v>91584</v>
+        <v>91589</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129733694</v>
       </c>
       <c r="B3" t="n">
-        <v>91584</v>
+        <v>91589</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129733684</v>
+        <v>129733680</v>
       </c>
       <c r="B4" t="n">
-        <v>57736</v>
+        <v>91593</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,50 +880,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>473270</v>
+        <v>473498</v>
       </c>
       <c r="R4" t="n">
-        <v>6991065</v>
+        <v>6991415</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -956,11 +940,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-11-05</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Observation av en födosökande individ av tretåig hackspett. Var dock svårt att se om det var en hona eller hane. I skogen omkring fyndplatsen finns höga livsmiljövärden för tretåig hackspett baserat på volymen stående död ved.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -987,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129733680</v>
+        <v>129733693</v>
       </c>
       <c r="B5" t="n">
-        <v>91588</v>
+        <v>91589</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -998,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1022,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>473498</v>
+        <v>473343</v>
       </c>
       <c r="R5" t="n">
-        <v>6991415</v>
+        <v>6991073</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1084,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129733693</v>
+        <v>129733684</v>
       </c>
       <c r="B6" t="n">
-        <v>91584</v>
+        <v>57736</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1095,34 +1074,50 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>473343</v>
+        <v>473270</v>
       </c>
       <c r="R6" t="n">
-        <v>6991073</v>
+        <v>6991065</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1155,6 +1150,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Observation av en födosökande individ av tretåig hackspett. Var dock svårt att se om det var en hona eller hane. I skogen omkring fyndplatsen finns höga livsmiljövärden för tretåig hackspett baserat på volymen stående död ved.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1184,7 +1184,7 @@
         <v>129733695</v>
       </c>
       <c r="B7" t="n">
-        <v>91584</v>
+        <v>91589</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1281,7 +1281,7 @@
         <v>129733692</v>
       </c>
       <c r="B8" t="n">
-        <v>91584</v>
+        <v>91589</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1375,10 +1375,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129733685</v>
+        <v>129733689</v>
       </c>
       <c r="B9" t="n">
-        <v>57733</v>
+        <v>91589</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1386,42 +1386,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>1108</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>473633</v>
+        <v>473505</v>
       </c>
       <c r="R9" t="n">
-        <v>6991388</v>
+        <v>6991422</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1454,11 +1446,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-11-05</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Färska hackspår.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1485,53 +1472,41 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129733686</v>
+        <v>129733696</v>
       </c>
       <c r="B10" t="n">
-        <v>98769</v>
+        <v>91613</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>473562</v>
+        <v>473472</v>
       </c>
       <c r="R10" t="n">
-        <v>6991360</v>
+        <v>6991545</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1572,7 +1547,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1591,10 +1565,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129733689</v>
+        <v>129733685</v>
       </c>
       <c r="B11" t="n">
-        <v>91584</v>
+        <v>57733</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1602,34 +1576,42 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1108</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>473505</v>
+        <v>473633</v>
       </c>
       <c r="R11" t="n">
-        <v>6991422</v>
+        <v>6991388</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1662,6 +1644,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Färska hackspår.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1688,41 +1675,53 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129733696</v>
+        <v>129733686</v>
       </c>
       <c r="B12" t="n">
-        <v>91608</v>
+        <v>98774</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>473472</v>
+        <v>473562</v>
       </c>
       <c r="R12" t="n">
-        <v>6991545</v>
+        <v>6991360</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1763,6 +1762,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1784,7 +1784,7 @@
         <v>129733681</v>
       </c>
       <c r="B13" t="n">
-        <v>91588</v>
+        <v>91593</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1881,7 +1881,7 @@
         <v>129733687</v>
       </c>
       <c r="B14" t="n">
-        <v>91584</v>
+        <v>91589</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1978,7 +1978,7 @@
         <v>129733691</v>
       </c>
       <c r="B15" t="n">
-        <v>91584</v>
+        <v>91589</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         <v>129733683</v>
       </c>
       <c r="B16" t="n">
-        <v>92306</v>
+        <v>92311</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2172,7 +2172,7 @@
         <v>129733682</v>
       </c>
       <c r="B17" t="n">
-        <v>92306</v>
+        <v>92311</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2269,7 +2269,7 @@
         <v>129733688</v>
       </c>
       <c r="B18" t="n">
-        <v>91584</v>
+        <v>91589</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2366,7 +2366,7 @@
         <v>129762562</v>
       </c>
       <c r="B19" t="n">
-        <v>92306</v>
+        <v>92311</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2501,7 +2501,7 @@
         <v>129762650</v>
       </c>
       <c r="B20" t="n">
-        <v>91584</v>
+        <v>91589</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2633,10 +2633,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129762643</v>
+        <v>129762639</v>
       </c>
       <c r="B21" t="n">
-        <v>91584</v>
+        <v>91589</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2675,10 +2675,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>473253</v>
+        <v>473289</v>
       </c>
       <c r="R21" t="n">
-        <v>6991258</v>
+        <v>6991144</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2715,7 +2715,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en stående döende gran.</t>
+          <t>I två stående döda granar.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2745,12 +2745,12 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -2771,7 +2771,7 @@
         <v>129762642</v>
       </c>
       <c r="B22" t="n">
-        <v>91584</v>
+        <v>91589</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2899,10 +2899,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129762639</v>
+        <v>129762643</v>
       </c>
       <c r="B23" t="n">
-        <v>91584</v>
+        <v>91589</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2941,10 +2941,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>473289</v>
+        <v>473253</v>
       </c>
       <c r="R23" t="n">
-        <v>6991144</v>
+        <v>6991258</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2981,7 +2981,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>I två stående döda granar.</t>
+          <t>Flera fruktkroppar i en stående döende gran.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3011,12 +3011,12 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3034,10 +3034,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129762652</v>
+        <v>129762654</v>
       </c>
       <c r="B24" t="n">
-        <v>91584</v>
+        <v>91589</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3064,11 +3064,7 @@
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3076,10 +3072,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>473621</v>
+        <v>473668</v>
       </c>
       <c r="R24" t="n">
-        <v>6991345</v>
+        <v>6991289</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3106,17 +3102,17 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en stående död gran med full längd och 35 cm i brösthöjdsdiameter.</t>
+          <t>Flera fruktkroppar i en granstubbe.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3146,12 +3142,12 @@
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Stubbe</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3169,10 +3165,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129762654</v>
+        <v>129762652</v>
       </c>
       <c r="B25" t="n">
-        <v>91584</v>
+        <v>91589</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3199,7 +3195,11 @@
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3207,10 +3207,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>473668</v>
+        <v>473621</v>
       </c>
       <c r="R25" t="n">
-        <v>6991289</v>
+        <v>6991345</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3237,17 +3237,17 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en granstubbe.</t>
+          <t>Flera fruktkroppar i en stående död gran med full längd och 35 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3277,12 +3277,12 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>Stubbe</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Stump # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3300,10 +3300,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129762649</v>
+        <v>129762662</v>
       </c>
       <c r="B26" t="n">
-        <v>91584</v>
+        <v>79081</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3311,30 +3311,26 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3342,10 +3338,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>473475</v>
+        <v>473631</v>
       </c>
       <c r="R26" t="n">
-        <v>6991471</v>
+        <v>6991321</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3372,17 +3368,17 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i stambasen av en stående död gran (24 cm BHD) med full längd. På fyndplatsen finns stående död ved i en volym som indikerar minst högt livsmiljövärde för tretåig hackspett.</t>
+          <t>På gran i granskog.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3412,12 +3408,12 @@
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3435,52 +3431,65 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129762641</v>
+        <v>129762632</v>
       </c>
       <c r="B27" t="n">
-        <v>91584</v>
+        <v>98774</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1108</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>473229</v>
+        <v>473644</v>
       </c>
       <c r="R27" t="n">
-        <v>6991116</v>
+        <v>6991272</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3507,17 +3516,17 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Gott om fruktkroppar i en stående död gran med full längd.</t>
+          <t>Minst 54 plantor inom ca 2 m2 yta strax norr om ett dike.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3533,26 +3542,6 @@
       <c r="AH27" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3570,10 +3559,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129762662</v>
+        <v>129762641</v>
       </c>
       <c r="B28" t="n">
-        <v>79076</v>
+        <v>91589</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3581,26 +3570,30 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3608,10 +3601,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>473631</v>
+        <v>473229</v>
       </c>
       <c r="R28" t="n">
-        <v>6991321</v>
+        <v>6991116</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3638,17 +3631,17 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>På gran i granskog.</t>
+          <t>Gott om fruktkroppar i en stående död gran med full längd.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3678,12 +3671,12 @@
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3701,65 +3694,52 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129762632</v>
+        <v>129762649</v>
       </c>
       <c r="B29" t="n">
-        <v>98769</v>
+        <v>91589</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>1108</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr"/>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>473644</v>
+        <v>473475</v>
       </c>
       <c r="R29" t="n">
-        <v>6991272</v>
+        <v>6991471</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3786,17 +3766,17 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Minst 54 plantor inom ca 2 m2 yta strax norr om ett dike.</t>
+          <t>Flera fruktkroppar i stambasen av en stående död gran (24 cm BHD) med full längd. På fyndplatsen finns stående död ved i en volym som indikerar minst högt livsmiljövärde för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3812,6 +3792,26 @@
       <c r="AH29" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -3832,7 +3832,7 @@
         <v>129762647</v>
       </c>
       <c r="B30" t="n">
-        <v>91584</v>
+        <v>91589</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3967,7 +3967,7 @@
         <v>129762640</v>
       </c>
       <c r="B31" t="n">
-        <v>91584</v>
+        <v>91589</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4102,7 +4102,7 @@
         <v>129762663</v>
       </c>
       <c r="B32" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4233,7 +4233,7 @@
         <v>129762651</v>
       </c>
       <c r="B33" t="n">
-        <v>91584</v>
+        <v>91589</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4365,37 +4365,42 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129762660</v>
+        <v>129762664</v>
       </c>
       <c r="B34" t="n">
-        <v>79076</v>
+        <v>98691</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4403,10 +4408,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>473564</v>
+        <v>473659</v>
       </c>
       <c r="R34" t="n">
-        <v>6991395</v>
+        <v>6991313</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4433,17 +4438,17 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>På bark av tall.</t>
+          <t>Minst 1 vinterståndare.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4459,26 +4464,6 @@
       <c r="AH34" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4496,65 +4481,48 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129762630</v>
+        <v>129762660</v>
       </c>
       <c r="B35" t="n">
-        <v>98769</v>
+        <v>79081</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr"/>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>473588</v>
+        <v>473564</v>
       </c>
       <c r="R35" t="n">
-        <v>6991340</v>
+        <v>6991395</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4591,7 +4559,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Minst 6 plantor och 1 vinterståndare inom ca 0,5 m2 yta precis intill korallrot i gammal barrblandskog.</t>
+          <t>På bark av tall.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4607,6 +4575,26 @@
       <c r="AH35" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM35" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4624,53 +4612,65 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129762664</v>
+        <v>129762630</v>
       </c>
       <c r="B36" t="n">
-        <v>98686</v>
+        <v>98774</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>473659</v>
+        <v>473588</v>
       </c>
       <c r="R36" t="n">
-        <v>6991313</v>
+        <v>6991340</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4697,17 +4697,17 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Minst 1 vinterståndare.</t>
+          <t>Minst 6 plantor och 1 vinterståndare inom ca 0,5 m2 yta precis intill korallrot i gammal barrblandskog.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4740,10 +4740,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129762593</v>
+        <v>129762644</v>
       </c>
       <c r="B37" t="n">
-        <v>57736</v>
+        <v>91589</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4751,46 +4751,41 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>473284</v>
+        <v>473430</v>
       </c>
       <c r="R37" t="n">
-        <v>6991191</v>
+        <v>6991442</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4827,7 +4822,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en gran i granskog.</t>
+          <t>I en granhögstubbe.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4836,12 +4831,13 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ37" t="inlineStr">
@@ -4856,12 +4852,12 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -4879,10 +4875,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129762644</v>
+        <v>129762593</v>
       </c>
       <c r="B38" t="n">
-        <v>91584</v>
+        <v>57736</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4890,41 +4886,46 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>473430</v>
+        <v>473284</v>
       </c>
       <c r="R38" t="n">
-        <v>6991442</v>
+        <v>6991191</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4961,7 +4962,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>I en granhögstubbe.</t>
+          <t>Ringhack, äldre, på stambasen av en gran i granskog.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4970,13 +4971,12 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ38" t="inlineStr">
@@ -4991,12 +4991,12 @@
       </c>
       <c r="AM38" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5017,7 +5017,7 @@
         <v>129762645</v>
       </c>
       <c r="B39" t="n">
-        <v>91584</v>
+        <v>91589</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5149,10 +5149,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129762655</v>
+        <v>129762603</v>
       </c>
       <c r="B40" t="n">
-        <v>91608</v>
+        <v>57733</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5160,37 +5160,46 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr"/>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>473666</v>
+        <v>473521</v>
       </c>
       <c r="R40" t="n">
-        <v>6991307</v>
+        <v>6991419</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5227,7 +5236,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en levande gran.</t>
+          <t>Rejäla hackspår i stambasen av en stående död gran med full längd.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5236,33 +5245,12 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5422,7 +5410,7 @@
         <v>129762620</v>
       </c>
       <c r="B42" t="n">
-        <v>98673</v>
+        <v>98678</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5547,10 +5535,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129762603</v>
+        <v>129762655</v>
       </c>
       <c r="B43" t="n">
-        <v>57733</v>
+        <v>91613</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5558,46 +5546,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>473521</v>
+        <v>473666</v>
       </c>
       <c r="R43" t="n">
-        <v>6991419</v>
+        <v>6991307</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5634,7 +5613,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Rejäla hackspår i stambasen av en stående död gran med full längd.</t>
+          <t>Flera fruktkroppar i en levande gran.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5643,12 +5622,33 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM43" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -5669,7 +5669,7 @@
         <v>129762648</v>
       </c>
       <c r="B44" t="n">
-        <v>91584</v>
+        <v>91589</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5804,7 +5804,7 @@
         <v>129762659</v>
       </c>
       <c r="B45" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5935,7 +5935,7 @@
         <v>129762631</v>
       </c>
       <c r="B46" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6060,10 +6060,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129762646</v>
+        <v>129762658</v>
       </c>
       <c r="B47" t="n">
-        <v>91584</v>
+        <v>79081</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6071,30 +6071,26 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K47" t="inlineStr"/>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -6102,10 +6098,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>473393</v>
+        <v>473495</v>
       </c>
       <c r="R47" t="n">
-        <v>6991465</v>
+        <v>6991469</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6142,7 +6138,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>I en stående död gran.</t>
+          <t>På flera både döda och levande granar.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6157,7 +6153,7 @@
       </c>
       <c r="AH47" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ47" t="inlineStr">
@@ -6172,12 +6168,12 @@
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6195,10 +6191,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129762658</v>
+        <v>129762646</v>
       </c>
       <c r="B48" t="n">
-        <v>79076</v>
+        <v>91589</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6206,26 +6202,30 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -6233,10 +6233,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>473495</v>
+        <v>473393</v>
       </c>
       <c r="R48" t="n">
-        <v>6991469</v>
+        <v>6991465</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6273,7 +6273,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>På flera både döda och levande granar.</t>
+          <t>I en stående död gran.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6288,7 +6288,7 @@
       </c>
       <c r="AH48" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ48" t="inlineStr">
@@ -6303,12 +6303,12 @@
       </c>
       <c r="AM48" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6591,7 +6591,7 @@
         <v>129762656</v>
       </c>
       <c r="B51" t="n">
-        <v>91608</v>
+        <v>91613</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6719,10 +6719,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129762601</v>
+        <v>129762594</v>
       </c>
       <c r="B52" t="n">
-        <v>57896</v>
+        <v>57736</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6730,33 +6730,29 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -6770,10 +6766,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>473628</v>
+        <v>473355</v>
       </c>
       <c r="R52" t="n">
-        <v>6991288</v>
+        <v>6991512</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6810,7 +6806,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Minst 2 individer med lockläte i flerskiktad barrblandskog med inslag av klena björkar och björkhögstubbar.</t>
+          <t>Ringhack, färska, på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6824,7 +6820,27 @@
       </c>
       <c r="AH52" t="inlineStr">
         <is>
-          <t>Barrträd</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM52" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -6842,50 +6858,46 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129762627</v>
+        <v>129762601</v>
       </c>
       <c r="B53" t="n">
-        <v>98769</v>
+        <v>57896</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N53" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -6897,10 +6909,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>473137</v>
+        <v>473628</v>
       </c>
       <c r="R53" t="n">
-        <v>6991201</v>
+        <v>6991288</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6937,7 +6949,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Minst 18 plantor och 1 vinterståndare inom ca 0,5 m2 yta söder om ett dike i barrblandskog.</t>
+          <t>Minst 2 individer med lockläte i flerskiktad barrblandskog med inslag av klena björkar och björkhögstubbar.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6946,13 +6958,12 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Barrträd</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -6970,42 +6981,50 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129762594</v>
+        <v>129762627</v>
       </c>
       <c r="B54" t="n">
-        <v>57736</v>
+        <v>98774</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N54" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -7017,10 +7036,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>473355</v>
+        <v>473137</v>
       </c>
       <c r="R54" t="n">
-        <v>6991512</v>
+        <v>6991201</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7057,7 +7076,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran vid hyggeskanten.</t>
+          <t>Minst 18 plantor och 1 vinterståndare inom ca 0,5 m2 yta söder om ett dike i barrblandskog.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7066,32 +7085,13 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ54" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK54" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM54" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO54" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -7109,10 +7109,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129762653</v>
+        <v>129762600</v>
       </c>
       <c r="B55" t="n">
-        <v>91584</v>
+        <v>57896</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7120,41 +7120,50 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1108</v>
+        <v>103021</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>473644</v>
+        <v>473307</v>
       </c>
       <c r="R55" t="n">
-        <v>6991369</v>
+        <v>6991179</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7181,17 +7190,17 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en stående död gran med full längd.</t>
+          <t>Minst 1 talltita med lockläte. Ev. fans fler individer på fyndplatsen där det är flerskiktad barrskog.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7200,33 +7209,12 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ55" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK55" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM55" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO55" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -7244,10 +7232,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129762556</v>
+        <v>129762653</v>
       </c>
       <c r="B56" t="n">
-        <v>91588</v>
+        <v>91589</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7255,21 +7243,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -7286,10 +7274,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>473292</v>
+        <v>473644</v>
       </c>
       <c r="R56" t="n">
-        <v>6991191</v>
+        <v>6991369</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7316,17 +7304,17 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Växer i en död granstam av en rotvälta.</t>
+          <t>Flera fruktkroppar i en stående död gran med full längd.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7356,12 +7344,12 @@
       </c>
       <c r="AM56" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -7379,10 +7367,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129762600</v>
+        <v>129762556</v>
       </c>
       <c r="B57" t="n">
-        <v>57896</v>
+        <v>91593</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7390,50 +7378,41 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>473307</v>
+        <v>473292</v>
       </c>
       <c r="R57" t="n">
-        <v>6991179</v>
+        <v>6991191</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7470,7 +7449,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Minst 1 talltita med lockläte. Ev. fans fler individer på fyndplatsen där det är flerskiktad barrskog.</t>
+          <t>Växer i en död granstam av en rotvälta.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7479,12 +7458,33 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ57" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK57" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM57" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO57" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -7641,10 +7641,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129762557</v>
+        <v>129762661</v>
       </c>
       <c r="B59" t="n">
-        <v>91588</v>
+        <v>79081</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7652,30 +7652,26 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K59" t="inlineStr"/>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -7683,10 +7679,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>473560</v>
+        <v>473612</v>
       </c>
       <c r="R59" t="n">
-        <v>6991376</v>
+        <v>6991344</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7713,17 +7709,17 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Fruktkroppar längs flera meter i en granlåga.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7738,7 +7734,7 @@
       </c>
       <c r="AH59" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ59" t="inlineStr">
@@ -7753,12 +7749,12 @@
       </c>
       <c r="AM59" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO59" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -7776,10 +7772,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129762661</v>
+        <v>129762557</v>
       </c>
       <c r="B60" t="n">
-        <v>79076</v>
+        <v>91593</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7787,26 +7783,30 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -7814,10 +7814,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>473612</v>
+        <v>473560</v>
       </c>
       <c r="R60" t="n">
-        <v>6991344</v>
+        <v>6991376</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7844,17 +7844,17 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Fruktkroppar längs flera meter i en granlåga.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7869,7 +7869,7 @@
       </c>
       <c r="AH60" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ60" t="inlineStr">
@@ -7884,12 +7884,12 @@
       </c>
       <c r="AM60" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO60" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
@@ -7910,7 +7910,7 @@
         <v>129762628</v>
       </c>
       <c r="B61" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -8165,7 +8165,7 @@
         <v>129762629</v>
       </c>
       <c r="B63" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>

--- a/artfynd/A 48959-2025 artfynd.xlsx
+++ b/artfynd/A 48959-2025 artfynd.xlsx
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129733680</v>
+        <v>129733684</v>
       </c>
       <c r="B4" t="n">
-        <v>91593</v>
+        <v>57736</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,34 +880,50 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>473498</v>
+        <v>473270</v>
       </c>
       <c r="R4" t="n">
-        <v>6991415</v>
+        <v>6991065</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -940,6 +956,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Observation av en födosökande individ av tretåig hackspett. Var dock svårt att se om det var en hona eller hane. I skogen omkring fyndplatsen finns höga livsmiljövärden för tretåig hackspett baserat på volymen stående död ved.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -966,10 +987,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129733693</v>
+        <v>129733680</v>
       </c>
       <c r="B5" t="n">
-        <v>91589</v>
+        <v>91593</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +998,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1022,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>473343</v>
+        <v>473498</v>
       </c>
       <c r="R5" t="n">
-        <v>6991073</v>
+        <v>6991415</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,10 +1084,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129733684</v>
+        <v>129733693</v>
       </c>
       <c r="B6" t="n">
-        <v>57736</v>
+        <v>91589</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,50 +1095,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>473270</v>
+        <v>473343</v>
       </c>
       <c r="R6" t="n">
-        <v>6991065</v>
+        <v>6991073</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1150,11 +1155,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-11-05</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Observation av en födosökande individ av tretåig hackspett. Var dock svårt att se om det var en hona eller hane. I skogen omkring fyndplatsen finns höga livsmiljövärden för tretåig hackspett baserat på volymen stående död ved.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1781,10 +1781,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129733681</v>
+        <v>129733687</v>
       </c>
       <c r="B13" t="n">
-        <v>91593</v>
+        <v>91589</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1792,21 +1792,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1816,10 +1816,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>473323</v>
+        <v>473216</v>
       </c>
       <c r="R13" t="n">
-        <v>6991104</v>
+        <v>6991223</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1878,10 +1878,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129733687</v>
+        <v>129733681</v>
       </c>
       <c r="B14" t="n">
-        <v>91589</v>
+        <v>91593</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1889,21 +1889,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1913,10 +1913,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>473216</v>
+        <v>473323</v>
       </c>
       <c r="R14" t="n">
-        <v>6991223</v>
+        <v>6991104</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2363,32 +2363,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129762562</v>
+        <v>129762650</v>
       </c>
       <c r="B19" t="n">
-        <v>92311</v>
+        <v>91589</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>3298</v>
+        <v>1108</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2405,10 +2405,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>473408</v>
+        <v>473464</v>
       </c>
       <c r="R19" t="n">
-        <v>6991459</v>
+        <v>6991416</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Rikligt med fruktkroppar i stambasen av en hyfsat grov stående död gran med full längd.</t>
+          <t>Flera fruktkroppar i stambasen av en stående döende grov gran.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2498,7 +2498,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129762650</v>
+        <v>129762639</v>
       </c>
       <c r="B20" t="n">
         <v>91589</v>
@@ -2540,10 +2540,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>473464</v>
+        <v>473289</v>
       </c>
       <c r="R20" t="n">
-        <v>6991416</v>
+        <v>6991144</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2580,7 +2580,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i stambasen av en stående döende grov gran.</t>
+          <t>I två stående döda granar.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2595,7 +2595,7 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
@@ -2633,7 +2633,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129762639</v>
+        <v>129762642</v>
       </c>
       <c r="B21" t="n">
         <v>91589</v>
@@ -2663,11 +2663,7 @@
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2675,10 +2671,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>473289</v>
+        <v>473243</v>
       </c>
       <c r="R21" t="n">
-        <v>6991144</v>
+        <v>6991220</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2715,7 +2711,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>I två stående döda granar.</t>
+          <t>I stambasen av en döende gran.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2745,12 +2741,12 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -2768,7 +2764,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129762642</v>
+        <v>129762643</v>
       </c>
       <c r="B22" t="n">
         <v>91589</v>
@@ -2798,7 +2794,11 @@
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2806,10 +2806,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>473243</v>
+        <v>473253</v>
       </c>
       <c r="R22" t="n">
-        <v>6991220</v>
+        <v>6991258</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2846,7 +2846,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>I stambasen av en döende gran.</t>
+          <t>Flera fruktkroppar i en stående döende gran.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2899,32 +2899,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129762643</v>
+        <v>129762562</v>
       </c>
       <c r="B23" t="n">
-        <v>91589</v>
+        <v>92311</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1108</v>
+        <v>3298</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2941,10 +2941,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>473253</v>
+        <v>473408</v>
       </c>
       <c r="R23" t="n">
-        <v>6991258</v>
+        <v>6991459</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2981,7 +2981,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en stående döende gran.</t>
+          <t>Rikligt med fruktkroppar i stambasen av en hyfsat grov stående död gran med full längd.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
@@ -3011,12 +3011,12 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3300,10 +3300,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129762662</v>
+        <v>129762641</v>
       </c>
       <c r="B26" t="n">
-        <v>79081</v>
+        <v>91589</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3311,26 +3311,30 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3338,10 +3342,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>473631</v>
+        <v>473229</v>
       </c>
       <c r="R26" t="n">
-        <v>6991321</v>
+        <v>6991116</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3368,17 +3372,17 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>På gran i granskog.</t>
+          <t>Gott om fruktkroppar i en stående död gran med full längd.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3408,12 +3412,12 @@
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3431,65 +3435,52 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129762632</v>
+        <v>129762649</v>
       </c>
       <c r="B27" t="n">
-        <v>98774</v>
+        <v>91589</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>1108</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr"/>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>473644</v>
+        <v>473475</v>
       </c>
       <c r="R27" t="n">
-        <v>6991272</v>
+        <v>6991471</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3516,17 +3507,17 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Minst 54 plantor inom ca 2 m2 yta strax norr om ett dike.</t>
+          <t>Flera fruktkroppar i stambasen av en stående död gran (24 cm BHD) med full längd. På fyndplatsen finns stående död ved i en volym som indikerar minst högt livsmiljövärde för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3542,6 +3533,26 @@
       <c r="AH27" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3559,10 +3570,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129762641</v>
+        <v>129762662</v>
       </c>
       <c r="B28" t="n">
-        <v>91589</v>
+        <v>79081</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3570,30 +3581,26 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3601,10 +3608,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>473229</v>
+        <v>473631</v>
       </c>
       <c r="R28" t="n">
-        <v>6991116</v>
+        <v>6991321</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3631,17 +3638,17 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Gott om fruktkroppar i en stående död gran med full längd.</t>
+          <t>På gran i granskog.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3671,12 +3678,12 @@
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3694,52 +3701,65 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129762649</v>
+        <v>129762632</v>
       </c>
       <c r="B29" t="n">
-        <v>91589</v>
+        <v>98774</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1108</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>473475</v>
+        <v>473644</v>
       </c>
       <c r="R29" t="n">
-        <v>6991471</v>
+        <v>6991272</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3766,17 +3786,17 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i stambasen av en stående död gran (24 cm BHD) med full längd. På fyndplatsen finns stående död ved i en volym som indikerar minst högt livsmiljövärde för tretåig hackspett.</t>
+          <t>Minst 54 plantor inom ca 2 m2 yta strax norr om ett dike.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3792,26 +3812,6 @@
       <c r="AH29" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -3964,10 +3964,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129762640</v>
+        <v>129762663</v>
       </c>
       <c r="B31" t="n">
-        <v>91589</v>
+        <v>79081</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3975,30 +3975,26 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -4006,10 +4002,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>473215</v>
+        <v>473588</v>
       </c>
       <c r="R31" t="n">
-        <v>6991103</v>
+        <v>6991409</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4036,17 +4032,17 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>I en smal stående död gran.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4061,7 +4057,7 @@
       </c>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ31" t="inlineStr">
@@ -4076,12 +4072,12 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4099,10 +4095,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129762663</v>
+        <v>129762640</v>
       </c>
       <c r="B32" t="n">
-        <v>79081</v>
+        <v>91589</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4110,26 +4106,30 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4137,10 +4137,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>473588</v>
+        <v>473215</v>
       </c>
       <c r="R32" t="n">
-        <v>6991409</v>
+        <v>6991103</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4167,17 +4167,17 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>I en smal stående död gran.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4192,7 +4192,7 @@
       </c>
       <c r="AH32" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ32" t="inlineStr">
@@ -4207,12 +4207,12 @@
       </c>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4230,10 +4230,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129762651</v>
+        <v>129762660</v>
       </c>
       <c r="B33" t="n">
-        <v>91589</v>
+        <v>79081</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4241,30 +4241,26 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4272,10 +4268,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>473497</v>
+        <v>473564</v>
       </c>
       <c r="R33" t="n">
-        <v>6991392</v>
+        <v>6991395</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4312,7 +4308,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en levande gran.</t>
+          <t>På bark av tall.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4332,22 +4328,22 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4365,53 +4361,65 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129762664</v>
+        <v>129762630</v>
       </c>
       <c r="B34" t="n">
-        <v>98691</v>
+        <v>98774</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>473659</v>
+        <v>473588</v>
       </c>
       <c r="R34" t="n">
-        <v>6991313</v>
+        <v>6991340</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4438,17 +4446,17 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Minst 1 vinterståndare.</t>
+          <t>Minst 6 plantor och 1 vinterståndare inom ca 0,5 m2 yta precis intill korallrot i gammal barrblandskog.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4481,10 +4489,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129762660</v>
+        <v>129762651</v>
       </c>
       <c r="B35" t="n">
-        <v>79081</v>
+        <v>91589</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4492,26 +4500,30 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4519,10 +4531,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>473564</v>
+        <v>473497</v>
       </c>
       <c r="R35" t="n">
-        <v>6991395</v>
+        <v>6991392</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4559,7 +4571,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>På bark av tall.</t>
+          <t>Flera fruktkroppar i en levande gran.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4579,22 +4591,22 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Pinus sylvestris</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4612,65 +4624,53 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129762630</v>
+        <v>129762664</v>
       </c>
       <c r="B36" t="n">
-        <v>98774</v>
+        <v>98691</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="L36" t="inlineStr"/>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>473588</v>
+        <v>473659</v>
       </c>
       <c r="R36" t="n">
-        <v>6991340</v>
+        <v>6991313</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4697,17 +4697,17 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Minst 6 plantor och 1 vinterståndare inom ca 0,5 m2 yta precis intill korallrot i gammal barrblandskog.</t>
+          <t>Minst 1 vinterståndare.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5268,10 +5268,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129762597</v>
+        <v>129762655</v>
       </c>
       <c r="B41" t="n">
-        <v>57736</v>
+        <v>91613</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5279,46 +5279,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>473383</v>
+        <v>473666</v>
       </c>
       <c r="R41" t="n">
-        <v>6991525</v>
+        <v>6991307</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5355,7 +5346,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Savhack (ringhack), färska, på en gran vid hyggeskanten.</t>
+          <t>Flera fruktkroppar i en levande gran.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5364,6 +5355,7 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5407,50 +5399,42 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129762620</v>
+        <v>129762597</v>
       </c>
       <c r="B42" t="n">
-        <v>98678</v>
+        <v>57736</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220093</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Châtel.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N42" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -5462,10 +5446,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>473586</v>
+        <v>473383</v>
       </c>
       <c r="R42" t="n">
-        <v>6991339</v>
+        <v>6991525</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5502,7 +5486,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>1 vinterståndare i gammal barrblandskog.</t>
+          <t>Savhack (ringhack), färska, på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5511,13 +5495,32 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM42" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5535,48 +5538,65 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129762655</v>
+        <v>129762620</v>
       </c>
       <c r="B43" t="n">
-        <v>91613</v>
+        <v>98678</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5432</v>
+        <v>220093</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
+          <t>Corallorhiza trifida</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr"/>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr"/>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>473666</v>
+        <v>473586</v>
       </c>
       <c r="R43" t="n">
-        <v>6991307</v>
+        <v>6991339</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5613,7 +5633,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en levande gran.</t>
+          <t>1 vinterståndare i gammal barrblandskog.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5628,27 +5648,7 @@
       </c>
       <c r="AH43" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -6060,10 +6060,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129762658</v>
+        <v>129762595</v>
       </c>
       <c r="B47" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6071,37 +6071,46 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>473495</v>
+        <v>473369</v>
       </c>
       <c r="R47" t="n">
-        <v>6991469</v>
+        <v>6991519</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6138,7 +6147,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>På flera både döda och levande granar.</t>
+          <t>Ringhack (savhack), färska, på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6147,7 +6156,6 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -6168,12 +6176,12 @@
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6326,10 +6334,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129762595</v>
+        <v>129762658</v>
       </c>
       <c r="B49" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6337,46 +6345,37 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>473369</v>
+        <v>473495</v>
       </c>
       <c r="R49" t="n">
-        <v>6991519</v>
+        <v>6991469</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6413,7 +6412,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en gran vid hyggeskanten.</t>
+          <t>På flera både döda och levande granar.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6422,6 +6421,7 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -6442,12 +6442,12 @@
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6588,10 +6588,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129762656</v>
+        <v>129762594</v>
       </c>
       <c r="B51" t="n">
-        <v>91613</v>
+        <v>57736</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6599,37 +6599,46 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>473615</v>
+        <v>473355</v>
       </c>
       <c r="R51" t="n">
-        <v>6991356</v>
+        <v>6991512</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6656,17 +6665,17 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Rikligt med fruktkroppar i en stående döende gran med full längd.</t>
+          <t>Ringhack, färska, på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6675,7 +6684,6 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -6719,10 +6727,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129762594</v>
+        <v>129762656</v>
       </c>
       <c r="B52" t="n">
-        <v>57736</v>
+        <v>91613</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6730,46 +6738,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>473355</v>
+        <v>473615</v>
       </c>
       <c r="R52" t="n">
-        <v>6991512</v>
+        <v>6991356</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6796,17 +6795,17 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran vid hyggeskanten.</t>
+          <t>Rikligt med fruktkroppar i en stående döende gran med full längd.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6815,6 +6814,7 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -7109,10 +7109,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129762600</v>
+        <v>129762653</v>
       </c>
       <c r="B55" t="n">
-        <v>57896</v>
+        <v>91589</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7120,50 +7120,41 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>103021</v>
+        <v>1108</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>473307</v>
+        <v>473644</v>
       </c>
       <c r="R55" t="n">
-        <v>6991179</v>
+        <v>6991369</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7190,17 +7181,17 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Minst 1 talltita med lockläte. Ev. fans fler individer på fyndplatsen där det är flerskiktad barrskog.</t>
+          <t>Flera fruktkroppar i en stående död gran med full längd.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7209,12 +7200,33 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK55" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM55" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -7232,10 +7244,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129762653</v>
+        <v>129762556</v>
       </c>
       <c r="B56" t="n">
-        <v>91589</v>
+        <v>91593</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7243,21 +7255,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -7274,10 +7286,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>473644</v>
+        <v>473292</v>
       </c>
       <c r="R56" t="n">
-        <v>6991369</v>
+        <v>6991191</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7304,17 +7316,17 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en stående död gran med full längd.</t>
+          <t>Växer i en död granstam av en rotvälta.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7344,12 +7356,12 @@
       </c>
       <c r="AM56" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -7367,10 +7379,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129762556</v>
+        <v>129762600</v>
       </c>
       <c r="B57" t="n">
-        <v>91593</v>
+        <v>57896</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7378,41 +7390,50 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>473292</v>
+        <v>473307</v>
       </c>
       <c r="R57" t="n">
-        <v>6991191</v>
+        <v>6991179</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7449,7 +7470,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Växer i en död granstam av en rotvälta.</t>
+          <t>Minst 1 talltita med lockläte. Ev. fans fler individer på fyndplatsen där det är flerskiktad barrskog.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7458,33 +7479,12 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ57" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK57" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM57" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO57" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>

--- a/artfynd/A 48959-2025 artfynd.xlsx
+++ b/artfynd/A 48959-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129733690</v>
+        <v>129733694</v>
       </c>
       <c r="B2" t="n">
         <v>91589</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>473509</v>
+        <v>473330</v>
       </c>
       <c r="R2" t="n">
-        <v>6991413</v>
+        <v>6991067</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,7 +772,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129733694</v>
+        <v>129733690</v>
       </c>
       <c r="B3" t="n">
         <v>91589</v>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>473330</v>
+        <v>473509</v>
       </c>
       <c r="R3" t="n">
-        <v>6991067</v>
+        <v>6991413</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129733684</v>
+        <v>129733693</v>
       </c>
       <c r="B4" t="n">
-        <v>57736</v>
+        <v>91589</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,50 +880,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>473270</v>
+        <v>473343</v>
       </c>
       <c r="R4" t="n">
-        <v>6991065</v>
+        <v>6991073</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -956,11 +940,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-11-05</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Observation av en födosökande individ av tretåig hackspett. Var dock svårt att se om det var en hona eller hane. I skogen omkring fyndplatsen finns höga livsmiljövärden för tretåig hackspett baserat på volymen stående död ved.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1084,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129733693</v>
+        <v>129733684</v>
       </c>
       <c r="B6" t="n">
-        <v>91589</v>
+        <v>57736</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1095,34 +1074,50 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>473343</v>
+        <v>473270</v>
       </c>
       <c r="R6" t="n">
-        <v>6991073</v>
+        <v>6991065</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1155,6 +1150,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Observation av en födosökande individ av tretåig hackspett. Var dock svårt att se om det var en hona eller hane. I skogen omkring fyndplatsen finns höga livsmiljövärden för tretåig hackspett baserat på volymen stående död ved.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1375,10 +1375,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129733689</v>
+        <v>129733696</v>
       </c>
       <c r="B9" t="n">
-        <v>91589</v>
+        <v>91613</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1386,23 +1386,19 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1410,10 +1406,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>473505</v>
+        <v>473472</v>
       </c>
       <c r="R9" t="n">
-        <v>6991422</v>
+        <v>6991545</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1472,10 +1468,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129733696</v>
+        <v>129733685</v>
       </c>
       <c r="B10" t="n">
-        <v>91613</v>
+        <v>57733</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1483,30 +1479,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>473472</v>
+        <v>473633</v>
       </c>
       <c r="R10" t="n">
-        <v>6991545</v>
+        <v>6991388</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1539,6 +1547,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Färska hackspår.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1565,10 +1578,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129733685</v>
+        <v>129733689</v>
       </c>
       <c r="B11" t="n">
-        <v>57733</v>
+        <v>91589</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1576,42 +1589,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>1108</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>473633</v>
+        <v>473505</v>
       </c>
       <c r="R11" t="n">
-        <v>6991388</v>
+        <v>6991422</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1644,11 +1649,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-11-05</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Färska hackspår.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1781,10 +1781,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129733687</v>
+        <v>129733681</v>
       </c>
       <c r="B13" t="n">
-        <v>91589</v>
+        <v>91593</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1792,21 +1792,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1816,10 +1816,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>473216</v>
+        <v>473323</v>
       </c>
       <c r="R13" t="n">
-        <v>6991223</v>
+        <v>6991104</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1878,10 +1878,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129733681</v>
+        <v>129733687</v>
       </c>
       <c r="B14" t="n">
-        <v>91593</v>
+        <v>91589</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1889,21 +1889,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1913,10 +1913,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>473323</v>
+        <v>473216</v>
       </c>
       <c r="R14" t="n">
-        <v>6991104</v>
+        <v>6991223</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2363,32 +2363,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129762650</v>
+        <v>129762562</v>
       </c>
       <c r="B19" t="n">
-        <v>91589</v>
+        <v>92311</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1108</v>
+        <v>3298</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2405,10 +2405,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>473464</v>
+        <v>473408</v>
       </c>
       <c r="R19" t="n">
-        <v>6991416</v>
+        <v>6991459</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i stambasen av en stående döende grov gran.</t>
+          <t>Rikligt med fruktkroppar i stambasen av en hyfsat grov stående död gran med full längd.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2498,7 +2498,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129762639</v>
+        <v>129762650</v>
       </c>
       <c r="B20" t="n">
         <v>91589</v>
@@ -2540,10 +2540,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>473289</v>
+        <v>473464</v>
       </c>
       <c r="R20" t="n">
-        <v>6991144</v>
+        <v>6991416</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2580,7 +2580,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>I två stående döda granar.</t>
+          <t>Flera fruktkroppar i stambasen av en stående döende grov gran.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2595,7 +2595,7 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
@@ -2633,7 +2633,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129762642</v>
+        <v>129762639</v>
       </c>
       <c r="B21" t="n">
         <v>91589</v>
@@ -2663,7 +2663,11 @@
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2671,10 +2675,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>473243</v>
+        <v>473289</v>
       </c>
       <c r="R21" t="n">
-        <v>6991220</v>
+        <v>6991144</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2711,7 +2715,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>I stambasen av en döende gran.</t>
+          <t>I två stående döda granar.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2741,12 +2745,12 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -2764,7 +2768,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129762643</v>
+        <v>129762642</v>
       </c>
       <c r="B22" t="n">
         <v>91589</v>
@@ -2794,11 +2798,7 @@
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2806,10 +2806,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>473253</v>
+        <v>473243</v>
       </c>
       <c r="R22" t="n">
-        <v>6991258</v>
+        <v>6991220</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2846,7 +2846,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en stående döende gran.</t>
+          <t>I stambasen av en döende gran.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2899,32 +2899,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129762562</v>
+        <v>129762643</v>
       </c>
       <c r="B23" t="n">
-        <v>92311</v>
+        <v>91589</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>3298</v>
+        <v>1108</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2941,10 +2941,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>473408</v>
+        <v>473253</v>
       </c>
       <c r="R23" t="n">
-        <v>6991459</v>
+        <v>6991258</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2981,7 +2981,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Rikligt med fruktkroppar i stambasen av en hyfsat grov stående död gran med full längd.</t>
+          <t>Flera fruktkroppar i en stående döende gran.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
@@ -3011,12 +3011,12 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3300,52 +3300,65 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129762641</v>
+        <v>129762632</v>
       </c>
       <c r="B26" t="n">
-        <v>91589</v>
+        <v>98774</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1108</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>473229</v>
+        <v>473644</v>
       </c>
       <c r="R26" t="n">
-        <v>6991116</v>
+        <v>6991272</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3372,17 +3385,17 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Gott om fruktkroppar i en stående död gran med full längd.</t>
+          <t>Minst 54 plantor inom ca 2 m2 yta strax norr om ett dike.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3398,26 +3411,6 @@
       <c r="AH26" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3435,10 +3428,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129762649</v>
+        <v>129762662</v>
       </c>
       <c r="B27" t="n">
-        <v>91589</v>
+        <v>79081</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3446,30 +3439,26 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3477,10 +3466,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>473475</v>
+        <v>473631</v>
       </c>
       <c r="R27" t="n">
-        <v>6991471</v>
+        <v>6991321</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3507,17 +3496,17 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i stambasen av en stående död gran (24 cm BHD) med full längd. På fyndplatsen finns stående död ved i en volym som indikerar minst högt livsmiljövärde för tretåig hackspett.</t>
+          <t>På gran i granskog.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3547,12 +3536,12 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3570,10 +3559,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129762662</v>
+        <v>129762641</v>
       </c>
       <c r="B28" t="n">
-        <v>79081</v>
+        <v>91589</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3581,26 +3570,30 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3608,10 +3601,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>473631</v>
+        <v>473229</v>
       </c>
       <c r="R28" t="n">
-        <v>6991321</v>
+        <v>6991116</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3638,17 +3631,17 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>På gran i granskog.</t>
+          <t>Gott om fruktkroppar i en stående död gran med full längd.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3678,12 +3671,12 @@
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3701,65 +3694,52 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129762632</v>
+        <v>129762649</v>
       </c>
       <c r="B29" t="n">
-        <v>98774</v>
+        <v>91589</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>1108</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr"/>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>473644</v>
+        <v>473475</v>
       </c>
       <c r="R29" t="n">
-        <v>6991272</v>
+        <v>6991471</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3786,17 +3766,17 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Minst 54 plantor inom ca 2 m2 yta strax norr om ett dike.</t>
+          <t>Flera fruktkroppar i stambasen av en stående död gran (24 cm BHD) med full längd. På fyndplatsen finns stående död ved i en volym som indikerar minst högt livsmiljövärde för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3812,6 +3792,26 @@
       <c r="AH29" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -3964,10 +3964,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129762663</v>
+        <v>129762640</v>
       </c>
       <c r="B31" t="n">
-        <v>79081</v>
+        <v>91589</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3975,26 +3975,30 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -4002,10 +4006,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>473588</v>
+        <v>473215</v>
       </c>
       <c r="R31" t="n">
-        <v>6991409</v>
+        <v>6991103</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4032,17 +4036,17 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>I en smal stående död gran.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4057,7 +4061,7 @@
       </c>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ31" t="inlineStr">
@@ -4072,12 +4076,12 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4095,10 +4099,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129762640</v>
+        <v>129762663</v>
       </c>
       <c r="B32" t="n">
-        <v>91589</v>
+        <v>79081</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4106,30 +4110,26 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4137,10 +4137,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>473215</v>
+        <v>473588</v>
       </c>
       <c r="R32" t="n">
-        <v>6991103</v>
+        <v>6991409</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4167,17 +4167,17 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>I en smal stående död gran.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4192,7 +4192,7 @@
       </c>
       <c r="AH32" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ32" t="inlineStr">
@@ -4207,12 +4207,12 @@
       </c>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4361,65 +4361,52 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129762630</v>
+        <v>129762651</v>
       </c>
       <c r="B34" t="n">
-        <v>98774</v>
+        <v>91589</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>1108</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr"/>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>473588</v>
+        <v>473497</v>
       </c>
       <c r="R34" t="n">
-        <v>6991340</v>
+        <v>6991392</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4456,7 +4443,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Minst 6 plantor och 1 vinterståndare inom ca 0,5 m2 yta precis intill korallrot i gammal barrblandskog.</t>
+          <t>Flera fruktkroppar i en levande gran.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4472,6 +4459,26 @@
       <c r="AH34" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM34" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4489,41 +4496,42 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129762651</v>
+        <v>129762664</v>
       </c>
       <c r="B35" t="n">
-        <v>91589</v>
+        <v>98691</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1108</v>
+        <v>219790</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr">
         <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4531,10 +4539,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>473497</v>
+        <v>473659</v>
       </c>
       <c r="R35" t="n">
-        <v>6991392</v>
+        <v>6991313</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4561,17 +4569,17 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en levande gran.</t>
+          <t>Minst 1 vinterståndare.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4587,26 +4595,6 @@
       <c r="AH35" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4624,53 +4612,65 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129762664</v>
+        <v>129762630</v>
       </c>
       <c r="B36" t="n">
-        <v>98691</v>
+        <v>98774</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>473659</v>
+        <v>473588</v>
       </c>
       <c r="R36" t="n">
-        <v>6991313</v>
+        <v>6991340</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4697,17 +4697,17 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Minst 1 vinterståndare.</t>
+          <t>Minst 6 plantor och 1 vinterståndare inom ca 0,5 m2 yta precis intill korallrot i gammal barrblandskog.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4740,10 +4740,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129762644</v>
+        <v>129762593</v>
       </c>
       <c r="B37" t="n">
-        <v>91589</v>
+        <v>57736</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4751,41 +4751,46 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>473430</v>
+        <v>473284</v>
       </c>
       <c r="R37" t="n">
-        <v>6991442</v>
+        <v>6991191</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4822,7 +4827,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>I en granhögstubbe.</t>
+          <t>Ringhack, äldre, på stambasen av en gran i granskog.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4831,13 +4836,12 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ37" t="inlineStr">
@@ -4852,12 +4856,12 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -4875,10 +4879,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129762593</v>
+        <v>129762644</v>
       </c>
       <c r="B38" t="n">
-        <v>57736</v>
+        <v>91589</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4886,46 +4890,41 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>473284</v>
+        <v>473430</v>
       </c>
       <c r="R38" t="n">
-        <v>6991191</v>
+        <v>6991442</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4962,7 +4961,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en gran i granskog.</t>
+          <t>I en granhögstubbe.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4971,12 +4970,13 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ38" t="inlineStr">
@@ -4991,12 +4991,12 @@
       </c>
       <c r="AM38" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5149,10 +5149,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129762603</v>
+        <v>129762655</v>
       </c>
       <c r="B40" t="n">
-        <v>57733</v>
+        <v>91613</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5160,46 +5160,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>473521</v>
+        <v>473666</v>
       </c>
       <c r="R40" t="n">
-        <v>6991419</v>
+        <v>6991307</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5236,7 +5227,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Rejäla hackspår i stambasen av en stående död gran med full längd.</t>
+          <t>Flera fruktkroppar i en levande gran.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5245,12 +5236,33 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM40" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5268,10 +5280,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129762655</v>
+        <v>129762603</v>
       </c>
       <c r="B41" t="n">
-        <v>91613</v>
+        <v>57733</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5279,37 +5291,46 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr"/>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>473666</v>
+        <v>473521</v>
       </c>
       <c r="R41" t="n">
-        <v>6991307</v>
+        <v>6991419</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5346,7 +5367,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en levande gran.</t>
+          <t>Rejäla hackspår i stambasen av en stående död gran med full längd.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5355,33 +5376,12 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5666,52 +5666,65 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129762648</v>
+        <v>129762631</v>
       </c>
       <c r="B44" t="n">
-        <v>91589</v>
+        <v>98774</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1108</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr"/>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr"/>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>473481</v>
+        <v>473609</v>
       </c>
       <c r="R44" t="n">
-        <v>6991527</v>
+        <v>6991306</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5748,7 +5761,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en stående döende gran med full längd.</t>
+          <t>Minst 8 plantor och 2 vinterståndare inom ca 0,5 m2 yta i barrblandskog. Troligen finns fler plantor på fyndplatsen.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5763,27 +5776,7 @@
       </c>
       <c r="AH44" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ44" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -5932,65 +5925,52 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129762631</v>
+        <v>129762648</v>
       </c>
       <c r="B46" t="n">
-        <v>98774</v>
+        <v>91589</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>1108</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr"/>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>473609</v>
+        <v>473481</v>
       </c>
       <c r="R46" t="n">
-        <v>6991306</v>
+        <v>6991527</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6027,7 +6007,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Minst 8 plantor och 2 vinterståndare inom ca 0,5 m2 yta i barrblandskog. Troligen finns fler plantor på fyndplatsen.</t>
+          <t>Flera fruktkroppar i en stående döende gran med full längd.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6042,7 +6022,27 @@
       </c>
       <c r="AH46" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM46" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6060,10 +6060,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129762595</v>
+        <v>129762658</v>
       </c>
       <c r="B47" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6071,46 +6071,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>473369</v>
+        <v>473495</v>
       </c>
       <c r="R47" t="n">
-        <v>6991519</v>
+        <v>6991469</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6147,7 +6138,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en gran vid hyggeskanten.</t>
+          <t>På flera både döda och levande granar.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6156,6 +6147,7 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -6176,12 +6168,12 @@
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6199,10 +6191,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129762646</v>
+        <v>129762595</v>
       </c>
       <c r="B48" t="n">
-        <v>91589</v>
+        <v>57736</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6210,41 +6202,46 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>473393</v>
+        <v>473369</v>
       </c>
       <c r="R48" t="n">
-        <v>6991465</v>
+        <v>6991519</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6281,7 +6278,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>I en stående död gran.</t>
+          <t>Ringhack (savhack), färska, på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6290,13 +6287,12 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ48" t="inlineStr">
@@ -6311,12 +6307,12 @@
       </c>
       <c r="AM48" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6334,10 +6330,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129762658</v>
+        <v>129762646</v>
       </c>
       <c r="B49" t="n">
-        <v>79081</v>
+        <v>91589</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6345,26 +6341,30 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -6372,10 +6372,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>473495</v>
+        <v>473393</v>
       </c>
       <c r="R49" t="n">
-        <v>6991469</v>
+        <v>6991465</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6412,7 +6412,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>På flera både döda och levande granar.</t>
+          <t>I en stående död gran.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6427,7 +6427,7 @@
       </c>
       <c r="AH49" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ49" t="inlineStr">
@@ -6442,12 +6442,12 @@
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6588,42 +6588,50 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129762594</v>
+        <v>129762627</v>
       </c>
       <c r="B51" t="n">
-        <v>57736</v>
+        <v>98774</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N51" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -6635,10 +6643,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>473355</v>
+        <v>473137</v>
       </c>
       <c r="R51" t="n">
-        <v>6991512</v>
+        <v>6991201</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6675,7 +6683,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran vid hyggeskanten.</t>
+          <t>Minst 18 plantor och 1 vinterståndare inom ca 0,5 m2 yta söder om ett dike i barrblandskog.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6684,32 +6692,13 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ51" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK51" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO51" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -6858,10 +6847,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129762601</v>
+        <v>129762594</v>
       </c>
       <c r="B53" t="n">
-        <v>57896</v>
+        <v>57736</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6869,33 +6858,29 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -6909,10 +6894,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>473628</v>
+        <v>473355</v>
       </c>
       <c r="R53" t="n">
-        <v>6991288</v>
+        <v>6991512</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6949,7 +6934,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Minst 2 individer med lockläte i flerskiktad barrblandskog med inslag av klena björkar och björkhögstubbar.</t>
+          <t>Ringhack, färska, på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6963,7 +6948,27 @@
       </c>
       <c r="AH53" t="inlineStr">
         <is>
-          <t>Barrträd</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM53" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -6981,50 +6986,46 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129762627</v>
+        <v>129762601</v>
       </c>
       <c r="B54" t="n">
-        <v>98774</v>
+        <v>57896</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N54" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -7036,10 +7037,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>473137</v>
+        <v>473628</v>
       </c>
       <c r="R54" t="n">
-        <v>6991201</v>
+        <v>6991288</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7076,7 +7077,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Minst 18 plantor och 1 vinterståndare inom ca 0,5 m2 yta söder om ett dike i barrblandskog.</t>
+          <t>Minst 2 individer med lockläte i flerskiktad barrblandskog med inslag av klena björkar och björkhögstubbar.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7085,13 +7086,12 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Barrträd</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>

--- a/artfynd/A 48959-2025 artfynd.xlsx
+++ b/artfynd/A 48959-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129733694</v>
+        <v>129733690</v>
       </c>
       <c r="B2" t="n">
         <v>91589</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>473330</v>
+        <v>473509</v>
       </c>
       <c r="R2" t="n">
-        <v>6991067</v>
+        <v>6991413</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,7 +772,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129733690</v>
+        <v>129733694</v>
       </c>
       <c r="B3" t="n">
         <v>91589</v>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>473509</v>
+        <v>473330</v>
       </c>
       <c r="R3" t="n">
-        <v>6991413</v>
+        <v>6991067</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129733693</v>
+        <v>129733680</v>
       </c>
       <c r="B4" t="n">
-        <v>91589</v>
+        <v>91593</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>473343</v>
+        <v>473498</v>
       </c>
       <c r="R4" t="n">
-        <v>6991073</v>
+        <v>6991415</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129733680</v>
+        <v>129733693</v>
       </c>
       <c r="B5" t="n">
-        <v>91593</v>
+        <v>91589</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>473498</v>
+        <v>473343</v>
       </c>
       <c r="R5" t="n">
-        <v>6991415</v>
+        <v>6991073</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1375,10 +1375,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129733696</v>
+        <v>129733689</v>
       </c>
       <c r="B9" t="n">
-        <v>91613</v>
+        <v>91589</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1386,19 +1386,23 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1406,10 +1410,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>473472</v>
+        <v>473505</v>
       </c>
       <c r="R9" t="n">
-        <v>6991545</v>
+        <v>6991422</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1468,10 +1472,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129733685</v>
+        <v>129733696</v>
       </c>
       <c r="B10" t="n">
-        <v>57733</v>
+        <v>91613</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1479,42 +1483,30 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>473633</v>
+        <v>473472</v>
       </c>
       <c r="R10" t="n">
-        <v>6991388</v>
+        <v>6991545</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1547,11 +1539,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-11-05</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Färska hackspår.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1578,10 +1565,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129733689</v>
+        <v>129733685</v>
       </c>
       <c r="B11" t="n">
-        <v>91589</v>
+        <v>57733</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1589,34 +1576,42 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1108</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>473505</v>
+        <v>473633</v>
       </c>
       <c r="R11" t="n">
-        <v>6991422</v>
+        <v>6991388</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1649,6 +1644,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Färska hackspår.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2363,32 +2363,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129762562</v>
+        <v>129762650</v>
       </c>
       <c r="B19" t="n">
-        <v>92311</v>
+        <v>91589</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>3298</v>
+        <v>1108</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2405,10 +2405,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>473408</v>
+        <v>473464</v>
       </c>
       <c r="R19" t="n">
-        <v>6991459</v>
+        <v>6991416</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Rikligt med fruktkroppar i stambasen av en hyfsat grov stående död gran med full längd.</t>
+          <t>Flera fruktkroppar i stambasen av en stående döende grov gran.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2498,7 +2498,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129762650</v>
+        <v>129762639</v>
       </c>
       <c r="B20" t="n">
         <v>91589</v>
@@ -2540,10 +2540,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>473464</v>
+        <v>473289</v>
       </c>
       <c r="R20" t="n">
-        <v>6991416</v>
+        <v>6991144</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2580,7 +2580,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i stambasen av en stående döende grov gran.</t>
+          <t>I två stående döda granar.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2595,7 +2595,7 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
@@ -2633,7 +2633,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129762639</v>
+        <v>129762642</v>
       </c>
       <c r="B21" t="n">
         <v>91589</v>
@@ -2663,11 +2663,7 @@
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2675,10 +2671,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>473289</v>
+        <v>473243</v>
       </c>
       <c r="R21" t="n">
-        <v>6991144</v>
+        <v>6991220</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2715,7 +2711,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>I två stående döda granar.</t>
+          <t>I stambasen av en döende gran.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2745,12 +2741,12 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -2768,7 +2764,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129762642</v>
+        <v>129762643</v>
       </c>
       <c r="B22" t="n">
         <v>91589</v>
@@ -2798,7 +2794,11 @@
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2806,10 +2806,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>473243</v>
+        <v>473253</v>
       </c>
       <c r="R22" t="n">
-        <v>6991220</v>
+        <v>6991258</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2846,7 +2846,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>I stambasen av en döende gran.</t>
+          <t>Flera fruktkroppar i en stående döende gran.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2899,32 +2899,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129762643</v>
+        <v>129762562</v>
       </c>
       <c r="B23" t="n">
-        <v>91589</v>
+        <v>92311</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1108</v>
+        <v>3298</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2941,10 +2941,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>473253</v>
+        <v>473408</v>
       </c>
       <c r="R23" t="n">
-        <v>6991258</v>
+        <v>6991459</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2981,7 +2981,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en stående döende gran.</t>
+          <t>Rikligt med fruktkroppar i stambasen av en hyfsat grov stående död gran med full längd.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
@@ -3011,12 +3011,12 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3428,10 +3428,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129762662</v>
+        <v>129762641</v>
       </c>
       <c r="B27" t="n">
-        <v>79081</v>
+        <v>91589</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3439,26 +3439,30 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3466,10 +3470,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>473631</v>
+        <v>473229</v>
       </c>
       <c r="R27" t="n">
-        <v>6991321</v>
+        <v>6991116</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3496,17 +3500,17 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>På gran i granskog.</t>
+          <t>Gott om fruktkroppar i en stående död gran med full längd.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3536,12 +3540,12 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3559,7 +3563,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129762641</v>
+        <v>129762649</v>
       </c>
       <c r="B28" t="n">
         <v>91589</v>
@@ -3601,10 +3605,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>473229</v>
+        <v>473475</v>
       </c>
       <c r="R28" t="n">
-        <v>6991116</v>
+        <v>6991471</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3641,7 +3645,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Gott om fruktkroppar i en stående död gran med full längd.</t>
+          <t>Flera fruktkroppar i stambasen av en stående död gran (24 cm BHD) med full längd. På fyndplatsen finns stående död ved i en volym som indikerar minst högt livsmiljövärde för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3694,10 +3698,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129762649</v>
+        <v>129762662</v>
       </c>
       <c r="B29" t="n">
-        <v>91589</v>
+        <v>79081</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3705,30 +3709,26 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3736,10 +3736,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>473475</v>
+        <v>473631</v>
       </c>
       <c r="R29" t="n">
-        <v>6991471</v>
+        <v>6991321</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3766,17 +3766,17 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i stambasen av en stående död gran (24 cm BHD) med full längd. På fyndplatsen finns stående död ved i en volym som indikerar minst högt livsmiljövärde för tretåig hackspett.</t>
+          <t>På gran i granskog.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3806,12 +3806,12 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4230,10 +4230,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129762660</v>
+        <v>129762651</v>
       </c>
       <c r="B33" t="n">
-        <v>79081</v>
+        <v>91589</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4241,26 +4241,30 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4268,10 +4272,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>473564</v>
+        <v>473497</v>
       </c>
       <c r="R33" t="n">
-        <v>6991395</v>
+        <v>6991392</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4308,7 +4312,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>På bark av tall.</t>
+          <t>Flera fruktkroppar i en levande gran.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4328,22 +4332,22 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Pinus sylvestris</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4361,41 +4365,42 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129762651</v>
+        <v>129762664</v>
       </c>
       <c r="B34" t="n">
-        <v>91589</v>
+        <v>98691</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1108</v>
+        <v>219790</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4403,10 +4408,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>473497</v>
+        <v>473659</v>
       </c>
       <c r="R34" t="n">
-        <v>6991392</v>
+        <v>6991313</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4433,17 +4438,17 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en levande gran.</t>
+          <t>Minst 1 vinterståndare.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4459,26 +4464,6 @@
       <c r="AH34" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4496,53 +4481,65 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129762664</v>
+        <v>129762630</v>
       </c>
       <c r="B35" t="n">
-        <v>98691</v>
+        <v>98774</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>473659</v>
+        <v>473588</v>
       </c>
       <c r="R35" t="n">
-        <v>6991313</v>
+        <v>6991340</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4569,17 +4566,17 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Minst 1 vinterståndare.</t>
+          <t>Minst 6 plantor och 1 vinterståndare inom ca 0,5 m2 yta precis intill korallrot i gammal barrblandskog.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4612,65 +4609,48 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129762630</v>
+        <v>129762660</v>
       </c>
       <c r="B36" t="n">
-        <v>98774</v>
+        <v>79081</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr"/>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>473588</v>
+        <v>473564</v>
       </c>
       <c r="R36" t="n">
-        <v>6991340</v>
+        <v>6991395</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4707,7 +4687,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Minst 6 plantor och 1 vinterståndare inom ca 0,5 m2 yta precis intill korallrot i gammal barrblandskog.</t>
+          <t>På bark av tall.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4723,6 +4703,26 @@
       <c r="AH36" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM36" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4740,10 +4740,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129762593</v>
+        <v>129762644</v>
       </c>
       <c r="B37" t="n">
-        <v>57736</v>
+        <v>91589</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4751,46 +4751,41 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>473284</v>
+        <v>473430</v>
       </c>
       <c r="R37" t="n">
-        <v>6991191</v>
+        <v>6991442</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4827,7 +4822,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en gran i granskog.</t>
+          <t>I en granhögstubbe.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4836,12 +4831,13 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ37" t="inlineStr">
@@ -4856,12 +4852,12 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -4879,10 +4875,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129762644</v>
+        <v>129762593</v>
       </c>
       <c r="B38" t="n">
-        <v>91589</v>
+        <v>57736</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4890,41 +4886,46 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>473430</v>
+        <v>473284</v>
       </c>
       <c r="R38" t="n">
-        <v>6991442</v>
+        <v>6991191</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4961,7 +4962,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>I en granhögstubbe.</t>
+          <t>Ringhack, äldre, på stambasen av en gran i granskog.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4970,13 +4971,12 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ38" t="inlineStr">
@@ -4991,12 +4991,12 @@
       </c>
       <c r="AM38" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5666,65 +5666,48 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129762631</v>
+        <v>129762659</v>
       </c>
       <c r="B44" t="n">
-        <v>98774</v>
+        <v>79081</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L44" t="inlineStr"/>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>473609</v>
+        <v>473494</v>
       </c>
       <c r="R44" t="n">
-        <v>6991306</v>
+        <v>6991425</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5761,7 +5744,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Minst 8 plantor och 2 vinterståndare inom ca 0,5 m2 yta i barrblandskog. Troligen finns fler plantor på fyndplatsen.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5777,6 +5760,26 @@
       <c r="AH44" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM44" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -5794,10 +5797,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129762659</v>
+        <v>129762648</v>
       </c>
       <c r="B45" t="n">
-        <v>79081</v>
+        <v>91589</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5805,26 +5808,30 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5832,10 +5839,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>473494</v>
+        <v>473481</v>
       </c>
       <c r="R45" t="n">
-        <v>6991425</v>
+        <v>6991527</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5872,7 +5879,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Flera fruktkroppar i en stående döende gran med full längd.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5887,7 +5894,7 @@
       </c>
       <c r="AH45" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ45" t="inlineStr">
@@ -5902,12 +5909,12 @@
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -5925,52 +5932,65 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129762648</v>
+        <v>129762631</v>
       </c>
       <c r="B46" t="n">
-        <v>91589</v>
+        <v>98774</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1108</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr"/>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr"/>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>473481</v>
+        <v>473609</v>
       </c>
       <c r="R46" t="n">
-        <v>6991527</v>
+        <v>6991306</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6007,7 +6027,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en stående döende gran med full längd.</t>
+          <t>Minst 8 plantor och 2 vinterståndare inom ca 0,5 m2 yta i barrblandskog. Troligen finns fler plantor på fyndplatsen.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6022,27 +6042,7 @@
       </c>
       <c r="AH46" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ46" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK46" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6060,10 +6060,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129762658</v>
+        <v>129762646</v>
       </c>
       <c r="B47" t="n">
-        <v>79081</v>
+        <v>91589</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6071,26 +6071,30 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -6098,10 +6102,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>473495</v>
+        <v>473393</v>
       </c>
       <c r="R47" t="n">
-        <v>6991469</v>
+        <v>6991465</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6138,7 +6142,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>På flera både döda och levande granar.</t>
+          <t>I en stående död gran.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6153,7 +6157,7 @@
       </c>
       <c r="AH47" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ47" t="inlineStr">
@@ -6168,12 +6172,12 @@
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6191,10 +6195,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129762595</v>
+        <v>129762658</v>
       </c>
       <c r="B48" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6202,46 +6206,37 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>473369</v>
+        <v>473495</v>
       </c>
       <c r="R48" t="n">
-        <v>6991519</v>
+        <v>6991469</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6278,7 +6273,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en gran vid hyggeskanten.</t>
+          <t>På flera både döda och levande granar.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6287,6 +6282,7 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -6307,12 +6303,12 @@
       </c>
       <c r="AM48" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6330,10 +6326,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129762646</v>
+        <v>129762595</v>
       </c>
       <c r="B49" t="n">
-        <v>91589</v>
+        <v>57736</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6341,41 +6337,46 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>473393</v>
+        <v>473369</v>
       </c>
       <c r="R49" t="n">
-        <v>6991465</v>
+        <v>6991519</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6412,7 +6413,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>I en stående död gran.</t>
+          <t>Ringhack (savhack), färska, på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6421,13 +6422,12 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ49" t="inlineStr">
@@ -6442,12 +6442,12 @@
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6716,10 +6716,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129762656</v>
+        <v>129762594</v>
       </c>
       <c r="B52" t="n">
-        <v>91613</v>
+        <v>57736</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6727,37 +6727,46 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>473615</v>
+        <v>473355</v>
       </c>
       <c r="R52" t="n">
-        <v>6991356</v>
+        <v>6991512</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6784,17 +6793,17 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Rikligt med fruktkroppar i en stående döende gran med full längd.</t>
+          <t>Ringhack, färska, på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6803,7 +6812,6 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -6847,10 +6855,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129762594</v>
+        <v>129762601</v>
       </c>
       <c r="B53" t="n">
-        <v>57736</v>
+        <v>57896</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6858,29 +6866,33 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -6894,10 +6906,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>473355</v>
+        <v>473628</v>
       </c>
       <c r="R53" t="n">
-        <v>6991512</v>
+        <v>6991288</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6934,7 +6946,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran vid hyggeskanten.</t>
+          <t>Minst 2 individer med lockläte i flerskiktad barrblandskog med inslag av klena björkar och björkhögstubbar.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6948,27 +6960,7 @@
       </c>
       <c r="AH53" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ53" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK53" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO53" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Barrträd</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -6986,10 +6978,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129762601</v>
+        <v>129762656</v>
       </c>
       <c r="B54" t="n">
-        <v>57896</v>
+        <v>91613</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6997,50 +6989,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>473628</v>
+        <v>473615</v>
       </c>
       <c r="R54" t="n">
-        <v>6991288</v>
+        <v>6991356</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7067,17 +7046,17 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Minst 2 individer med lockläte i flerskiktad barrblandskog med inslag av klena björkar och björkhögstubbar.</t>
+          <t>Rikligt med fruktkroppar i en stående döende gran med full längd.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7086,12 +7065,33 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
-          <t>Barrträd</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ54" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK54" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM54" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO54" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -7109,10 +7109,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129762653</v>
+        <v>129762556</v>
       </c>
       <c r="B55" t="n">
-        <v>91589</v>
+        <v>91593</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7120,21 +7120,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -7151,10 +7151,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>473644</v>
+        <v>473292</v>
       </c>
       <c r="R55" t="n">
-        <v>6991369</v>
+        <v>6991191</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7181,17 +7181,17 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en stående död gran med full längd.</t>
+          <t>Växer i en död granstam av en rotvälta.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7221,12 +7221,12 @@
       </c>
       <c r="AM55" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -7244,10 +7244,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129762556</v>
+        <v>129762600</v>
       </c>
       <c r="B56" t="n">
-        <v>91593</v>
+        <v>57896</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7255,41 +7255,50 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>473292</v>
+        <v>473307</v>
       </c>
       <c r="R56" t="n">
-        <v>6991191</v>
+        <v>6991179</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7326,7 +7335,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Växer i en död granstam av en rotvälta.</t>
+          <t>Minst 1 talltita med lockläte. Ev. fans fler individer på fyndplatsen där det är flerskiktad barrskog.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7335,33 +7344,12 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ56" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK56" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM56" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO56" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -7379,10 +7367,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129762600</v>
+        <v>129762653</v>
       </c>
       <c r="B57" t="n">
-        <v>57896</v>
+        <v>91589</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7390,50 +7378,41 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>103021</v>
+        <v>1108</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>473307</v>
+        <v>473644</v>
       </c>
       <c r="R57" t="n">
-        <v>6991179</v>
+        <v>6991369</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7460,17 +7439,17 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Minst 1 talltita med lockläte. Ev. fans fler individer på fyndplatsen där det är flerskiktad barrskog.</t>
+          <t>Flera fruktkroppar i en stående död gran med full längd.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7479,12 +7458,33 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ57" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK57" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM57" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO57" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -7641,10 +7641,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129762661</v>
+        <v>129762557</v>
       </c>
       <c r="B59" t="n">
-        <v>79081</v>
+        <v>91593</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7652,26 +7652,30 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -7679,10 +7683,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>473612</v>
+        <v>473560</v>
       </c>
       <c r="R59" t="n">
-        <v>6991344</v>
+        <v>6991376</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7709,17 +7713,17 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Fruktkroppar längs flera meter i en granlåga.</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7734,7 +7738,7 @@
       </c>
       <c r="AH59" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ59" t="inlineStr">
@@ -7749,12 +7753,12 @@
       </c>
       <c r="AM59" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO59" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -7772,10 +7776,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129762557</v>
+        <v>129762661</v>
       </c>
       <c r="B60" t="n">
-        <v>91593</v>
+        <v>79081</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7783,30 +7787,26 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K60" t="inlineStr"/>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -7814,10 +7814,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>473560</v>
+        <v>473612</v>
       </c>
       <c r="R60" t="n">
-        <v>6991376</v>
+        <v>6991344</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7844,17 +7844,17 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Fruktkroppar längs flera meter i en granlåga.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7869,7 +7869,7 @@
       </c>
       <c r="AH60" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ60" t="inlineStr">
@@ -7884,12 +7884,12 @@
       </c>
       <c r="AM60" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO60" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>

--- a/artfynd/A 48959-2025 artfynd.xlsx
+++ b/artfynd/A 48959-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129733690</v>
       </c>
       <c r="B2" t="n">
-        <v>91589</v>
+        <v>91593</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129733694</v>
       </c>
       <c r="B3" t="n">
-        <v>91589</v>
+        <v>91593</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129733680</v>
       </c>
       <c r="B4" t="n">
-        <v>91593</v>
+        <v>91597</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129733693</v>
       </c>
       <c r="B5" t="n">
-        <v>91589</v>
+        <v>91593</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1184,7 +1184,7 @@
         <v>129733695</v>
       </c>
       <c r="B7" t="n">
-        <v>91589</v>
+        <v>91593</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1281,7 +1281,7 @@
         <v>129733692</v>
       </c>
       <c r="B8" t="n">
-        <v>91589</v>
+        <v>91593</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1378,7 +1378,7 @@
         <v>129733689</v>
       </c>
       <c r="B9" t="n">
-        <v>91589</v>
+        <v>91593</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1475,7 +1475,7 @@
         <v>129733696</v>
       </c>
       <c r="B10" t="n">
-        <v>91613</v>
+        <v>91617</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1565,42 +1565,42 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129733685</v>
+        <v>129733686</v>
       </c>
       <c r="B11" t="n">
-        <v>57733</v>
+        <v>98778</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1608,10 +1608,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>473633</v>
+        <v>473562</v>
       </c>
       <c r="R11" t="n">
-        <v>6991388</v>
+        <v>6991360</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1646,17 +1646,13 @@
           <t>2025-11-05</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Färska hackspår.</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1675,42 +1671,42 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129733686</v>
+        <v>129733685</v>
       </c>
       <c r="B12" t="n">
-        <v>98774</v>
+        <v>57733</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1718,10 +1714,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>473562</v>
+        <v>473633</v>
       </c>
       <c r="R12" t="n">
-        <v>6991360</v>
+        <v>6991388</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1756,13 +1752,17 @@
           <t>2025-11-05</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Färska hackspår.</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1784,7 +1784,7 @@
         <v>129733681</v>
       </c>
       <c r="B13" t="n">
-        <v>91593</v>
+        <v>91597</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1881,7 +1881,7 @@
         <v>129733687</v>
       </c>
       <c r="B14" t="n">
-        <v>91589</v>
+        <v>91593</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1978,7 +1978,7 @@
         <v>129733691</v>
       </c>
       <c r="B15" t="n">
-        <v>91589</v>
+        <v>91593</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         <v>129733683</v>
       </c>
       <c r="B16" t="n">
-        <v>92311</v>
+        <v>92315</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2172,7 +2172,7 @@
         <v>129733682</v>
       </c>
       <c r="B17" t="n">
-        <v>92311</v>
+        <v>92315</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2269,7 +2269,7 @@
         <v>129733688</v>
       </c>
       <c r="B18" t="n">
-        <v>91589</v>
+        <v>91593</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2366,7 +2366,7 @@
         <v>129762650</v>
       </c>
       <c r="B19" t="n">
-        <v>91589</v>
+        <v>91593</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129762639</v>
+        <v>129762643</v>
       </c>
       <c r="B20" t="n">
-        <v>91589</v>
+        <v>91593</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2540,10 +2540,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>473289</v>
+        <v>473253</v>
       </c>
       <c r="R20" t="n">
-        <v>6991144</v>
+        <v>6991258</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2580,7 +2580,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>I två stående döda granar.</t>
+          <t>Flera fruktkroppar i en stående döende gran.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2610,12 +2610,12 @@
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2636,7 +2636,7 @@
         <v>129762642</v>
       </c>
       <c r="B21" t="n">
-        <v>91589</v>
+        <v>91593</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2764,10 +2764,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129762643</v>
+        <v>129762639</v>
       </c>
       <c r="B22" t="n">
-        <v>91589</v>
+        <v>91593</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2806,10 +2806,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>473253</v>
+        <v>473289</v>
       </c>
       <c r="R22" t="n">
-        <v>6991258</v>
+        <v>6991144</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2846,7 +2846,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en stående döende gran.</t>
+          <t>I två stående döda granar.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -2902,7 +2902,7 @@
         <v>129762562</v>
       </c>
       <c r="B23" t="n">
-        <v>92311</v>
+        <v>92315</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3034,10 +3034,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129762654</v>
+        <v>129762652</v>
       </c>
       <c r="B24" t="n">
-        <v>91589</v>
+        <v>91593</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3064,7 +3064,11 @@
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3072,10 +3076,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>473668</v>
+        <v>473621</v>
       </c>
       <c r="R24" t="n">
-        <v>6991289</v>
+        <v>6991345</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3102,17 +3106,17 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en granstubbe.</t>
+          <t>Flera fruktkroppar i en stående död gran med full längd och 35 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3142,12 +3146,12 @@
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>Stubbe</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Stump # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3165,10 +3169,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129762652</v>
+        <v>129762654</v>
       </c>
       <c r="B25" t="n">
-        <v>91589</v>
+        <v>91593</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3195,11 +3199,7 @@
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3207,10 +3207,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>473621</v>
+        <v>473668</v>
       </c>
       <c r="R25" t="n">
-        <v>6991345</v>
+        <v>6991289</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3237,17 +3237,17 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en stående död gran med full längd och 35 cm i brösthöjdsdiameter.</t>
+          <t>Flera fruktkroppar i en granstubbe.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3277,12 +3277,12 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Stubbe</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3303,7 +3303,7 @@
         <v>129762632</v>
       </c>
       <c r="B26" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3428,10 +3428,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129762641</v>
+        <v>129762649</v>
       </c>
       <c r="B27" t="n">
-        <v>91589</v>
+        <v>91593</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3470,10 +3470,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>473229</v>
+        <v>473475</v>
       </c>
       <c r="R27" t="n">
-        <v>6991116</v>
+        <v>6991471</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3510,7 +3510,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Gott om fruktkroppar i en stående död gran med full längd.</t>
+          <t>Flera fruktkroppar i stambasen av en stående död gran (24 cm BHD) med full längd. På fyndplatsen finns stående död ved i en volym som indikerar minst högt livsmiljövärde för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3563,10 +3563,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129762649</v>
+        <v>129762641</v>
       </c>
       <c r="B28" t="n">
-        <v>91589</v>
+        <v>91593</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3605,10 +3605,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>473475</v>
+        <v>473229</v>
       </c>
       <c r="R28" t="n">
-        <v>6991471</v>
+        <v>6991116</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3645,7 +3645,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i stambasen av en stående död gran (24 cm BHD) med full längd. På fyndplatsen finns stående död ved i en volym som indikerar minst högt livsmiljövärde för tretåig hackspett.</t>
+          <t>Gott om fruktkroppar i en stående död gran med full längd.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3832,7 +3832,7 @@
         <v>129762647</v>
       </c>
       <c r="B30" t="n">
-        <v>91589</v>
+        <v>91593</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3964,10 +3964,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129762640</v>
+        <v>129762663</v>
       </c>
       <c r="B31" t="n">
-        <v>91589</v>
+        <v>79081</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3975,30 +3975,26 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -4006,10 +4002,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>473215</v>
+        <v>473588</v>
       </c>
       <c r="R31" t="n">
-        <v>6991103</v>
+        <v>6991409</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4036,17 +4032,17 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>I en smal stående död gran.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4061,7 +4057,7 @@
       </c>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ31" t="inlineStr">
@@ -4076,12 +4072,12 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4099,10 +4095,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129762663</v>
+        <v>129762640</v>
       </c>
       <c r="B32" t="n">
-        <v>79081</v>
+        <v>91593</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4110,26 +4106,30 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4137,10 +4137,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>473588</v>
+        <v>473215</v>
       </c>
       <c r="R32" t="n">
-        <v>6991409</v>
+        <v>6991103</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4167,17 +4167,17 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>I en smal stående död gran.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4192,7 +4192,7 @@
       </c>
       <c r="AH32" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ32" t="inlineStr">
@@ -4207,12 +4207,12 @@
       </c>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4230,52 +4230,65 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129762651</v>
+        <v>129762630</v>
       </c>
       <c r="B33" t="n">
-        <v>91589</v>
+        <v>98778</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1108</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr"/>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>473497</v>
+        <v>473588</v>
       </c>
       <c r="R33" t="n">
-        <v>6991392</v>
+        <v>6991340</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4312,7 +4325,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en levande gran.</t>
+          <t>Minst 6 plantor och 1 vinterståndare inom ca 0,5 m2 yta precis intill korallrot i gammal barrblandskog.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4328,26 +4341,6 @@
       <c r="AH33" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4365,42 +4358,41 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129762664</v>
+        <v>129762651</v>
       </c>
       <c r="B34" t="n">
-        <v>98691</v>
+        <v>91593</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>219790</v>
+        <v>1108</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr"/>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4408,10 +4400,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>473659</v>
+        <v>473497</v>
       </c>
       <c r="R34" t="n">
-        <v>6991313</v>
+        <v>6991392</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4438,17 +4430,17 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Minst 1 vinterståndare.</t>
+          <t>Flera fruktkroppar i en levande gran.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4464,6 +4456,26 @@
       <c r="AH34" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM34" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4481,65 +4493,48 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129762630</v>
+        <v>129762660</v>
       </c>
       <c r="B35" t="n">
-        <v>98774</v>
+        <v>79081</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr"/>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>473588</v>
+        <v>473564</v>
       </c>
       <c r="R35" t="n">
-        <v>6991340</v>
+        <v>6991395</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4576,7 +4571,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Minst 6 plantor och 1 vinterståndare inom ca 0,5 m2 yta precis intill korallrot i gammal barrblandskog.</t>
+          <t>På bark av tall.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4592,6 +4587,26 @@
       <c r="AH35" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM35" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4609,37 +4624,42 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129762660</v>
+        <v>129762664</v>
       </c>
       <c r="B36" t="n">
-        <v>79081</v>
+        <v>98695</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4647,10 +4667,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>473564</v>
+        <v>473659</v>
       </c>
       <c r="R36" t="n">
-        <v>6991395</v>
+        <v>6991313</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4677,17 +4697,17 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>På bark av tall.</t>
+          <t>Minst 1 vinterståndare.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4703,26 +4723,6 @@
       <c r="AH36" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4743,7 +4743,7 @@
         <v>129762644</v>
       </c>
       <c r="B37" t="n">
-        <v>91589</v>
+        <v>91593</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5017,7 +5017,7 @@
         <v>129762645</v>
       </c>
       <c r="B39" t="n">
-        <v>91589</v>
+        <v>91593</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5149,10 +5149,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129762655</v>
+        <v>129762603</v>
       </c>
       <c r="B40" t="n">
-        <v>91613</v>
+        <v>57733</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5160,37 +5160,46 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr"/>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>473666</v>
+        <v>473521</v>
       </c>
       <c r="R40" t="n">
-        <v>6991307</v>
+        <v>6991419</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5227,7 +5236,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en levande gran.</t>
+          <t>Rejäla hackspår i stambasen av en stående död gran med full längd.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5236,33 +5245,12 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5280,10 +5268,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129762603</v>
+        <v>129762655</v>
       </c>
       <c r="B41" t="n">
-        <v>57733</v>
+        <v>91617</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5291,46 +5279,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>473521</v>
+        <v>473666</v>
       </c>
       <c r="R41" t="n">
-        <v>6991419</v>
+        <v>6991307</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5367,7 +5346,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Rejäla hackspår i stambasen av en stående död gran med full längd.</t>
+          <t>Flera fruktkroppar i en levande gran.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5376,12 +5355,33 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM41" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5541,7 +5541,7 @@
         <v>129762620</v>
       </c>
       <c r="B43" t="n">
-        <v>98678</v>
+        <v>98682</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5666,10 +5666,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129762659</v>
+        <v>129762648</v>
       </c>
       <c r="B44" t="n">
-        <v>79081</v>
+        <v>91593</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5677,26 +5677,30 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5704,10 +5708,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>473494</v>
+        <v>473481</v>
       </c>
       <c r="R44" t="n">
-        <v>6991425</v>
+        <v>6991527</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5744,7 +5748,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Flera fruktkroppar i en stående döende gran med full längd.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5759,7 +5763,7 @@
       </c>
       <c r="AH44" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ44" t="inlineStr">
@@ -5774,12 +5778,12 @@
       </c>
       <c r="AM44" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -5797,10 +5801,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129762648</v>
+        <v>129762659</v>
       </c>
       <c r="B45" t="n">
-        <v>91589</v>
+        <v>79081</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5808,30 +5812,26 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5839,10 +5839,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>473481</v>
+        <v>473494</v>
       </c>
       <c r="R45" t="n">
-        <v>6991527</v>
+        <v>6991425</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5879,7 +5879,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en stående döende gran med full längd.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5894,7 +5894,7 @@
       </c>
       <c r="AH45" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ45" t="inlineStr">
@@ -5909,12 +5909,12 @@
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -5935,7 +5935,7 @@
         <v>129762631</v>
       </c>
       <c r="B46" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6063,7 +6063,7 @@
         <v>129762646</v>
       </c>
       <c r="B47" t="n">
-        <v>91589</v>
+        <v>91593</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6195,10 +6195,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129762658</v>
+        <v>129762595</v>
       </c>
       <c r="B48" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6206,37 +6206,46 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>473495</v>
+        <v>473369</v>
       </c>
       <c r="R48" t="n">
-        <v>6991469</v>
+        <v>6991519</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6273,7 +6282,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>På flera både döda och levande granar.</t>
+          <t>Ringhack (savhack), färska, på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6282,7 +6291,6 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -6303,12 +6311,12 @@
       </c>
       <c r="AM48" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6326,10 +6334,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129762595</v>
+        <v>129762658</v>
       </c>
       <c r="B49" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6337,46 +6345,37 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>473369</v>
+        <v>473495</v>
       </c>
       <c r="R49" t="n">
-        <v>6991519</v>
+        <v>6991469</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6413,7 +6412,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en gran vid hyggeskanten.</t>
+          <t>På flera både döda och levande granar.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6422,6 +6421,7 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -6442,12 +6442,12 @@
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6588,65 +6588,48 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129762627</v>
+        <v>129762656</v>
       </c>
       <c r="B51" t="n">
-        <v>98774</v>
+        <v>91617</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L51" t="inlineStr"/>
-      <c r="N51" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>473137</v>
+        <v>473615</v>
       </c>
       <c r="R51" t="n">
-        <v>6991201</v>
+        <v>6991356</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6673,17 +6656,17 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Minst 18 plantor och 1 vinterståndare inom ca 0,5 m2 yta söder om ett dike i barrblandskog.</t>
+          <t>Rikligt med fruktkroppar i en stående döende gran med full längd.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6698,7 +6681,27 @@
       </c>
       <c r="AH51" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM51" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -6716,10 +6719,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129762594</v>
+        <v>129762601</v>
       </c>
       <c r="B52" t="n">
-        <v>57736</v>
+        <v>57896</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6727,29 +6730,33 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -6763,10 +6770,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>473355</v>
+        <v>473628</v>
       </c>
       <c r="R52" t="n">
-        <v>6991512</v>
+        <v>6991288</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6803,7 +6810,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran vid hyggeskanten.</t>
+          <t>Minst 2 individer med lockläte i flerskiktad barrblandskog med inslag av klena björkar och björkhögstubbar.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6817,27 +6824,7 @@
       </c>
       <c r="AH52" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ52" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK52" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO52" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Barrträd</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -6855,10 +6842,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129762601</v>
+        <v>129762594</v>
       </c>
       <c r="B53" t="n">
-        <v>57896</v>
+        <v>57736</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6866,33 +6853,29 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -6906,10 +6889,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>473628</v>
+        <v>473355</v>
       </c>
       <c r="R53" t="n">
-        <v>6991288</v>
+        <v>6991512</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6946,7 +6929,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Minst 2 individer med lockläte i flerskiktad barrblandskog med inslag av klena björkar och björkhögstubbar.</t>
+          <t>Ringhack, färska, på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6960,7 +6943,27 @@
       </c>
       <c r="AH53" t="inlineStr">
         <is>
-          <t>Barrträd</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM53" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -6978,48 +6981,65 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129762656</v>
+        <v>129762627</v>
       </c>
       <c r="B54" t="n">
-        <v>91613</v>
+        <v>98778</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr"/>
-      <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr"/>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr"/>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>473615</v>
+        <v>473137</v>
       </c>
       <c r="R54" t="n">
-        <v>6991356</v>
+        <v>6991201</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7046,17 +7066,17 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Rikligt med fruktkroppar i en stående döende gran med full längd.</t>
+          <t>Minst 18 plantor och 1 vinterståndare inom ca 0,5 m2 yta söder om ett dike i barrblandskog.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7071,27 +7091,7 @@
       </c>
       <c r="AH54" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ54" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK54" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM54" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO54" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -7109,7 +7109,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129762556</v>
+        <v>129762653</v>
       </c>
       <c r="B55" t="n">
         <v>91593</v>
@@ -7120,21 +7120,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -7151,10 +7151,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>473292</v>
+        <v>473644</v>
       </c>
       <c r="R55" t="n">
-        <v>6991191</v>
+        <v>6991369</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7181,17 +7181,17 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Växer i en död granstam av en rotvälta.</t>
+          <t>Flera fruktkroppar i en stående död gran med full längd.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7221,12 +7221,12 @@
       </c>
       <c r="AM55" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -7244,10 +7244,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129762600</v>
+        <v>129762556</v>
       </c>
       <c r="B56" t="n">
-        <v>57896</v>
+        <v>91597</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7255,50 +7255,41 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>473307</v>
+        <v>473292</v>
       </c>
       <c r="R56" t="n">
-        <v>6991179</v>
+        <v>6991191</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7335,7 +7326,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Minst 1 talltita med lockläte. Ev. fans fler individer på fyndplatsen där det är flerskiktad barrskog.</t>
+          <t>Växer i en död granstam av en rotvälta.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7344,12 +7335,33 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ56" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK56" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM56" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO56" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -7367,10 +7379,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129762653</v>
+        <v>129762600</v>
       </c>
       <c r="B57" t="n">
-        <v>91589</v>
+        <v>57896</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7378,41 +7390,50 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1108</v>
+        <v>103021</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>473644</v>
+        <v>473307</v>
       </c>
       <c r="R57" t="n">
-        <v>6991369</v>
+        <v>6991179</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7439,17 +7460,17 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en stående död gran med full längd.</t>
+          <t>Minst 1 talltita med lockläte. Ev. fans fler individer på fyndplatsen där det är flerskiktad barrskog.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7458,33 +7479,12 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ57" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK57" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM57" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO57" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -7641,10 +7641,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129762557</v>
+        <v>129762661</v>
       </c>
       <c r="B59" t="n">
-        <v>91593</v>
+        <v>79081</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7652,30 +7652,26 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K59" t="inlineStr"/>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -7683,10 +7679,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>473560</v>
+        <v>473612</v>
       </c>
       <c r="R59" t="n">
-        <v>6991376</v>
+        <v>6991344</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7713,17 +7709,17 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Fruktkroppar längs flera meter i en granlåga.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7738,7 +7734,7 @@
       </c>
       <c r="AH59" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ59" t="inlineStr">
@@ -7753,12 +7749,12 @@
       </c>
       <c r="AM59" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO59" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -7776,10 +7772,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129762661</v>
+        <v>129762557</v>
       </c>
       <c r="B60" t="n">
-        <v>79081</v>
+        <v>91597</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7787,26 +7783,30 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -7814,10 +7814,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>473612</v>
+        <v>473560</v>
       </c>
       <c r="R60" t="n">
-        <v>6991344</v>
+        <v>6991376</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7844,17 +7844,17 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Fruktkroppar längs flera meter i en granlåga.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7869,7 +7869,7 @@
       </c>
       <c r="AH60" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ60" t="inlineStr">
@@ -7884,12 +7884,12 @@
       </c>
       <c r="AM60" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO60" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
@@ -7910,7 +7910,7 @@
         <v>129762628</v>
       </c>
       <c r="B61" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -8165,7 +8165,7 @@
         <v>129762629</v>
       </c>
       <c r="B63" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>

--- a/artfynd/A 48959-2025 artfynd.xlsx
+++ b/artfynd/A 48959-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129733690</v>
       </c>
       <c r="B2" t="n">
-        <v>91593</v>
+        <v>91595</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129733694</v>
       </c>
       <c r="B3" t="n">
-        <v>91593</v>
+        <v>91595</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129733680</v>
       </c>
       <c r="B4" t="n">
-        <v>91597</v>
+        <v>91599</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129733693</v>
       </c>
       <c r="B5" t="n">
-        <v>91593</v>
+        <v>91595</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1184,7 +1184,7 @@
         <v>129733695</v>
       </c>
       <c r="B7" t="n">
-        <v>91593</v>
+        <v>91595</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1281,7 +1281,7 @@
         <v>129733692</v>
       </c>
       <c r="B8" t="n">
-        <v>91593</v>
+        <v>91595</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1375,10 +1375,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129733689</v>
+        <v>129733696</v>
       </c>
       <c r="B9" t="n">
-        <v>91593</v>
+        <v>91619</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1386,23 +1386,19 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1410,10 +1406,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>473505</v>
+        <v>473472</v>
       </c>
       <c r="R9" t="n">
-        <v>6991422</v>
+        <v>6991545</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1472,10 +1468,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129733696</v>
+        <v>129733685</v>
       </c>
       <c r="B10" t="n">
-        <v>91617</v>
+        <v>57733</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1483,30 +1479,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>473472</v>
+        <v>473633</v>
       </c>
       <c r="R10" t="n">
-        <v>6991545</v>
+        <v>6991388</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1539,6 +1547,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Färska hackspår.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1568,7 +1581,7 @@
         <v>129733686</v>
       </c>
       <c r="B11" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1671,10 +1684,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129733685</v>
+        <v>129733689</v>
       </c>
       <c r="B12" t="n">
-        <v>57733</v>
+        <v>91595</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1682,42 +1695,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>1108</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>473633</v>
+        <v>473505</v>
       </c>
       <c r="R12" t="n">
-        <v>6991388</v>
+        <v>6991422</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1750,11 +1755,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-11-05</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Färska hackspår.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1784,7 +1784,7 @@
         <v>129733681</v>
       </c>
       <c r="B13" t="n">
-        <v>91597</v>
+        <v>91599</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1881,7 +1881,7 @@
         <v>129733687</v>
       </c>
       <c r="B14" t="n">
-        <v>91593</v>
+        <v>91595</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1978,7 +1978,7 @@
         <v>129733691</v>
       </c>
       <c r="B15" t="n">
-        <v>91593</v>
+        <v>91595</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         <v>129733683</v>
       </c>
       <c r="B16" t="n">
-        <v>92315</v>
+        <v>92317</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2172,7 +2172,7 @@
         <v>129733682</v>
       </c>
       <c r="B17" t="n">
-        <v>92315</v>
+        <v>92317</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2269,7 +2269,7 @@
         <v>129733688</v>
       </c>
       <c r="B18" t="n">
-        <v>91593</v>
+        <v>91595</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2363,32 +2363,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129762650</v>
+        <v>129762562</v>
       </c>
       <c r="B19" t="n">
-        <v>91593</v>
+        <v>92317</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1108</v>
+        <v>3298</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2405,10 +2405,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>473464</v>
+        <v>473408</v>
       </c>
       <c r="R19" t="n">
-        <v>6991416</v>
+        <v>6991459</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i stambasen av en stående döende grov gran.</t>
+          <t>Rikligt med fruktkroppar i stambasen av en hyfsat grov stående död gran med full längd.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2498,10 +2498,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129762643</v>
+        <v>129762650</v>
       </c>
       <c r="B20" t="n">
-        <v>91593</v>
+        <v>91595</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2540,10 +2540,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>473253</v>
+        <v>473464</v>
       </c>
       <c r="R20" t="n">
-        <v>6991258</v>
+        <v>6991416</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2580,7 +2580,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en stående döende gran.</t>
+          <t>Flera fruktkroppar i stambasen av en stående döende grov gran.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2595,7 +2595,7 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
@@ -2610,12 +2610,12 @@
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2633,10 +2633,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129762642</v>
+        <v>129762639</v>
       </c>
       <c r="B21" t="n">
-        <v>91593</v>
+        <v>91595</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2663,7 +2663,11 @@
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2671,10 +2675,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>473243</v>
+        <v>473289</v>
       </c>
       <c r="R21" t="n">
-        <v>6991220</v>
+        <v>6991144</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2711,7 +2715,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>I stambasen av en döende gran.</t>
+          <t>I två stående döda granar.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2741,12 +2745,12 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -2764,10 +2768,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129762639</v>
+        <v>129762642</v>
       </c>
       <c r="B22" t="n">
-        <v>91593</v>
+        <v>91595</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2794,11 +2798,7 @@
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2806,10 +2806,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>473289</v>
+        <v>473243</v>
       </c>
       <c r="R22" t="n">
-        <v>6991144</v>
+        <v>6991220</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2846,7 +2846,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>I två stående döda granar.</t>
+          <t>I stambasen av en döende gran.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -2899,32 +2899,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129762562</v>
+        <v>129762643</v>
       </c>
       <c r="B23" t="n">
-        <v>92315</v>
+        <v>91595</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>3298</v>
+        <v>1108</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2941,10 +2941,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>473408</v>
+        <v>473253</v>
       </c>
       <c r="R23" t="n">
-        <v>6991459</v>
+        <v>6991258</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2981,7 +2981,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Rikligt med fruktkroppar i stambasen av en hyfsat grov stående död gran med full längd.</t>
+          <t>Flera fruktkroppar i en stående döende gran.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
@@ -3011,12 +3011,12 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3034,10 +3034,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129762652</v>
+        <v>129762654</v>
       </c>
       <c r="B24" t="n">
-        <v>91593</v>
+        <v>91595</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3064,11 +3064,7 @@
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3076,10 +3072,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>473621</v>
+        <v>473668</v>
       </c>
       <c r="R24" t="n">
-        <v>6991345</v>
+        <v>6991289</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3106,17 +3102,17 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en stående död gran med full längd och 35 cm i brösthöjdsdiameter.</t>
+          <t>Flera fruktkroppar i en granstubbe.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3146,12 +3142,12 @@
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Stubbe</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3169,10 +3165,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129762654</v>
+        <v>129762652</v>
       </c>
       <c r="B25" t="n">
-        <v>91593</v>
+        <v>91595</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3199,7 +3195,11 @@
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3207,10 +3207,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>473668</v>
+        <v>473621</v>
       </c>
       <c r="R25" t="n">
-        <v>6991289</v>
+        <v>6991345</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3237,17 +3237,17 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en granstubbe.</t>
+          <t>Flera fruktkroppar i en stående död gran med full längd och 35 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3277,12 +3277,12 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>Stubbe</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Stump # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3300,65 +3300,52 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129762632</v>
+        <v>129762641</v>
       </c>
       <c r="B26" t="n">
-        <v>98778</v>
+        <v>91595</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>1108</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr"/>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>473644</v>
+        <v>473229</v>
       </c>
       <c r="R26" t="n">
-        <v>6991272</v>
+        <v>6991116</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3385,17 +3372,17 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Minst 54 plantor inom ca 2 m2 yta strax norr om ett dike.</t>
+          <t>Gott om fruktkroppar i en stående död gran med full längd.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3411,6 +3398,26 @@
       <c r="AH26" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM26" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3428,52 +3435,65 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129762649</v>
+        <v>129762632</v>
       </c>
       <c r="B27" t="n">
-        <v>91593</v>
+        <v>98780</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1108</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>473475</v>
+        <v>473644</v>
       </c>
       <c r="R27" t="n">
-        <v>6991471</v>
+        <v>6991272</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3500,17 +3520,17 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i stambasen av en stående död gran (24 cm BHD) med full längd. På fyndplatsen finns stående död ved i en volym som indikerar minst högt livsmiljövärde för tretåig hackspett.</t>
+          <t>Minst 54 plantor inom ca 2 m2 yta strax norr om ett dike.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3526,26 +3546,6 @@
       <c r="AH27" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3563,10 +3563,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129762641</v>
+        <v>129762649</v>
       </c>
       <c r="B28" t="n">
-        <v>91593</v>
+        <v>91595</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3605,10 +3605,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>473229</v>
+        <v>473475</v>
       </c>
       <c r="R28" t="n">
-        <v>6991116</v>
+        <v>6991471</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3645,7 +3645,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Gott om fruktkroppar i en stående död gran med full längd.</t>
+          <t>Flera fruktkroppar i stambasen av en stående död gran (24 cm BHD) med full längd. På fyndplatsen finns stående död ved i en volym som indikerar minst högt livsmiljövärde för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3832,7 +3832,7 @@
         <v>129762647</v>
       </c>
       <c r="B30" t="n">
-        <v>91593</v>
+        <v>91595</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4098,7 +4098,7 @@
         <v>129762640</v>
       </c>
       <c r="B32" t="n">
-        <v>91593</v>
+        <v>91595</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4230,65 +4230,52 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129762630</v>
+        <v>129762651</v>
       </c>
       <c r="B33" t="n">
-        <v>98778</v>
+        <v>91595</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>1108</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr"/>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>473588</v>
+        <v>473497</v>
       </c>
       <c r="R33" t="n">
-        <v>6991340</v>
+        <v>6991392</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4325,7 +4312,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Minst 6 plantor och 1 vinterståndare inom ca 0,5 m2 yta precis intill korallrot i gammal barrblandskog.</t>
+          <t>Flera fruktkroppar i en levande gran.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4341,6 +4328,26 @@
       <c r="AH33" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM33" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4358,10 +4365,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129762651</v>
+        <v>129762660</v>
       </c>
       <c r="B34" t="n">
-        <v>91593</v>
+        <v>79081</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4369,30 +4376,26 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4400,10 +4403,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>473497</v>
+        <v>473564</v>
       </c>
       <c r="R34" t="n">
-        <v>6991392</v>
+        <v>6991395</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4440,7 +4443,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en levande gran.</t>
+          <t>På bark av tall.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4460,22 +4463,22 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4493,37 +4496,42 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129762660</v>
+        <v>129762664</v>
       </c>
       <c r="B35" t="n">
-        <v>79081</v>
+        <v>98697</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4531,10 +4539,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>473564</v>
+        <v>473659</v>
       </c>
       <c r="R35" t="n">
-        <v>6991395</v>
+        <v>6991313</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4561,17 +4569,17 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>På bark av tall.</t>
+          <t>Minst 1 vinterståndare.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4587,26 +4595,6 @@
       <c r="AH35" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4624,53 +4612,65 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129762664</v>
+        <v>129762630</v>
       </c>
       <c r="B36" t="n">
-        <v>98695</v>
+        <v>98780</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>473659</v>
+        <v>473588</v>
       </c>
       <c r="R36" t="n">
-        <v>6991313</v>
+        <v>6991340</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4697,17 +4697,17 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Minst 1 vinterståndare.</t>
+          <t>Minst 6 plantor och 1 vinterståndare inom ca 0,5 m2 yta precis intill korallrot i gammal barrblandskog.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4743,7 +4743,7 @@
         <v>129762644</v>
       </c>
       <c r="B37" t="n">
-        <v>91593</v>
+        <v>91595</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5017,7 +5017,7 @@
         <v>129762645</v>
       </c>
       <c r="B39" t="n">
-        <v>91593</v>
+        <v>91595</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5149,10 +5149,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129762603</v>
+        <v>129762655</v>
       </c>
       <c r="B40" t="n">
-        <v>57733</v>
+        <v>91619</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5160,46 +5160,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>473521</v>
+        <v>473666</v>
       </c>
       <c r="R40" t="n">
-        <v>6991419</v>
+        <v>6991307</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5236,7 +5227,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Rejäla hackspår i stambasen av en stående död gran med full längd.</t>
+          <t>Flera fruktkroppar i en levande gran.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5245,12 +5236,33 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM40" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5268,10 +5280,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129762655</v>
+        <v>129762597</v>
       </c>
       <c r="B41" t="n">
-        <v>91617</v>
+        <v>57736</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5279,37 +5291,46 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>473666</v>
+        <v>473383</v>
       </c>
       <c r="R41" t="n">
-        <v>6991307</v>
+        <v>6991525</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5346,7 +5367,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en levande gran.</t>
+          <t>Savhack (ringhack), färska, på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5355,7 +5376,6 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5399,10 +5419,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129762597</v>
+        <v>129762603</v>
       </c>
       <c r="B42" t="n">
-        <v>57736</v>
+        <v>57733</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5410,16 +5430,16 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -5446,10 +5466,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>473383</v>
+        <v>473521</v>
       </c>
       <c r="R42" t="n">
-        <v>6991525</v>
+        <v>6991419</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5486,7 +5506,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Savhack (ringhack), färska, på en gran vid hyggeskanten.</t>
+          <t>Rejäla hackspår i stambasen av en stående död gran med full längd.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5501,26 +5521,6 @@
       <c r="AH42" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK42" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5541,7 +5541,7 @@
         <v>129762620</v>
       </c>
       <c r="B43" t="n">
-        <v>98682</v>
+        <v>98684</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5669,7 +5669,7 @@
         <v>129762648</v>
       </c>
       <c r="B44" t="n">
-        <v>91593</v>
+        <v>91595</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5935,7 +5935,7 @@
         <v>129762631</v>
       </c>
       <c r="B46" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6060,10 +6060,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129762646</v>
+        <v>129762658</v>
       </c>
       <c r="B47" t="n">
-        <v>91593</v>
+        <v>79081</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6071,30 +6071,26 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K47" t="inlineStr"/>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -6102,10 +6098,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>473393</v>
+        <v>473495</v>
       </c>
       <c r="R47" t="n">
-        <v>6991465</v>
+        <v>6991469</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6142,7 +6138,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>I en stående död gran.</t>
+          <t>På flera både döda och levande granar.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6157,7 +6153,7 @@
       </c>
       <c r="AH47" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ47" t="inlineStr">
@@ -6172,12 +6168,12 @@
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6195,10 +6191,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129762595</v>
+        <v>129762646</v>
       </c>
       <c r="B48" t="n">
-        <v>57736</v>
+        <v>91595</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6206,46 +6202,41 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>473369</v>
+        <v>473393</v>
       </c>
       <c r="R48" t="n">
-        <v>6991519</v>
+        <v>6991465</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6282,7 +6273,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en gran vid hyggeskanten.</t>
+          <t>I en stående död gran.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6291,12 +6282,13 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ48" t="inlineStr">
@@ -6311,12 +6303,12 @@
       </c>
       <c r="AM48" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6334,10 +6326,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129762658</v>
+        <v>129762595</v>
       </c>
       <c r="B49" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6345,37 +6337,46 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>473495</v>
+        <v>473369</v>
       </c>
       <c r="R49" t="n">
-        <v>6991469</v>
+        <v>6991519</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6412,7 +6413,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>På flera både döda och levande granar.</t>
+          <t>Ringhack (savhack), färska, på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6421,7 +6422,6 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -6442,12 +6442,12 @@
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6591,7 +6591,7 @@
         <v>129762656</v>
       </c>
       <c r="B51" t="n">
-        <v>91617</v>
+        <v>91619</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6719,46 +6719,50 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129762601</v>
+        <v>129762627</v>
       </c>
       <c r="B52" t="n">
-        <v>57896</v>
+        <v>98780</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr"/>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N52" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -6770,10 +6774,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>473628</v>
+        <v>473137</v>
       </c>
       <c r="R52" t="n">
-        <v>6991288</v>
+        <v>6991201</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6810,7 +6814,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Minst 2 individer med lockläte i flerskiktad barrblandskog med inslag av klena björkar och björkhögstubbar.</t>
+          <t>Minst 18 plantor och 1 vinterståndare inom ca 0,5 m2 yta söder om ett dike i barrblandskog.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6819,12 +6823,13 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
-          <t>Barrträd</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -6981,50 +6986,46 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129762627</v>
+        <v>129762601</v>
       </c>
       <c r="B54" t="n">
-        <v>98778</v>
+        <v>57896</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N54" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -7036,10 +7037,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>473137</v>
+        <v>473628</v>
       </c>
       <c r="R54" t="n">
-        <v>6991201</v>
+        <v>6991288</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7076,7 +7077,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Minst 18 plantor och 1 vinterståndare inom ca 0,5 m2 yta söder om ett dike i barrblandskog.</t>
+          <t>Minst 2 individer med lockläte i flerskiktad barrblandskog med inslag av klena björkar och björkhögstubbar.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7085,13 +7086,12 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Barrträd</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -7112,7 +7112,7 @@
         <v>129762653</v>
       </c>
       <c r="B55" t="n">
-        <v>91593</v>
+        <v>91595</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7247,7 +7247,7 @@
         <v>129762556</v>
       </c>
       <c r="B56" t="n">
-        <v>91597</v>
+        <v>91599</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7641,10 +7641,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129762661</v>
+        <v>129762557</v>
       </c>
       <c r="B59" t="n">
-        <v>79081</v>
+        <v>91599</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7652,26 +7652,30 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -7679,10 +7683,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>473612</v>
+        <v>473560</v>
       </c>
       <c r="R59" t="n">
-        <v>6991344</v>
+        <v>6991376</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7709,17 +7713,17 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Fruktkroppar längs flera meter i en granlåga.</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7734,7 +7738,7 @@
       </c>
       <c r="AH59" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ59" t="inlineStr">
@@ -7749,12 +7753,12 @@
       </c>
       <c r="AM59" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO59" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -7772,10 +7776,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129762557</v>
+        <v>129762661</v>
       </c>
       <c r="B60" t="n">
-        <v>91597</v>
+        <v>79081</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7783,30 +7787,26 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K60" t="inlineStr"/>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -7814,10 +7814,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>473560</v>
+        <v>473612</v>
       </c>
       <c r="R60" t="n">
-        <v>6991376</v>
+        <v>6991344</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7844,17 +7844,17 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Fruktkroppar längs flera meter i en granlåga.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7869,7 +7869,7 @@
       </c>
       <c r="AH60" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ60" t="inlineStr">
@@ -7884,12 +7884,12 @@
       </c>
       <c r="AM60" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO60" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
@@ -7910,7 +7910,7 @@
         <v>129762628</v>
       </c>
       <c r="B61" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -8165,7 +8165,7 @@
         <v>129762629</v>
       </c>
       <c r="B63" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>

--- a/artfynd/A 48959-2025 artfynd.xlsx
+++ b/artfynd/A 48959-2025 artfynd.xlsx
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129733680</v>
+        <v>129733684</v>
       </c>
       <c r="B4" t="n">
-        <v>91599</v>
+        <v>57736</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,34 +880,50 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>473498</v>
+        <v>473270</v>
       </c>
       <c r="R4" t="n">
-        <v>6991415</v>
+        <v>6991065</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -940,6 +956,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Observation av en födosökande individ av tretåig hackspett. Var dock svårt att se om det var en hona eller hane. I skogen omkring fyndplatsen finns höga livsmiljövärden för tretåig hackspett baserat på volymen stående död ved.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -966,10 +987,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129733693</v>
+        <v>129733680</v>
       </c>
       <c r="B5" t="n">
-        <v>91595</v>
+        <v>91599</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +998,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1022,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>473343</v>
+        <v>473498</v>
       </c>
       <c r="R5" t="n">
-        <v>6991073</v>
+        <v>6991415</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,10 +1084,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129733684</v>
+        <v>129733693</v>
       </c>
       <c r="B6" t="n">
-        <v>57736</v>
+        <v>91595</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,50 +1095,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>473270</v>
+        <v>473343</v>
       </c>
       <c r="R6" t="n">
-        <v>6991065</v>
+        <v>6991073</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1150,11 +1155,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-11-05</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Observation av en födosökande individ av tretåig hackspett. Var dock svårt att se om det var en hona eller hane. I skogen omkring fyndplatsen finns höga livsmiljövärden för tretåig hackspett baserat på volymen stående död ved.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1375,10 +1375,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129733696</v>
+        <v>129733689</v>
       </c>
       <c r="B9" t="n">
-        <v>91619</v>
+        <v>91595</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1386,19 +1386,23 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1406,10 +1410,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>473472</v>
+        <v>473505</v>
       </c>
       <c r="R9" t="n">
-        <v>6991545</v>
+        <v>6991422</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1468,10 +1472,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129733685</v>
+        <v>129733696</v>
       </c>
       <c r="B10" t="n">
-        <v>57733</v>
+        <v>91619</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1479,42 +1483,30 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>473633</v>
+        <v>473472</v>
       </c>
       <c r="R10" t="n">
-        <v>6991388</v>
+        <v>6991545</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1547,11 +1539,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-11-05</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Färska hackspår.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1578,42 +1565,42 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129733686</v>
+        <v>129733685</v>
       </c>
       <c r="B11" t="n">
-        <v>98780</v>
+        <v>57733</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1621,10 +1608,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>473562</v>
+        <v>473633</v>
       </c>
       <c r="R11" t="n">
-        <v>6991360</v>
+        <v>6991388</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1659,13 +1646,17 @@
           <t>2025-11-05</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Färska hackspår.</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1684,45 +1675,53 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129733689</v>
+        <v>129733686</v>
       </c>
       <c r="B12" t="n">
-        <v>91595</v>
+        <v>98780</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1108</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>473505</v>
+        <v>473562</v>
       </c>
       <c r="R12" t="n">
-        <v>6991422</v>
+        <v>6991360</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1763,6 +1762,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -3964,10 +3964,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129762663</v>
+        <v>129762640</v>
       </c>
       <c r="B31" t="n">
-        <v>79081</v>
+        <v>91595</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3975,26 +3975,30 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -4002,10 +4006,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>473588</v>
+        <v>473215</v>
       </c>
       <c r="R31" t="n">
-        <v>6991409</v>
+        <v>6991103</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4032,17 +4036,17 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>I en smal stående död gran.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4057,7 +4061,7 @@
       </c>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ31" t="inlineStr">
@@ -4072,12 +4076,12 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4095,10 +4099,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129762640</v>
+        <v>129762663</v>
       </c>
       <c r="B32" t="n">
-        <v>91595</v>
+        <v>79081</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4106,30 +4110,26 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4137,10 +4137,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>473215</v>
+        <v>473588</v>
       </c>
       <c r="R32" t="n">
-        <v>6991103</v>
+        <v>6991409</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4167,17 +4167,17 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>I en smal stående död gran.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4192,7 +4192,7 @@
       </c>
       <c r="AH32" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ32" t="inlineStr">
@@ -4207,12 +4207,12 @@
       </c>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4230,41 +4230,42 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129762651</v>
+        <v>129762664</v>
       </c>
       <c r="B33" t="n">
-        <v>91595</v>
+        <v>98697</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1108</v>
+        <v>219790</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr">
         <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4272,10 +4273,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>473497</v>
+        <v>473659</v>
       </c>
       <c r="R33" t="n">
-        <v>6991392</v>
+        <v>6991313</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4302,17 +4303,17 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en levande gran.</t>
+          <t>Minst 1 vinterståndare.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4328,26 +4329,6 @@
       <c r="AH33" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4496,53 +4477,65 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129762664</v>
+        <v>129762630</v>
       </c>
       <c r="B35" t="n">
-        <v>98697</v>
+        <v>98780</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>473659</v>
+        <v>473588</v>
       </c>
       <c r="R35" t="n">
-        <v>6991313</v>
+        <v>6991340</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4569,17 +4562,17 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Minst 1 vinterståndare.</t>
+          <t>Minst 6 plantor och 1 vinterståndare inom ca 0,5 m2 yta precis intill korallrot i gammal barrblandskog.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4612,65 +4605,52 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129762630</v>
+        <v>129762651</v>
       </c>
       <c r="B36" t="n">
-        <v>98780</v>
+        <v>91595</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>1108</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr"/>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>473588</v>
+        <v>473497</v>
       </c>
       <c r="R36" t="n">
-        <v>6991340</v>
+        <v>6991392</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4707,7 +4687,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Minst 6 plantor och 1 vinterståndare inom ca 0,5 m2 yta precis intill korallrot i gammal barrblandskog.</t>
+          <t>Flera fruktkroppar i en levande gran.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4723,6 +4703,26 @@
       <c r="AH36" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM36" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -6060,10 +6060,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129762658</v>
+        <v>129762646</v>
       </c>
       <c r="B47" t="n">
-        <v>79081</v>
+        <v>91595</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6071,26 +6071,30 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -6098,10 +6102,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>473495</v>
+        <v>473393</v>
       </c>
       <c r="R47" t="n">
-        <v>6991469</v>
+        <v>6991465</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6138,7 +6142,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>På flera både döda och levande granar.</t>
+          <t>I en stående död gran.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6153,7 +6157,7 @@
       </c>
       <c r="AH47" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ47" t="inlineStr">
@@ -6168,12 +6172,12 @@
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6191,10 +6195,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129762646</v>
+        <v>129762595</v>
       </c>
       <c r="B48" t="n">
-        <v>91595</v>
+        <v>57736</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6202,41 +6206,46 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>473393</v>
+        <v>473369</v>
       </c>
       <c r="R48" t="n">
-        <v>6991465</v>
+        <v>6991519</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6273,7 +6282,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>I en stående död gran.</t>
+          <t>Ringhack (savhack), färska, på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6282,13 +6291,12 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ48" t="inlineStr">
@@ -6303,12 +6311,12 @@
       </c>
       <c r="AM48" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6326,10 +6334,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129762595</v>
+        <v>129762658</v>
       </c>
       <c r="B49" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6337,46 +6345,37 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>473369</v>
+        <v>473495</v>
       </c>
       <c r="R49" t="n">
-        <v>6991519</v>
+        <v>6991469</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6413,7 +6412,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en gran vid hyggeskanten.</t>
+          <t>På flera både döda och levande granar.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6422,6 +6421,7 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -6442,12 +6442,12 @@
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>

--- a/artfynd/A 48959-2025 artfynd.xlsx
+++ b/artfynd/A 48959-2025 artfynd.xlsx
@@ -1375,10 +1375,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129733689</v>
+        <v>129733696</v>
       </c>
       <c r="B9" t="n">
-        <v>91595</v>
+        <v>91619</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1386,23 +1386,19 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1410,10 +1406,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>473505</v>
+        <v>473472</v>
       </c>
       <c r="R9" t="n">
-        <v>6991422</v>
+        <v>6991545</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1472,10 +1468,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129733696</v>
+        <v>129733685</v>
       </c>
       <c r="B10" t="n">
-        <v>91619</v>
+        <v>57733</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1483,30 +1479,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>473472</v>
+        <v>473633</v>
       </c>
       <c r="R10" t="n">
-        <v>6991545</v>
+        <v>6991388</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1539,6 +1547,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Färska hackspår.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1565,42 +1578,42 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129733685</v>
+        <v>129733686</v>
       </c>
       <c r="B11" t="n">
-        <v>57733</v>
+        <v>98780</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1608,10 +1621,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>473633</v>
+        <v>473562</v>
       </c>
       <c r="R11" t="n">
-        <v>6991388</v>
+        <v>6991360</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1646,17 +1659,13 @@
           <t>2025-11-05</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Färska hackspår.</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1675,53 +1684,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129733686</v>
+        <v>129733689</v>
       </c>
       <c r="B12" t="n">
-        <v>98780</v>
+        <v>91595</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>1108</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>473562</v>
+        <v>473505</v>
       </c>
       <c r="R12" t="n">
-        <v>6991360</v>
+        <v>6991422</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1762,7 +1763,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -3435,65 +3435,52 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129762632</v>
+        <v>129762649</v>
       </c>
       <c r="B27" t="n">
-        <v>98780</v>
+        <v>91595</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>1108</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr"/>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>473644</v>
+        <v>473475</v>
       </c>
       <c r="R27" t="n">
-        <v>6991272</v>
+        <v>6991471</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3520,17 +3507,17 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Minst 54 plantor inom ca 2 m2 yta strax norr om ett dike.</t>
+          <t>Flera fruktkroppar i stambasen av en stående död gran (24 cm BHD) med full längd. På fyndplatsen finns stående död ved i en volym som indikerar minst högt livsmiljövärde för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3546,6 +3533,26 @@
       <c r="AH27" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3563,10 +3570,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129762649</v>
+        <v>129762662</v>
       </c>
       <c r="B28" t="n">
-        <v>91595</v>
+        <v>79081</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3574,30 +3581,26 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3605,10 +3608,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>473475</v>
+        <v>473631</v>
       </c>
       <c r="R28" t="n">
-        <v>6991471</v>
+        <v>6991321</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3635,17 +3638,17 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i stambasen av en stående död gran (24 cm BHD) med full längd. På fyndplatsen finns stående död ved i en volym som indikerar minst högt livsmiljövärde för tretåig hackspett.</t>
+          <t>På gran i granskog.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3675,12 +3678,12 @@
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3698,48 +3701,65 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129762662</v>
+        <v>129762632</v>
       </c>
       <c r="B29" t="n">
-        <v>79081</v>
+        <v>98780</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>473631</v>
+        <v>473644</v>
       </c>
       <c r="R29" t="n">
-        <v>6991321</v>
+        <v>6991272</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3776,7 +3796,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>På gran i granskog.</t>
+          <t>Minst 54 plantor inom ca 2 m2 yta strax norr om ett dike.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3792,26 +3812,6 @@
       <c r="AH29" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -3964,10 +3964,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129762640</v>
+        <v>129762663</v>
       </c>
       <c r="B31" t="n">
-        <v>91595</v>
+        <v>79081</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3975,30 +3975,26 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -4006,10 +4002,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>473215</v>
+        <v>473588</v>
       </c>
       <c r="R31" t="n">
-        <v>6991103</v>
+        <v>6991409</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4036,17 +4032,17 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>I en smal stående död gran.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4061,7 +4057,7 @@
       </c>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ31" t="inlineStr">
@@ -4076,12 +4072,12 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4099,10 +4095,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129762663</v>
+        <v>129762640</v>
       </c>
       <c r="B32" t="n">
-        <v>79081</v>
+        <v>91595</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4110,26 +4106,30 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4137,10 +4137,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>473588</v>
+        <v>473215</v>
       </c>
       <c r="R32" t="n">
-        <v>6991409</v>
+        <v>6991103</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4167,17 +4167,17 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>I en smal stående död gran.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4192,7 +4192,7 @@
       </c>
       <c r="AH32" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ32" t="inlineStr">
@@ -4207,12 +4207,12 @@
       </c>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -6719,50 +6719,42 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129762627</v>
+        <v>129762594</v>
       </c>
       <c r="B52" t="n">
-        <v>98780</v>
+        <v>57736</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N52" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -6774,10 +6766,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>473137</v>
+        <v>473355</v>
       </c>
       <c r="R52" t="n">
-        <v>6991201</v>
+        <v>6991512</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6814,7 +6806,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Minst 18 plantor och 1 vinterståndare inom ca 0,5 m2 yta söder om ett dike i barrblandskog.</t>
+          <t>Ringhack, färska, på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6823,13 +6815,32 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM52" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -6847,10 +6858,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129762594</v>
+        <v>129762601</v>
       </c>
       <c r="B53" t="n">
-        <v>57736</v>
+        <v>57896</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6858,29 +6869,33 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -6894,10 +6909,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>473355</v>
+        <v>473628</v>
       </c>
       <c r="R53" t="n">
-        <v>6991512</v>
+        <v>6991288</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6934,7 +6949,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran vid hyggeskanten.</t>
+          <t>Minst 2 individer med lockläte i flerskiktad barrblandskog med inslag av klena björkar och björkhögstubbar.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6948,27 +6963,7 @@
       </c>
       <c r="AH53" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ53" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK53" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO53" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Barrträd</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -6986,46 +6981,50 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129762601</v>
+        <v>129762627</v>
       </c>
       <c r="B54" t="n">
-        <v>57896</v>
+        <v>98780</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr"/>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N54" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -7037,10 +7036,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>473628</v>
+        <v>473137</v>
       </c>
       <c r="R54" t="n">
-        <v>6991288</v>
+        <v>6991201</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7077,7 +7076,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Minst 2 individer med lockläte i flerskiktad barrblandskog med inslag av klena björkar och björkhögstubbar.</t>
+          <t>Minst 18 plantor och 1 vinterståndare inom ca 0,5 m2 yta söder om ett dike i barrblandskog.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7086,12 +7085,13 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
-          <t>Barrträd</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>

--- a/artfynd/A 48959-2025 artfynd.xlsx
+++ b/artfynd/A 48959-2025 artfynd.xlsx
@@ -6719,42 +6719,50 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129762594</v>
+        <v>129762627</v>
       </c>
       <c r="B52" t="n">
-        <v>57736</v>
+        <v>98780</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N52" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -6766,10 +6774,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>473355</v>
+        <v>473137</v>
       </c>
       <c r="R52" t="n">
-        <v>6991512</v>
+        <v>6991201</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6806,7 +6814,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran vid hyggeskanten.</t>
+          <t>Minst 18 plantor och 1 vinterståndare inom ca 0,5 m2 yta söder om ett dike i barrblandskog.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6815,32 +6823,13 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ52" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK52" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO52" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -6858,10 +6847,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129762601</v>
+        <v>129762594</v>
       </c>
       <c r="B53" t="n">
-        <v>57896</v>
+        <v>57736</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6869,33 +6858,29 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -6909,10 +6894,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>473628</v>
+        <v>473355</v>
       </c>
       <c r="R53" t="n">
-        <v>6991288</v>
+        <v>6991512</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6949,7 +6934,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Minst 2 individer med lockläte i flerskiktad barrblandskog med inslag av klena björkar och björkhögstubbar.</t>
+          <t>Ringhack, färska, på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6963,7 +6948,27 @@
       </c>
       <c r="AH53" t="inlineStr">
         <is>
-          <t>Barrträd</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM53" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -6981,50 +6986,46 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129762627</v>
+        <v>129762601</v>
       </c>
       <c r="B54" t="n">
-        <v>98780</v>
+        <v>57896</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N54" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -7036,10 +7037,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>473137</v>
+        <v>473628</v>
       </c>
       <c r="R54" t="n">
-        <v>6991201</v>
+        <v>6991288</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7076,7 +7077,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Minst 18 plantor och 1 vinterståndare inom ca 0,5 m2 yta söder om ett dike i barrblandskog.</t>
+          <t>Minst 2 individer med lockläte i flerskiktad barrblandskog med inslag av klena björkar och björkhögstubbar.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7085,13 +7086,12 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Barrträd</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>

--- a/artfynd/A 48959-2025 artfynd.xlsx
+++ b/artfynd/A 48959-2025 artfynd.xlsx
@@ -1375,10 +1375,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129733696</v>
+        <v>129733689</v>
       </c>
       <c r="B9" t="n">
-        <v>91619</v>
+        <v>91595</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1386,19 +1386,23 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1406,10 +1410,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>473472</v>
+        <v>473505</v>
       </c>
       <c r="R9" t="n">
-        <v>6991545</v>
+        <v>6991422</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1468,10 +1472,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129733685</v>
+        <v>129733696</v>
       </c>
       <c r="B10" t="n">
-        <v>57733</v>
+        <v>91619</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1479,42 +1483,30 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>473633</v>
+        <v>473472</v>
       </c>
       <c r="R10" t="n">
-        <v>6991388</v>
+        <v>6991545</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1547,11 +1539,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-11-05</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Färska hackspår.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1578,42 +1565,42 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129733686</v>
+        <v>129733685</v>
       </c>
       <c r="B11" t="n">
-        <v>98780</v>
+        <v>57733</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1621,10 +1608,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>473562</v>
+        <v>473633</v>
       </c>
       <c r="R11" t="n">
-        <v>6991360</v>
+        <v>6991388</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1659,13 +1646,17 @@
           <t>2025-11-05</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Färska hackspår.</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1684,45 +1675,53 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129733689</v>
+        <v>129733686</v>
       </c>
       <c r="B12" t="n">
-        <v>91595</v>
+        <v>98790</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1108</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>473505</v>
+        <v>473562</v>
       </c>
       <c r="R12" t="n">
-        <v>6991422</v>
+        <v>6991360</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1763,6 +1762,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -3704,7 +3704,7 @@
         <v>129762632</v>
       </c>
       <c r="B29" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4230,42 +4230,37 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129762664</v>
+        <v>129762660</v>
       </c>
       <c r="B33" t="n">
-        <v>98697</v>
+        <v>79081</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4273,10 +4268,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>473659</v>
+        <v>473564</v>
       </c>
       <c r="R33" t="n">
-        <v>6991313</v>
+        <v>6991395</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4303,17 +4298,17 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Minst 1 vinterståndare.</t>
+          <t>På bark av tall.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4329,6 +4324,26 @@
       <c r="AH33" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM33" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4346,48 +4361,65 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129762660</v>
+        <v>129762630</v>
       </c>
       <c r="B34" t="n">
-        <v>79081</v>
+        <v>98790</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr"/>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>473564</v>
+        <v>473588</v>
       </c>
       <c r="R34" t="n">
-        <v>6991395</v>
+        <v>6991340</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4424,7 +4456,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>På bark av tall.</t>
+          <t>Minst 6 plantor och 1 vinterståndare inom ca 0,5 m2 yta precis intill korallrot i gammal barrblandskog.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4440,26 +4472,6 @@
       <c r="AH34" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4477,65 +4489,52 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129762630</v>
+        <v>129762651</v>
       </c>
       <c r="B35" t="n">
-        <v>98780</v>
+        <v>91595</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>1108</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr"/>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>473588</v>
+        <v>473497</v>
       </c>
       <c r="R35" t="n">
-        <v>6991340</v>
+        <v>6991392</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4572,7 +4571,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Minst 6 plantor och 1 vinterståndare inom ca 0,5 m2 yta precis intill korallrot i gammal barrblandskog.</t>
+          <t>Flera fruktkroppar i en levande gran.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4588,6 +4587,26 @@
       <c r="AH35" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM35" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4605,41 +4624,42 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129762651</v>
+        <v>129762664</v>
       </c>
       <c r="B36" t="n">
-        <v>91595</v>
+        <v>98707</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1108</v>
+        <v>219790</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr">
         <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4647,10 +4667,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>473497</v>
+        <v>473659</v>
       </c>
       <c r="R36" t="n">
-        <v>6991392</v>
+        <v>6991313</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4677,17 +4697,17 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en levande gran.</t>
+          <t>Minst 1 vinterståndare.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4703,26 +4723,6 @@
       <c r="AH36" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4740,10 +4740,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129762644</v>
+        <v>129762593</v>
       </c>
       <c r="B37" t="n">
-        <v>91595</v>
+        <v>57736</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4751,41 +4751,46 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>473430</v>
+        <v>473284</v>
       </c>
       <c r="R37" t="n">
-        <v>6991442</v>
+        <v>6991191</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4822,7 +4827,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>I en granhögstubbe.</t>
+          <t>Ringhack, äldre, på stambasen av en gran i granskog.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4831,13 +4836,12 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ37" t="inlineStr">
@@ -4852,12 +4856,12 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -4875,10 +4879,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129762593</v>
+        <v>129762644</v>
       </c>
       <c r="B38" t="n">
-        <v>57736</v>
+        <v>91595</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4886,46 +4890,41 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>473284</v>
+        <v>473430</v>
       </c>
       <c r="R38" t="n">
-        <v>6991191</v>
+        <v>6991442</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4962,7 +4961,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en gran i granskog.</t>
+          <t>I en granhögstubbe.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4971,12 +4970,13 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ38" t="inlineStr">
@@ -4991,12 +4991,12 @@
       </c>
       <c r="AM38" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5541,7 +5541,7 @@
         <v>129762620</v>
       </c>
       <c r="B43" t="n">
-        <v>98684</v>
+        <v>98694</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5666,10 +5666,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129762648</v>
+        <v>129762659</v>
       </c>
       <c r="B44" t="n">
-        <v>91595</v>
+        <v>79081</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5677,30 +5677,26 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5708,10 +5704,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>473481</v>
+        <v>473494</v>
       </c>
       <c r="R44" t="n">
-        <v>6991527</v>
+        <v>6991425</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5748,7 +5744,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en stående döende gran med full längd.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5763,7 +5759,7 @@
       </c>
       <c r="AH44" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ44" t="inlineStr">
@@ -5778,12 +5774,12 @@
       </c>
       <c r="AM44" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -5801,48 +5797,65 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129762659</v>
+        <v>129762631</v>
       </c>
       <c r="B45" t="n">
-        <v>79081</v>
+        <v>98790</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr"/>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>473494</v>
+        <v>473609</v>
       </c>
       <c r="R45" t="n">
-        <v>6991425</v>
+        <v>6991306</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5879,7 +5892,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Minst 8 plantor och 2 vinterståndare inom ca 0,5 m2 yta i barrblandskog. Troligen finns fler plantor på fyndplatsen.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5895,26 +5908,6 @@
       <c r="AH45" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -5932,65 +5925,52 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129762631</v>
+        <v>129762648</v>
       </c>
       <c r="B46" t="n">
-        <v>98780</v>
+        <v>91595</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>1108</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr"/>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>473609</v>
+        <v>473481</v>
       </c>
       <c r="R46" t="n">
-        <v>6991306</v>
+        <v>6991527</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6027,7 +6007,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Minst 8 plantor och 2 vinterståndare inom ca 0,5 m2 yta i barrblandskog. Troligen finns fler plantor på fyndplatsen.</t>
+          <t>Flera fruktkroppar i en stående döende gran med full längd.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6042,7 +6022,27 @@
       </c>
       <c r="AH46" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM46" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6060,10 +6060,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129762646</v>
+        <v>129762658</v>
       </c>
       <c r="B47" t="n">
-        <v>91595</v>
+        <v>79081</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6071,30 +6071,26 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K47" t="inlineStr"/>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -6102,10 +6098,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>473393</v>
+        <v>473495</v>
       </c>
       <c r="R47" t="n">
-        <v>6991465</v>
+        <v>6991469</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6142,7 +6138,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>I en stående död gran.</t>
+          <t>På flera både döda och levande granar.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6157,7 +6153,7 @@
       </c>
       <c r="AH47" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ47" t="inlineStr">
@@ -6172,12 +6168,12 @@
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6195,10 +6191,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129762595</v>
+        <v>129762646</v>
       </c>
       <c r="B48" t="n">
-        <v>57736</v>
+        <v>91595</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6206,46 +6202,41 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>473369</v>
+        <v>473393</v>
       </c>
       <c r="R48" t="n">
-        <v>6991519</v>
+        <v>6991465</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6282,7 +6273,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en gran vid hyggeskanten.</t>
+          <t>I en stående död gran.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6291,12 +6282,13 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ48" t="inlineStr">
@@ -6311,12 +6303,12 @@
       </c>
       <c r="AM48" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6334,10 +6326,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129762658</v>
+        <v>129762595</v>
       </c>
       <c r="B49" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6345,37 +6337,46 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>473495</v>
+        <v>473369</v>
       </c>
       <c r="R49" t="n">
-        <v>6991469</v>
+        <v>6991519</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6412,7 +6413,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>På flera både döda och levande granar.</t>
+          <t>Ringhack (savhack), färska, på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6421,7 +6422,6 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -6442,12 +6442,12 @@
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6588,10 +6588,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129762656</v>
+        <v>129762594</v>
       </c>
       <c r="B51" t="n">
-        <v>91619</v>
+        <v>57736</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6599,37 +6599,46 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>473615</v>
+        <v>473355</v>
       </c>
       <c r="R51" t="n">
-        <v>6991356</v>
+        <v>6991512</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6656,17 +6665,17 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Rikligt med fruktkroppar i en stående döende gran med full längd.</t>
+          <t>Ringhack, färska, på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6675,7 +6684,6 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -6719,50 +6727,46 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129762627</v>
+        <v>129762601</v>
       </c>
       <c r="B52" t="n">
-        <v>98780</v>
+        <v>57896</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N52" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -6774,10 +6778,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>473137</v>
+        <v>473628</v>
       </c>
       <c r="R52" t="n">
-        <v>6991201</v>
+        <v>6991288</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6814,7 +6818,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Minst 18 plantor och 1 vinterståndare inom ca 0,5 m2 yta söder om ett dike i barrblandskog.</t>
+          <t>Minst 2 individer med lockläte i flerskiktad barrblandskog med inslag av klena björkar och björkhögstubbar.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6823,13 +6827,12 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Barrträd</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -6847,42 +6850,50 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129762594</v>
+        <v>129762627</v>
       </c>
       <c r="B53" t="n">
-        <v>57736</v>
+        <v>98790</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N53" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -6894,10 +6905,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>473355</v>
+        <v>473137</v>
       </c>
       <c r="R53" t="n">
-        <v>6991512</v>
+        <v>6991201</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6934,7 +6945,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran vid hyggeskanten.</t>
+          <t>Minst 18 plantor och 1 vinterståndare inom ca 0,5 m2 yta söder om ett dike i barrblandskog.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6943,32 +6954,13 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ53" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK53" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO53" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -6986,10 +6978,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129762601</v>
+        <v>129762656</v>
       </c>
       <c r="B54" t="n">
-        <v>57896</v>
+        <v>91619</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6997,50 +6989,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>473628</v>
+        <v>473615</v>
       </c>
       <c r="R54" t="n">
-        <v>6991288</v>
+        <v>6991356</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7067,17 +7046,17 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Minst 2 individer med lockläte i flerskiktad barrblandskog med inslag av klena björkar och björkhögstubbar.</t>
+          <t>Rikligt med fruktkroppar i en stående döende gran med full längd.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7086,12 +7065,33 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
-          <t>Barrträd</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ54" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK54" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM54" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO54" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -7910,7 +7910,7 @@
         <v>129762628</v>
       </c>
       <c r="B61" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -8165,7 +8165,7 @@
         <v>129762629</v>
       </c>
       <c r="B63" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>

--- a/artfynd/A 48959-2025 artfynd.xlsx
+++ b/artfynd/A 48959-2025 artfynd.xlsx
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129733684</v>
+        <v>129733680</v>
       </c>
       <c r="B4" t="n">
-        <v>57736</v>
+        <v>91599</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,50 +880,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>473270</v>
+        <v>473498</v>
       </c>
       <c r="R4" t="n">
-        <v>6991065</v>
+        <v>6991415</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -956,11 +940,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-11-05</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Observation av en födosökande individ av tretåig hackspett. Var dock svårt att se om det var en hona eller hane. I skogen omkring fyndplatsen finns höga livsmiljövärden för tretåig hackspett baserat på volymen stående död ved.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -987,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129733680</v>
+        <v>129733693</v>
       </c>
       <c r="B5" t="n">
-        <v>91599</v>
+        <v>91595</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -998,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1022,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>473498</v>
+        <v>473343</v>
       </c>
       <c r="R5" t="n">
-        <v>6991415</v>
+        <v>6991073</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1084,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129733693</v>
+        <v>129733684</v>
       </c>
       <c r="B6" t="n">
-        <v>91595</v>
+        <v>57736</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1095,34 +1074,50 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>473343</v>
+        <v>473270</v>
       </c>
       <c r="R6" t="n">
-        <v>6991073</v>
+        <v>6991065</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1155,6 +1150,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Observation av en födosökande individ av tretåig hackspett. Var dock svårt att se om det var en hona eller hane. I skogen omkring fyndplatsen finns höga livsmiljövärden för tretåig hackspett baserat på volymen stående död ved.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -3300,10 +3300,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129762641</v>
+        <v>129762662</v>
       </c>
       <c r="B26" t="n">
-        <v>91595</v>
+        <v>79081</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3311,30 +3311,26 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3342,10 +3338,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>473229</v>
+        <v>473631</v>
       </c>
       <c r="R26" t="n">
-        <v>6991116</v>
+        <v>6991321</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3372,17 +3368,17 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Gott om fruktkroppar i en stående död gran med full längd.</t>
+          <t>På gran i granskog.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3412,12 +3408,12 @@
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3435,7 +3431,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129762649</v>
+        <v>129762641</v>
       </c>
       <c r="B27" t="n">
         <v>91595</v>
@@ -3477,10 +3473,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>473475</v>
+        <v>473229</v>
       </c>
       <c r="R27" t="n">
-        <v>6991471</v>
+        <v>6991116</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3517,7 +3513,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i stambasen av en stående död gran (24 cm BHD) med full längd. På fyndplatsen finns stående död ved i en volym som indikerar minst högt livsmiljövärde för tretåig hackspett.</t>
+          <t>Gott om fruktkroppar i en stående död gran med full längd.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3570,10 +3566,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129762662</v>
+        <v>129762649</v>
       </c>
       <c r="B28" t="n">
-        <v>79081</v>
+        <v>91595</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3581,26 +3577,30 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3608,10 +3608,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>473631</v>
+        <v>473475</v>
       </c>
       <c r="R28" t="n">
-        <v>6991321</v>
+        <v>6991471</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3638,17 +3638,17 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>På gran i granskog.</t>
+          <t>Flera fruktkroppar i stambasen av en stående död gran (24 cm BHD) med full längd. På fyndplatsen finns stående död ved i en volym som indikerar minst högt livsmiljövärde för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3678,12 +3678,12 @@
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -5280,42 +5280,50 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129762597</v>
+        <v>129762620</v>
       </c>
       <c r="B41" t="n">
-        <v>57736</v>
+        <v>98694</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>220093</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N41" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -5327,10 +5335,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>473383</v>
+        <v>473586</v>
       </c>
       <c r="R41" t="n">
-        <v>6991525</v>
+        <v>6991339</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5367,7 +5375,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Savhack (ringhack), färska, på en gran vid hyggeskanten.</t>
+          <t>1 vinterståndare i gammal barrblandskog.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5376,32 +5384,13 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5419,10 +5408,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129762603</v>
+        <v>129762597</v>
       </c>
       <c r="B42" t="n">
-        <v>57733</v>
+        <v>57736</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5430,16 +5419,16 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -5466,10 +5455,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>473521</v>
+        <v>473383</v>
       </c>
       <c r="R42" t="n">
-        <v>6991419</v>
+        <v>6991525</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5506,7 +5495,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Rejäla hackspår i stambasen av en stående död gran med full längd.</t>
+          <t>Savhack (ringhack), färska, på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5521,6 +5510,26 @@
       <c r="AH42" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM42" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5538,50 +5547,42 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129762620</v>
+        <v>129762603</v>
       </c>
       <c r="B43" t="n">
-        <v>98694</v>
+        <v>57733</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220093</v>
+        <v>100049</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Châtel.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N43" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -5593,10 +5594,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>473586</v>
+        <v>473521</v>
       </c>
       <c r="R43" t="n">
-        <v>6991339</v>
+        <v>6991419</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5633,7 +5634,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>1 vinterståndare i gammal barrblandskog.</t>
+          <t>Rejäla hackspår i stambasen av en stående död gran med full längd.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5642,13 +5643,12 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -5666,10 +5666,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129762659</v>
+        <v>129762648</v>
       </c>
       <c r="B44" t="n">
-        <v>79081</v>
+        <v>91595</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5677,26 +5677,30 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5704,10 +5708,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>473494</v>
+        <v>473481</v>
       </c>
       <c r="R44" t="n">
-        <v>6991425</v>
+        <v>6991527</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5744,7 +5748,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Flera fruktkroppar i en stående döende gran med full längd.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5759,7 +5763,7 @@
       </c>
       <c r="AH44" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ44" t="inlineStr">
@@ -5774,12 +5778,12 @@
       </c>
       <c r="AM44" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -5925,10 +5929,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129762648</v>
+        <v>129762659</v>
       </c>
       <c r="B46" t="n">
-        <v>91595</v>
+        <v>79081</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5936,30 +5940,26 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -5967,10 +5967,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>473481</v>
+        <v>473494</v>
       </c>
       <c r="R46" t="n">
-        <v>6991527</v>
+        <v>6991425</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6007,7 +6007,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en stående döende gran med full längd.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6022,7 +6022,7 @@
       </c>
       <c r="AH46" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ46" t="inlineStr">
@@ -6037,12 +6037,12 @@
       </c>
       <c r="AM46" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6588,10 +6588,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129762594</v>
+        <v>129762601</v>
       </c>
       <c r="B51" t="n">
-        <v>57736</v>
+        <v>57896</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6599,29 +6599,33 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr"/>
       <c r="M51" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -6635,10 +6639,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>473355</v>
+        <v>473628</v>
       </c>
       <c r="R51" t="n">
-        <v>6991512</v>
+        <v>6991288</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6675,7 +6679,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran vid hyggeskanten.</t>
+          <t>Minst 2 individer med lockläte i flerskiktad barrblandskog med inslag av klena björkar och björkhögstubbar.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6689,27 +6693,7 @@
       </c>
       <c r="AH51" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ51" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK51" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO51" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Barrträd</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -6727,10 +6711,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129762601</v>
+        <v>129762656</v>
       </c>
       <c r="B52" t="n">
-        <v>57896</v>
+        <v>91619</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6738,50 +6722,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>473628</v>
+        <v>473615</v>
       </c>
       <c r="R52" t="n">
-        <v>6991288</v>
+        <v>6991356</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6808,17 +6779,17 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Minst 2 individer med lockläte i flerskiktad barrblandskog med inslag av klena björkar och björkhögstubbar.</t>
+          <t>Rikligt med fruktkroppar i en stående döende gran med full längd.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6827,12 +6798,33 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
-          <t>Barrträd</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM52" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -6850,50 +6842,42 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129762627</v>
+        <v>129762594</v>
       </c>
       <c r="B53" t="n">
-        <v>98790</v>
+        <v>57736</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N53" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -6905,10 +6889,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>473137</v>
+        <v>473355</v>
       </c>
       <c r="R53" t="n">
-        <v>6991201</v>
+        <v>6991512</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6945,7 +6929,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Minst 18 plantor och 1 vinterståndare inom ca 0,5 m2 yta söder om ett dike i barrblandskog.</t>
+          <t>Ringhack, färska, på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6954,13 +6938,32 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM53" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -6978,48 +6981,65 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129762656</v>
+        <v>129762627</v>
       </c>
       <c r="B54" t="n">
-        <v>91619</v>
+        <v>98790</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr"/>
-      <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr"/>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr"/>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>473615</v>
+        <v>473137</v>
       </c>
       <c r="R54" t="n">
-        <v>6991356</v>
+        <v>6991201</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7046,17 +7066,17 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Rikligt med fruktkroppar i en stående döende gran med full längd.</t>
+          <t>Minst 18 plantor och 1 vinterståndare inom ca 0,5 m2 yta söder om ett dike i barrblandskog.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7071,27 +7091,7 @@
       </c>
       <c r="AH54" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ54" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK54" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM54" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO54" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -7641,10 +7641,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129762557</v>
+        <v>129762661</v>
       </c>
       <c r="B59" t="n">
-        <v>91599</v>
+        <v>79081</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7652,30 +7652,26 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K59" t="inlineStr"/>
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -7683,10 +7679,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>473560</v>
+        <v>473612</v>
       </c>
       <c r="R59" t="n">
-        <v>6991376</v>
+        <v>6991344</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7713,17 +7709,17 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Fruktkroppar längs flera meter i en granlåga.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7738,7 +7734,7 @@
       </c>
       <c r="AH59" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ59" t="inlineStr">
@@ -7753,12 +7749,12 @@
       </c>
       <c r="AM59" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO59" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -7776,10 +7772,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129762661</v>
+        <v>129762557</v>
       </c>
       <c r="B60" t="n">
-        <v>79081</v>
+        <v>91599</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7787,26 +7783,30 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -7814,10 +7814,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>473612</v>
+        <v>473560</v>
       </c>
       <c r="R60" t="n">
-        <v>6991344</v>
+        <v>6991376</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7844,17 +7844,17 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Fruktkroppar längs flera meter i en granlåga.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7869,7 +7869,7 @@
       </c>
       <c r="AH60" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ60" t="inlineStr">
@@ -7884,12 +7884,12 @@
       </c>
       <c r="AM60" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO60" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>

--- a/artfynd/A 48959-2025 artfynd.xlsx
+++ b/artfynd/A 48959-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129733690</v>
       </c>
       <c r="B2" t="n">
-        <v>91595</v>
+        <v>91598</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129733694</v>
       </c>
       <c r="B3" t="n">
-        <v>91595</v>
+        <v>91598</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129733680</v>
+        <v>129733693</v>
       </c>
       <c r="B4" t="n">
-        <v>91599</v>
+        <v>91598</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>473498</v>
+        <v>473343</v>
       </c>
       <c r="R4" t="n">
-        <v>6991415</v>
+        <v>6991073</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129733693</v>
+        <v>129733680</v>
       </c>
       <c r="B5" t="n">
-        <v>91595</v>
+        <v>91602</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>473343</v>
+        <v>473498</v>
       </c>
       <c r="R5" t="n">
-        <v>6991073</v>
+        <v>6991415</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1066,7 @@
         <v>129733684</v>
       </c>
       <c r="B6" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1184,7 +1184,7 @@
         <v>129733695</v>
       </c>
       <c r="B7" t="n">
-        <v>91595</v>
+        <v>91598</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1281,7 +1281,7 @@
         <v>129733692</v>
       </c>
       <c r="B8" t="n">
-        <v>91595</v>
+        <v>91598</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1375,45 +1375,53 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129733689</v>
+        <v>129733686</v>
       </c>
       <c r="B9" t="n">
-        <v>91595</v>
+        <v>98794</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1108</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>473505</v>
+        <v>473562</v>
       </c>
       <c r="R9" t="n">
-        <v>6991422</v>
+        <v>6991360</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1454,6 +1462,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1472,10 +1481,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129733696</v>
+        <v>129733685</v>
       </c>
       <c r="B10" t="n">
-        <v>91619</v>
+        <v>57734</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1483,30 +1492,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>473472</v>
+        <v>473633</v>
       </c>
       <c r="R10" t="n">
-        <v>6991545</v>
+        <v>6991388</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1539,6 +1560,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Färska hackspår.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1565,10 +1591,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129733685</v>
+        <v>129733689</v>
       </c>
       <c r="B11" t="n">
-        <v>57733</v>
+        <v>91598</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1576,42 +1602,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>1108</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>473633</v>
+        <v>473505</v>
       </c>
       <c r="R11" t="n">
-        <v>6991388</v>
+        <v>6991422</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1644,11 +1662,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-11-05</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Färska hackspår.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1675,53 +1688,41 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129733686</v>
+        <v>129733696</v>
       </c>
       <c r="B12" t="n">
-        <v>98790</v>
+        <v>91622</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>473562</v>
+        <v>473472</v>
       </c>
       <c r="R12" t="n">
-        <v>6991360</v>
+        <v>6991545</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1762,7 +1763,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1784,7 +1784,7 @@
         <v>129733681</v>
       </c>
       <c r="B13" t="n">
-        <v>91599</v>
+        <v>91602</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1881,7 +1881,7 @@
         <v>129733687</v>
       </c>
       <c r="B14" t="n">
-        <v>91595</v>
+        <v>91598</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1978,7 +1978,7 @@
         <v>129733691</v>
       </c>
       <c r="B15" t="n">
-        <v>91595</v>
+        <v>91598</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         <v>129733683</v>
       </c>
       <c r="B16" t="n">
-        <v>92317</v>
+        <v>92320</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2172,7 +2172,7 @@
         <v>129733682</v>
       </c>
       <c r="B17" t="n">
-        <v>92317</v>
+        <v>92320</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2269,7 +2269,7 @@
         <v>129733688</v>
       </c>
       <c r="B18" t="n">
-        <v>91595</v>
+        <v>91598</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2363,32 +2363,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129762562</v>
+        <v>129762650</v>
       </c>
       <c r="B19" t="n">
-        <v>92317</v>
+        <v>91598</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>3298</v>
+        <v>1108</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2405,10 +2405,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>473408</v>
+        <v>473464</v>
       </c>
       <c r="R19" t="n">
-        <v>6991459</v>
+        <v>6991416</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Rikligt med fruktkroppar i stambasen av en hyfsat grov stående död gran med full längd.</t>
+          <t>Flera fruktkroppar i stambasen av en stående döende grov gran.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2498,10 +2498,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129762650</v>
+        <v>129762639</v>
       </c>
       <c r="B20" t="n">
-        <v>91595</v>
+        <v>91598</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2540,10 +2540,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>473464</v>
+        <v>473289</v>
       </c>
       <c r="R20" t="n">
-        <v>6991416</v>
+        <v>6991144</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2580,7 +2580,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i stambasen av en stående döende grov gran.</t>
+          <t>I två stående döda granar.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2595,7 +2595,7 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
@@ -2633,10 +2633,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129762639</v>
+        <v>129762642</v>
       </c>
       <c r="B21" t="n">
-        <v>91595</v>
+        <v>91598</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2663,11 +2663,7 @@
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2675,10 +2671,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>473289</v>
+        <v>473243</v>
       </c>
       <c r="R21" t="n">
-        <v>6991144</v>
+        <v>6991220</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2715,7 +2711,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>I två stående döda granar.</t>
+          <t>I stambasen av en döende gran.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2745,12 +2741,12 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -2768,10 +2764,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129762642</v>
+        <v>129762643</v>
       </c>
       <c r="B22" t="n">
-        <v>91595</v>
+        <v>91598</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2798,7 +2794,11 @@
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2806,10 +2806,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>473243</v>
+        <v>473253</v>
       </c>
       <c r="R22" t="n">
-        <v>6991220</v>
+        <v>6991258</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2846,7 +2846,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>I stambasen av en döende gran.</t>
+          <t>Flera fruktkroppar i en stående döende gran.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2899,32 +2899,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129762643</v>
+        <v>129762562</v>
       </c>
       <c r="B23" t="n">
-        <v>91595</v>
+        <v>92320</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1108</v>
+        <v>3298</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2941,10 +2941,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>473253</v>
+        <v>473408</v>
       </c>
       <c r="R23" t="n">
-        <v>6991258</v>
+        <v>6991459</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2981,7 +2981,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en stående döende gran.</t>
+          <t>Rikligt med fruktkroppar i stambasen av en hyfsat grov stående död gran med full längd.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
@@ -3011,12 +3011,12 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3037,7 +3037,7 @@
         <v>129762654</v>
       </c>
       <c r="B24" t="n">
-        <v>91595</v>
+        <v>91598</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3168,7 +3168,7 @@
         <v>129762652</v>
       </c>
       <c r="B25" t="n">
-        <v>91595</v>
+        <v>91598</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3303,7 +3303,7 @@
         <v>129762662</v>
       </c>
       <c r="B26" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3434,7 +3434,7 @@
         <v>129762641</v>
       </c>
       <c r="B27" t="n">
-        <v>91595</v>
+        <v>91598</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3569,7 +3569,7 @@
         <v>129762649</v>
       </c>
       <c r="B28" t="n">
-        <v>91595</v>
+        <v>91598</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3704,7 +3704,7 @@
         <v>129762632</v>
       </c>
       <c r="B29" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3832,7 +3832,7 @@
         <v>129762647</v>
       </c>
       <c r="B30" t="n">
-        <v>91595</v>
+        <v>91598</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3967,7 +3967,7 @@
         <v>129762663</v>
       </c>
       <c r="B31" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4098,7 +4098,7 @@
         <v>129762640</v>
       </c>
       <c r="B32" t="n">
-        <v>91595</v>
+        <v>91598</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4230,37 +4230,42 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129762660</v>
+        <v>129762664</v>
       </c>
       <c r="B33" t="n">
-        <v>79081</v>
+        <v>98711</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4268,10 +4273,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>473564</v>
+        <v>473659</v>
       </c>
       <c r="R33" t="n">
-        <v>6991395</v>
+        <v>6991313</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4298,17 +4303,17 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>På bark av tall.</t>
+          <t>Minst 1 vinterståndare.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4324,26 +4329,6 @@
       <c r="AH33" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4361,65 +4346,52 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129762630</v>
+        <v>129762651</v>
       </c>
       <c r="B34" t="n">
-        <v>98790</v>
+        <v>91598</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>1108</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr"/>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>473588</v>
+        <v>473497</v>
       </c>
       <c r="R34" t="n">
-        <v>6991340</v>
+        <v>6991392</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4456,7 +4428,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Minst 6 plantor och 1 vinterståndare inom ca 0,5 m2 yta precis intill korallrot i gammal barrblandskog.</t>
+          <t>Flera fruktkroppar i en levande gran.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4472,6 +4444,26 @@
       <c r="AH34" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM34" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4489,52 +4481,65 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129762651</v>
+        <v>129762630</v>
       </c>
       <c r="B35" t="n">
-        <v>91595</v>
+        <v>98794</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1108</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr"/>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>473497</v>
+        <v>473588</v>
       </c>
       <c r="R35" t="n">
-        <v>6991392</v>
+        <v>6991340</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4571,7 +4576,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en levande gran.</t>
+          <t>Minst 6 plantor och 1 vinterståndare inom ca 0,5 m2 yta precis intill korallrot i gammal barrblandskog.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4587,26 +4592,6 @@
       <c r="AH35" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4624,42 +4609,37 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129762664</v>
+        <v>129762660</v>
       </c>
       <c r="B36" t="n">
-        <v>98707</v>
+        <v>79084</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4667,10 +4647,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>473659</v>
+        <v>473564</v>
       </c>
       <c r="R36" t="n">
-        <v>6991313</v>
+        <v>6991395</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4697,17 +4677,17 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Minst 1 vinterståndare.</t>
+          <t>På bark av tall.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4723,6 +4703,26 @@
       <c r="AH36" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM36" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4740,10 +4740,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129762593</v>
+        <v>129762644</v>
       </c>
       <c r="B37" t="n">
-        <v>57736</v>
+        <v>91598</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4751,46 +4751,41 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>473284</v>
+        <v>473430</v>
       </c>
       <c r="R37" t="n">
-        <v>6991191</v>
+        <v>6991442</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4827,7 +4822,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en gran i granskog.</t>
+          <t>I en granhögstubbe.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4836,12 +4831,13 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ37" t="inlineStr">
@@ -4856,12 +4852,12 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -4879,10 +4875,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129762644</v>
+        <v>129762593</v>
       </c>
       <c r="B38" t="n">
-        <v>91595</v>
+        <v>57737</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4890,41 +4886,46 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>473430</v>
+        <v>473284</v>
       </c>
       <c r="R38" t="n">
-        <v>6991442</v>
+        <v>6991191</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4961,7 +4962,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>I en granhögstubbe.</t>
+          <t>Ringhack, äldre, på stambasen av en gran i granskog.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4970,13 +4971,12 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ38" t="inlineStr">
@@ -4991,12 +4991,12 @@
       </c>
       <c r="AM38" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5017,7 +5017,7 @@
         <v>129762645</v>
       </c>
       <c r="B39" t="n">
-        <v>91595</v>
+        <v>91598</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5149,10 +5149,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129762655</v>
+        <v>129762603</v>
       </c>
       <c r="B40" t="n">
-        <v>91619</v>
+        <v>57734</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5160,37 +5160,46 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr"/>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>473666</v>
+        <v>473521</v>
       </c>
       <c r="R40" t="n">
-        <v>6991307</v>
+        <v>6991419</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5227,7 +5236,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en levande gran.</t>
+          <t>Rejäla hackspår i stambasen av en stående död gran med full längd.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5236,33 +5245,12 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5280,50 +5268,42 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129762620</v>
+        <v>129762597</v>
       </c>
       <c r="B41" t="n">
-        <v>98694</v>
+        <v>57737</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220093</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Châtel.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N41" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -5335,10 +5315,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>473586</v>
+        <v>473383</v>
       </c>
       <c r="R41" t="n">
-        <v>6991339</v>
+        <v>6991525</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5375,7 +5355,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>1 vinterståndare i gammal barrblandskog.</t>
+          <t>Savhack (ringhack), färska, på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5384,13 +5364,32 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM41" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5408,42 +5407,50 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129762597</v>
+        <v>129762620</v>
       </c>
       <c r="B42" t="n">
-        <v>57736</v>
+        <v>98698</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>220093</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N42" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -5455,10 +5462,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>473383</v>
+        <v>473586</v>
       </c>
       <c r="R42" t="n">
-        <v>6991525</v>
+        <v>6991339</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5495,7 +5502,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Savhack (ringhack), färska, på en gran vid hyggeskanten.</t>
+          <t>1 vinterståndare i gammal barrblandskog.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5504,32 +5511,13 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK42" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5547,10 +5535,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129762603</v>
+        <v>129762655</v>
       </c>
       <c r="B43" t="n">
-        <v>57733</v>
+        <v>91622</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5558,46 +5546,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>473521</v>
+        <v>473666</v>
       </c>
       <c r="R43" t="n">
-        <v>6991419</v>
+        <v>6991307</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5634,7 +5613,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Rejäla hackspår i stambasen av en stående död gran med full längd.</t>
+          <t>Flera fruktkroppar i en levande gran.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5643,12 +5622,33 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM43" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -5666,10 +5666,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129762648</v>
+        <v>129762659</v>
       </c>
       <c r="B44" t="n">
-        <v>91595</v>
+        <v>79084</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5677,30 +5677,26 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5708,10 +5704,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>473481</v>
+        <v>473494</v>
       </c>
       <c r="R44" t="n">
-        <v>6991527</v>
+        <v>6991425</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5748,7 +5744,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en stående döende gran med full längd.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5763,7 +5759,7 @@
       </c>
       <c r="AH44" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ44" t="inlineStr">
@@ -5778,12 +5774,12 @@
       </c>
       <c r="AM44" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -5801,65 +5797,52 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129762631</v>
+        <v>129762648</v>
       </c>
       <c r="B45" t="n">
-        <v>98790</v>
+        <v>91598</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>1108</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L45" t="inlineStr"/>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>473609</v>
+        <v>473481</v>
       </c>
       <c r="R45" t="n">
-        <v>6991306</v>
+        <v>6991527</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5896,7 +5879,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Minst 8 plantor och 2 vinterståndare inom ca 0,5 m2 yta i barrblandskog. Troligen finns fler plantor på fyndplatsen.</t>
+          <t>Flera fruktkroppar i en stående döende gran med full längd.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5911,7 +5894,27 @@
       </c>
       <c r="AH45" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM45" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -5929,48 +5932,65 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129762659</v>
+        <v>129762631</v>
       </c>
       <c r="B46" t="n">
-        <v>79081</v>
+        <v>98794</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr"/>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>473494</v>
+        <v>473609</v>
       </c>
       <c r="R46" t="n">
-        <v>6991425</v>
+        <v>6991306</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6007,7 +6027,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Minst 8 plantor och 2 vinterståndare inom ca 0,5 m2 yta i barrblandskog. Troligen finns fler plantor på fyndplatsen.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6023,26 +6043,6 @@
       <c r="AH46" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ46" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK46" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6063,7 +6063,7 @@
         <v>129762658</v>
       </c>
       <c r="B47" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6191,10 +6191,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129762646</v>
+        <v>129762595</v>
       </c>
       <c r="B48" t="n">
-        <v>91595</v>
+        <v>57737</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6202,41 +6202,46 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>473393</v>
+        <v>473369</v>
       </c>
       <c r="R48" t="n">
-        <v>6991465</v>
+        <v>6991519</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6273,7 +6278,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>I en stående död gran.</t>
+          <t>Ringhack (savhack), färska, på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6282,13 +6287,12 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ48" t="inlineStr">
@@ -6303,12 +6307,12 @@
       </c>
       <c r="AM48" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6326,10 +6330,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129762595</v>
+        <v>129762646</v>
       </c>
       <c r="B49" t="n">
-        <v>57736</v>
+        <v>91598</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6337,46 +6341,41 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>473369</v>
+        <v>473393</v>
       </c>
       <c r="R49" t="n">
-        <v>6991519</v>
+        <v>6991465</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6413,7 +6412,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en gran vid hyggeskanten.</t>
+          <t>I en stående död gran.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6422,12 +6421,13 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ49" t="inlineStr">
@@ -6442,12 +6442,12 @@
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6468,7 +6468,7 @@
         <v>129762602</v>
       </c>
       <c r="B50" t="n">
-        <v>57733</v>
+        <v>57734</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6588,10 +6588,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129762601</v>
+        <v>129762656</v>
       </c>
       <c r="B51" t="n">
-        <v>57896</v>
+        <v>91622</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6599,50 +6599,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>473628</v>
+        <v>473615</v>
       </c>
       <c r="R51" t="n">
-        <v>6991288</v>
+        <v>6991356</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6669,17 +6656,17 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Minst 2 individer med lockläte i flerskiktad barrblandskog med inslag av klena björkar och björkhögstubbar.</t>
+          <t>Rikligt med fruktkroppar i en stående döende gran med full längd.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6688,12 +6675,33 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
-          <t>Barrträd</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM51" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -6711,10 +6719,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129762656</v>
+        <v>129762594</v>
       </c>
       <c r="B52" t="n">
-        <v>91619</v>
+        <v>57737</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6722,37 +6730,46 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>473615</v>
+        <v>473355</v>
       </c>
       <c r="R52" t="n">
-        <v>6991356</v>
+        <v>6991512</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6779,17 +6796,17 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Rikligt med fruktkroppar i en stående döende gran med full längd.</t>
+          <t>Ringhack, färska, på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6798,7 +6815,6 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -6842,10 +6858,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129762594</v>
+        <v>129762601</v>
       </c>
       <c r="B53" t="n">
-        <v>57736</v>
+        <v>57895</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6853,29 +6869,33 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -6889,10 +6909,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>473355</v>
+        <v>473628</v>
       </c>
       <c r="R53" t="n">
-        <v>6991512</v>
+        <v>6991288</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6929,7 +6949,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran vid hyggeskanten.</t>
+          <t>Minst 2 individer med lockläte i flerskiktad barrblandskog med inslag av klena björkar och björkhögstubbar.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6943,27 +6963,7 @@
       </c>
       <c r="AH53" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ53" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK53" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO53" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Barrträd</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -6984,7 +6984,7 @@
         <v>129762627</v>
       </c>
       <c r="B54" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7112,7 +7112,7 @@
         <v>129762653</v>
       </c>
       <c r="B55" t="n">
-        <v>91595</v>
+        <v>91598</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7247,7 +7247,7 @@
         <v>129762556</v>
       </c>
       <c r="B56" t="n">
-        <v>91599</v>
+        <v>91602</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7382,7 +7382,7 @@
         <v>129762600</v>
       </c>
       <c r="B57" t="n">
-        <v>57896</v>
+        <v>57895</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7505,7 +7505,7 @@
         <v>129762596</v>
       </c>
       <c r="B58" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7644,7 +7644,7 @@
         <v>129762661</v>
       </c>
       <c r="B59" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7775,7 +7775,7 @@
         <v>129762557</v>
       </c>
       <c r="B60" t="n">
-        <v>91599</v>
+        <v>91602</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7910,7 +7910,7 @@
         <v>129762628</v>
       </c>
       <c r="B61" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -8038,7 +8038,7 @@
         <v>129762598</v>
       </c>
       <c r="B62" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8165,7 +8165,7 @@
         <v>129762629</v>
       </c>
       <c r="B63" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>

--- a/artfynd/A 48959-2025 artfynd.xlsx
+++ b/artfynd/A 48959-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129733690</v>
+        <v>129733694</v>
       </c>
       <c r="B2" t="n">
         <v>91598</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>473509</v>
+        <v>473330</v>
       </c>
       <c r="R2" t="n">
-        <v>6991413</v>
+        <v>6991067</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,7 +772,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129733694</v>
+        <v>129733690</v>
       </c>
       <c r="B3" t="n">
         <v>91598</v>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>473330</v>
+        <v>473509</v>
       </c>
       <c r="R3" t="n">
-        <v>6991067</v>
+        <v>6991413</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129733693</v>
+        <v>129733680</v>
       </c>
       <c r="B4" t="n">
-        <v>91598</v>
+        <v>91602</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>473343</v>
+        <v>473498</v>
       </c>
       <c r="R4" t="n">
-        <v>6991073</v>
+        <v>6991415</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129733680</v>
+        <v>129733693</v>
       </c>
       <c r="B5" t="n">
-        <v>91602</v>
+        <v>91598</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>473498</v>
+        <v>473343</v>
       </c>
       <c r="R5" t="n">
-        <v>6991415</v>
+        <v>6991073</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1481,10 +1481,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129733685</v>
+        <v>129733689</v>
       </c>
       <c r="B10" t="n">
-        <v>57734</v>
+        <v>91598</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1492,42 +1492,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>1108</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>473633</v>
+        <v>473505</v>
       </c>
       <c r="R10" t="n">
-        <v>6991388</v>
+        <v>6991422</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1560,11 +1552,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-11-05</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Färska hackspår.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1591,10 +1578,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129733689</v>
+        <v>129733696</v>
       </c>
       <c r="B11" t="n">
-        <v>91598</v>
+        <v>91622</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1602,23 +1589,19 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1626,10 +1609,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>473505</v>
+        <v>473472</v>
       </c>
       <c r="R11" t="n">
-        <v>6991422</v>
+        <v>6991545</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1688,10 +1671,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129733696</v>
+        <v>129733685</v>
       </c>
       <c r="B12" t="n">
-        <v>91622</v>
+        <v>57734</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1699,30 +1682,42 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>473472</v>
+        <v>473633</v>
       </c>
       <c r="R12" t="n">
-        <v>6991545</v>
+        <v>6991388</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1755,6 +1750,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Färska hackspår.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2363,7 +2363,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129762650</v>
+        <v>129762642</v>
       </c>
       <c r="B19" t="n">
         <v>91598</v>
@@ -2393,11 +2393,7 @@
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2405,10 +2401,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>473464</v>
+        <v>473243</v>
       </c>
       <c r="R19" t="n">
-        <v>6991416</v>
+        <v>6991220</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2445,7 +2441,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i stambasen av en stående döende grov gran.</t>
+          <t>I stambasen av en döende gran.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2460,7 +2456,7 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
@@ -2475,12 +2471,12 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2498,32 +2494,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129762639</v>
+        <v>129762562</v>
       </c>
       <c r="B20" t="n">
-        <v>91598</v>
+        <v>92320</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1108</v>
+        <v>3298</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2540,10 +2536,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>473289</v>
+        <v>473408</v>
       </c>
       <c r="R20" t="n">
-        <v>6991144</v>
+        <v>6991459</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2580,7 +2576,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>I två stående döda granar.</t>
+          <t>Rikligt med fruktkroppar i stambasen av en hyfsat grov stående död gran med full längd.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2595,7 +2591,7 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
@@ -2633,7 +2629,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129762642</v>
+        <v>129762650</v>
       </c>
       <c r="B21" t="n">
         <v>91598</v>
@@ -2663,7 +2659,11 @@
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>473243</v>
+        <v>473464</v>
       </c>
       <c r="R21" t="n">
-        <v>6991220</v>
+        <v>6991416</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2711,7 +2711,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>I stambasen av en döende gran.</t>
+          <t>Flera fruktkroppar i stambasen av en stående döende grov gran.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
@@ -2741,12 +2741,12 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -2764,7 +2764,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129762643</v>
+        <v>129762639</v>
       </c>
       <c r="B22" t="n">
         <v>91598</v>
@@ -2806,10 +2806,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>473253</v>
+        <v>473289</v>
       </c>
       <c r="R22" t="n">
-        <v>6991258</v>
+        <v>6991144</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2846,7 +2846,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en stående döende gran.</t>
+          <t>I två stående döda granar.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -2899,32 +2899,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129762562</v>
+        <v>129762643</v>
       </c>
       <c r="B23" t="n">
-        <v>92320</v>
+        <v>91598</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>3298</v>
+        <v>1108</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2941,10 +2941,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>473408</v>
+        <v>473253</v>
       </c>
       <c r="R23" t="n">
-        <v>6991459</v>
+        <v>6991258</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2981,7 +2981,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Rikligt med fruktkroppar i stambasen av en hyfsat grov stående död gran med full längd.</t>
+          <t>Flera fruktkroppar i en stående döende gran.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
@@ -3011,12 +3011,12 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3431,52 +3431,65 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129762641</v>
+        <v>129762632</v>
       </c>
       <c r="B27" t="n">
-        <v>91598</v>
+        <v>98794</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1108</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>473229</v>
+        <v>473644</v>
       </c>
       <c r="R27" t="n">
-        <v>6991116</v>
+        <v>6991272</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3503,17 +3516,17 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Gott om fruktkroppar i en stående död gran med full längd.</t>
+          <t>Minst 54 plantor inom ca 2 m2 yta strax norr om ett dike.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3529,26 +3542,6 @@
       <c r="AH27" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3566,7 +3559,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129762649</v>
+        <v>129762641</v>
       </c>
       <c r="B28" t="n">
         <v>91598</v>
@@ -3608,10 +3601,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>473475</v>
+        <v>473229</v>
       </c>
       <c r="R28" t="n">
-        <v>6991471</v>
+        <v>6991116</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3648,7 +3641,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i stambasen av en stående död gran (24 cm BHD) med full längd. På fyndplatsen finns stående död ved i en volym som indikerar minst högt livsmiljövärde för tretåig hackspett.</t>
+          <t>Gott om fruktkroppar i en stående död gran med full längd.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3701,65 +3694,52 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129762632</v>
+        <v>129762649</v>
       </c>
       <c r="B29" t="n">
-        <v>98794</v>
+        <v>91598</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>1108</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr"/>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>473644</v>
+        <v>473475</v>
       </c>
       <c r="R29" t="n">
-        <v>6991272</v>
+        <v>6991471</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3786,17 +3766,17 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Minst 54 plantor inom ca 2 m2 yta strax norr om ett dike.</t>
+          <t>Flera fruktkroppar i stambasen av en stående död gran (24 cm BHD) med full längd. På fyndplatsen finns stående död ved i en volym som indikerar minst högt livsmiljövärde för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3812,6 +3792,26 @@
       <c r="AH29" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -4230,42 +4230,41 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129762664</v>
+        <v>129762651</v>
       </c>
       <c r="B33" t="n">
-        <v>98711</v>
+        <v>91598</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>219790</v>
+        <v>1108</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr"/>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4273,10 +4272,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>473659</v>
+        <v>473497</v>
       </c>
       <c r="R33" t="n">
-        <v>6991313</v>
+        <v>6991392</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4303,17 +4302,17 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Minst 1 vinterståndare.</t>
+          <t>Flera fruktkroppar i en levande gran.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4329,6 +4328,26 @@
       <c r="AH33" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM33" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4346,41 +4365,42 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129762651</v>
+        <v>129762664</v>
       </c>
       <c r="B34" t="n">
-        <v>91598</v>
+        <v>98711</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1108</v>
+        <v>219790</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4388,10 +4408,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>473497</v>
+        <v>473659</v>
       </c>
       <c r="R34" t="n">
-        <v>6991392</v>
+        <v>6991313</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4418,17 +4438,17 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en levande gran.</t>
+          <t>Minst 1 vinterståndare.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4444,26 +4464,6 @@
       <c r="AH34" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4740,10 +4740,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129762644</v>
+        <v>129762593</v>
       </c>
       <c r="B37" t="n">
-        <v>91598</v>
+        <v>57737</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4751,41 +4751,46 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>473430</v>
+        <v>473284</v>
       </c>
       <c r="R37" t="n">
-        <v>6991442</v>
+        <v>6991191</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4822,7 +4827,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>I en granhögstubbe.</t>
+          <t>Ringhack, äldre, på stambasen av en gran i granskog.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4831,13 +4836,12 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ37" t="inlineStr">
@@ -4852,12 +4856,12 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -4875,10 +4879,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129762593</v>
+        <v>129762644</v>
       </c>
       <c r="B38" t="n">
-        <v>57737</v>
+        <v>91598</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4886,46 +4890,41 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>473284</v>
+        <v>473430</v>
       </c>
       <c r="R38" t="n">
-        <v>6991191</v>
+        <v>6991442</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4962,7 +4961,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en gran i granskog.</t>
+          <t>I en granhögstubbe.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4971,12 +4970,13 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ38" t="inlineStr">
@@ -4991,12 +4991,12 @@
       </c>
       <c r="AM38" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5149,10 +5149,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129762603</v>
+        <v>129762597</v>
       </c>
       <c r="B40" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5160,16 +5160,16 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -5196,10 +5196,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>473521</v>
+        <v>473383</v>
       </c>
       <c r="R40" t="n">
-        <v>6991419</v>
+        <v>6991525</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5236,7 +5236,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Rejäla hackspår i stambasen av en stående död gran med full längd.</t>
+          <t>Savhack (ringhack), färska, på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5251,6 +5251,26 @@
       <c r="AH40" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM40" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5268,10 +5288,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129762597</v>
+        <v>129762603</v>
       </c>
       <c r="B41" t="n">
-        <v>57737</v>
+        <v>57734</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5279,16 +5299,16 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -5315,10 +5335,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>473383</v>
+        <v>473521</v>
       </c>
       <c r="R41" t="n">
-        <v>6991525</v>
+        <v>6991419</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5355,7 +5375,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Savhack (ringhack), färska, på en gran vid hyggeskanten.</t>
+          <t>Rejäla hackspår i stambasen av en stående död gran med full längd.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5370,26 +5390,6 @@
       <c r="AH41" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5407,65 +5407,48 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129762620</v>
+        <v>129762655</v>
       </c>
       <c r="B42" t="n">
-        <v>98698</v>
+        <v>91622</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220093</v>
+        <v>5432</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>Châtel.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L42" t="inlineStr"/>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>473586</v>
+        <v>473666</v>
       </c>
       <c r="R42" t="n">
-        <v>6991339</v>
+        <v>6991307</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5502,7 +5485,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>1 vinterståndare i gammal barrblandskog.</t>
+          <t>Flera fruktkroppar i en levande gran.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5517,7 +5500,27 @@
       </c>
       <c r="AH42" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM42" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5535,48 +5538,65 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129762655</v>
+        <v>129762620</v>
       </c>
       <c r="B43" t="n">
-        <v>91622</v>
+        <v>98698</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5432</v>
+        <v>220093</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
+          <t>Corallorhiza trifida</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr"/>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr"/>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>473666</v>
+        <v>473586</v>
       </c>
       <c r="R43" t="n">
-        <v>6991307</v>
+        <v>6991339</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5613,7 +5633,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en levande gran.</t>
+          <t>1 vinterståndare i gammal barrblandskog.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5628,27 +5648,7 @@
       </c>
       <c r="AH43" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -5666,48 +5666,65 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129762659</v>
+        <v>129762631</v>
       </c>
       <c r="B44" t="n">
-        <v>79084</v>
+        <v>98794</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr"/>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>473494</v>
+        <v>473609</v>
       </c>
       <c r="R44" t="n">
-        <v>6991425</v>
+        <v>6991306</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5744,7 +5761,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Minst 8 plantor och 2 vinterståndare inom ca 0,5 m2 yta i barrblandskog. Troligen finns fler plantor på fyndplatsen.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5760,26 +5777,6 @@
       <c r="AH44" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ44" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -5797,10 +5794,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129762648</v>
+        <v>129762659</v>
       </c>
       <c r="B45" t="n">
-        <v>91598</v>
+        <v>79084</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5808,30 +5805,26 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5839,10 +5832,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>473481</v>
+        <v>473494</v>
       </c>
       <c r="R45" t="n">
-        <v>6991527</v>
+        <v>6991425</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5879,7 +5872,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en stående döende gran med full längd.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5894,7 +5887,7 @@
       </c>
       <c r="AH45" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ45" t="inlineStr">
@@ -5909,12 +5902,12 @@
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -5932,65 +5925,52 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129762631</v>
+        <v>129762648</v>
       </c>
       <c r="B46" t="n">
-        <v>98794</v>
+        <v>91598</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>1108</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr"/>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>473609</v>
+        <v>473481</v>
       </c>
       <c r="R46" t="n">
-        <v>6991306</v>
+        <v>6991527</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6027,7 +6007,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Minst 8 plantor och 2 vinterståndare inom ca 0,5 m2 yta i barrblandskog. Troligen finns fler plantor på fyndplatsen.</t>
+          <t>Flera fruktkroppar i en stående döende gran med full längd.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6042,7 +6022,27 @@
       </c>
       <c r="AH46" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM46" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6858,46 +6858,50 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129762601</v>
+        <v>129762627</v>
       </c>
       <c r="B53" t="n">
-        <v>57895</v>
+        <v>98794</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr"/>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N53" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -6909,10 +6913,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>473628</v>
+        <v>473137</v>
       </c>
       <c r="R53" t="n">
-        <v>6991288</v>
+        <v>6991201</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6949,7 +6953,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Minst 2 individer med lockläte i flerskiktad barrblandskog med inslag av klena björkar och björkhögstubbar.</t>
+          <t>Minst 18 plantor och 1 vinterståndare inom ca 0,5 m2 yta söder om ett dike i barrblandskog.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6958,12 +6962,13 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
-          <t>Barrträd</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -6981,50 +6986,46 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129762627</v>
+        <v>129762601</v>
       </c>
       <c r="B54" t="n">
-        <v>98794</v>
+        <v>57895</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N54" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -7036,10 +7037,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>473137</v>
+        <v>473628</v>
       </c>
       <c r="R54" t="n">
-        <v>6991201</v>
+        <v>6991288</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7076,7 +7077,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Minst 18 plantor och 1 vinterståndare inom ca 0,5 m2 yta söder om ett dike i barrblandskog.</t>
+          <t>Minst 2 individer med lockläte i flerskiktad barrblandskog med inslag av klena björkar och björkhögstubbar.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7085,13 +7086,12 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Barrträd</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr"/>
@@ -7109,10 +7109,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129762653</v>
+        <v>129762600</v>
       </c>
       <c r="B55" t="n">
-        <v>91598</v>
+        <v>57895</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7120,41 +7120,50 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1108</v>
+        <v>103021</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>473644</v>
+        <v>473307</v>
       </c>
       <c r="R55" t="n">
-        <v>6991369</v>
+        <v>6991179</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7181,17 +7190,17 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en stående död gran med full längd.</t>
+          <t>Minst 1 talltita med lockläte. Ev. fans fler individer på fyndplatsen där det är flerskiktad barrskog.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7200,33 +7209,12 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ55" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK55" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM55" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO55" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -7244,10 +7232,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129762556</v>
+        <v>129762653</v>
       </c>
       <c r="B56" t="n">
-        <v>91602</v>
+        <v>91598</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7255,21 +7243,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -7286,10 +7274,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>473292</v>
+        <v>473644</v>
       </c>
       <c r="R56" t="n">
-        <v>6991191</v>
+        <v>6991369</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7316,17 +7304,17 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Växer i en död granstam av en rotvälta.</t>
+          <t>Flera fruktkroppar i en stående död gran med full längd.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7356,12 +7344,12 @@
       </c>
       <c r="AM56" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -7379,10 +7367,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129762600</v>
+        <v>129762556</v>
       </c>
       <c r="B57" t="n">
-        <v>57895</v>
+        <v>91602</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7390,50 +7378,41 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>473307</v>
+        <v>473292</v>
       </c>
       <c r="R57" t="n">
-        <v>6991179</v>
+        <v>6991191</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7470,7 +7449,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Minst 1 talltita med lockläte. Ev. fans fler individer på fyndplatsen där det är flerskiktad barrskog.</t>
+          <t>Växer i en död granstam av en rotvälta.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7479,12 +7458,33 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ57" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK57" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM57" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO57" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>

--- a/artfynd/A 48959-2025 artfynd.xlsx
+++ b/artfynd/A 48959-2025 artfynd.xlsx
@@ -2363,37 +2363,41 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129762642</v>
+        <v>129762562</v>
       </c>
       <c r="B19" t="n">
-        <v>91598</v>
+        <v>92320</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1108</v>
+        <v>3298</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2401,10 +2405,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>473243</v>
+        <v>473408</v>
       </c>
       <c r="R19" t="n">
-        <v>6991220</v>
+        <v>6991459</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2441,7 +2445,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>I stambasen av en döende gran.</t>
+          <t>Rikligt med fruktkroppar i stambasen av en hyfsat grov stående död gran med full längd.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2456,7 +2460,7 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
@@ -2471,12 +2475,12 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2494,32 +2498,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129762562</v>
+        <v>129762650</v>
       </c>
       <c r="B20" t="n">
-        <v>92320</v>
+        <v>91598</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>3298</v>
+        <v>1108</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2536,10 +2540,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>473408</v>
+        <v>473464</v>
       </c>
       <c r="R20" t="n">
-        <v>6991459</v>
+        <v>6991416</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2576,7 +2580,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Rikligt med fruktkroppar i stambasen av en hyfsat grov stående död gran med full längd.</t>
+          <t>Flera fruktkroppar i stambasen av en stående döende grov gran.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2629,7 +2633,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129762650</v>
+        <v>129762639</v>
       </c>
       <c r="B21" t="n">
         <v>91598</v>
@@ -2671,10 +2675,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>473464</v>
+        <v>473289</v>
       </c>
       <c r="R21" t="n">
-        <v>6991416</v>
+        <v>6991144</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2711,7 +2715,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i stambasen av en stående döende grov gran.</t>
+          <t>I två stående döda granar.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2726,7 +2730,7 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
@@ -2764,7 +2768,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129762639</v>
+        <v>129762642</v>
       </c>
       <c r="B22" t="n">
         <v>91598</v>
@@ -2794,11 +2798,7 @@
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2806,10 +2806,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>473289</v>
+        <v>473243</v>
       </c>
       <c r="R22" t="n">
-        <v>6991144</v>
+        <v>6991220</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2846,7 +2846,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>I två stående döda granar.</t>
+          <t>I stambasen av en döende gran.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3431,65 +3431,52 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129762632</v>
+        <v>129762641</v>
       </c>
       <c r="B27" t="n">
-        <v>98794</v>
+        <v>91598</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>1108</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr"/>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>473644</v>
+        <v>473229</v>
       </c>
       <c r="R27" t="n">
-        <v>6991272</v>
+        <v>6991116</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3516,17 +3503,17 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Minst 54 plantor inom ca 2 m2 yta strax norr om ett dike.</t>
+          <t>Gott om fruktkroppar i en stående död gran med full längd.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3542,6 +3529,26 @@
       <c r="AH27" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3559,7 +3566,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129762641</v>
+        <v>129762649</v>
       </c>
       <c r="B28" t="n">
         <v>91598</v>
@@ -3601,10 +3608,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>473229</v>
+        <v>473475</v>
       </c>
       <c r="R28" t="n">
-        <v>6991116</v>
+        <v>6991471</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3641,7 +3648,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Gott om fruktkroppar i en stående död gran med full längd.</t>
+          <t>Flera fruktkroppar i stambasen av en stående död gran (24 cm BHD) med full längd. På fyndplatsen finns stående död ved i en volym som indikerar minst högt livsmiljövärde för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3694,52 +3701,65 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129762649</v>
+        <v>129762632</v>
       </c>
       <c r="B29" t="n">
-        <v>91598</v>
+        <v>98794</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1108</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>473475</v>
+        <v>473644</v>
       </c>
       <c r="R29" t="n">
-        <v>6991471</v>
+        <v>6991272</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3766,17 +3786,17 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i stambasen av en stående död gran (24 cm BHD) med full längd. På fyndplatsen finns stående död ved i en volym som indikerar minst högt livsmiljövärde för tretåig hackspett.</t>
+          <t>Minst 54 plantor inom ca 2 m2 yta strax norr om ett dike.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3792,26 +3812,6 @@
       <c r="AH29" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -6588,48 +6588,65 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129762656</v>
+        <v>129762627</v>
       </c>
       <c r="B51" t="n">
-        <v>91622</v>
+        <v>98794</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr"/>
-      <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr"/>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr"/>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>473615</v>
+        <v>473137</v>
       </c>
       <c r="R51" t="n">
-        <v>6991356</v>
+        <v>6991201</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6656,17 +6673,17 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Rikligt med fruktkroppar i en stående döende gran med full längd.</t>
+          <t>Minst 18 plantor och 1 vinterståndare inom ca 0,5 m2 yta söder om ett dike i barrblandskog.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6681,27 +6698,7 @@
       </c>
       <c r="AH51" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ51" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK51" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO51" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -6858,65 +6855,48 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129762627</v>
+        <v>129762656</v>
       </c>
       <c r="B53" t="n">
-        <v>98794</v>
+        <v>91622</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L53" t="inlineStr"/>
-      <c r="N53" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>473137</v>
+        <v>473615</v>
       </c>
       <c r="R53" t="n">
-        <v>6991201</v>
+        <v>6991356</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6943,17 +6923,17 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Minst 18 plantor och 1 vinterståndare inom ca 0,5 m2 yta söder om ett dike i barrblandskog.</t>
+          <t>Rikligt med fruktkroppar i en stående döende gran med full längd.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6968,7 +6948,27 @@
       </c>
       <c r="AH53" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM53" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>

--- a/artfynd/A 48959-2025 artfynd.xlsx
+++ b/artfynd/A 48959-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY63"/>
+  <dimension ref="A1:AY61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129733690</v>
+        <v>129733687</v>
       </c>
       <c r="B2" t="n">
-        <v>91634</v>
+        <v>91905</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>473509</v>
+        <v>473216</v>
       </c>
       <c r="R2" t="n">
-        <v>6991413</v>
+        <v>6991223</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129733694</v>
+        <v>129733691</v>
       </c>
       <c r="B3" t="n">
-        <v>91634</v>
+        <v>91905</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>473330</v>
+        <v>473347</v>
       </c>
       <c r="R3" t="n">
-        <v>6991067</v>
+        <v>6991168</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129733680</v>
+        <v>129733692</v>
       </c>
       <c r="B4" t="n">
-        <v>91638</v>
+        <v>91905</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>473498</v>
+        <v>473337</v>
       </c>
       <c r="R4" t="n">
-        <v>6991415</v>
+        <v>6991082</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129733684</v>
+        <v>129733693</v>
       </c>
       <c r="B5" t="n">
-        <v>57740</v>
+        <v>91905</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,50 +977,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>473270</v>
+        <v>473343</v>
       </c>
       <c r="R5" t="n">
-        <v>6991065</v>
+        <v>6991073</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1053,11 +1037,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-11-05</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Observation av en födosökande individ av tretåig hackspett. Var dock svårt att se om det var en hona eller hane. I skogen omkring fyndplatsen finns höga livsmiljövärden för tretåig hackspett baserat på volymen stående död ved.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1084,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129733693</v>
+        <v>129733694</v>
       </c>
       <c r="B6" t="n">
-        <v>91634</v>
+        <v>91905</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1119,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>473343</v>
+        <v>473330</v>
       </c>
       <c r="R6" t="n">
-        <v>6991073</v>
+        <v>6991067</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1184,7 +1163,7 @@
         <v>129733695</v>
       </c>
       <c r="B7" t="n">
-        <v>91634</v>
+        <v>91905</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1278,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129733692</v>
+        <v>129762639</v>
       </c>
       <c r="B8" t="n">
-        <v>91634</v>
+        <v>91905</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1307,16 +1286,23 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>473337</v>
+        <v>473289</v>
       </c>
       <c r="R8" t="n">
-        <v>6991082</v>
+        <v>6991144</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1343,12 +1329,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>I två stående döda granar.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1357,8 +1348,34 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1375,10 +1392,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129733689</v>
+        <v>129762640</v>
       </c>
       <c r="B9" t="n">
-        <v>91634</v>
+        <v>91905</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1404,16 +1421,23 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>473505</v>
+        <v>473215</v>
       </c>
       <c r="R9" t="n">
-        <v>6991422</v>
+        <v>6991103</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1440,12 +1464,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>I en smal stående död gran.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1454,8 +1483,34 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1472,10 +1527,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129733685</v>
+        <v>129762641</v>
       </c>
       <c r="B10" t="n">
-        <v>57737</v>
+        <v>91905</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1483,29 +1538,28 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>1108</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1515,10 +1569,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>473633</v>
+        <v>473229</v>
       </c>
       <c r="R10" t="n">
-        <v>6991388</v>
+        <v>6991116</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1545,17 +1599,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Färska hackspår.</t>
+          <t>Gott om fruktkroppar i en stående död gran med full längd.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1564,8 +1618,34 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1582,10 +1662,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129733696</v>
+        <v>129762642</v>
       </c>
       <c r="B11" t="n">
-        <v>91658</v>
+        <v>91905</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1593,30 +1673,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr"/>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>473472</v>
+        <v>473243</v>
       </c>
       <c r="R11" t="n">
-        <v>6991545</v>
+        <v>6991220</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1643,12 +1730,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>I stambasen av en döende gran.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1657,8 +1749,34 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1675,42 +1793,41 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129733686</v>
+        <v>129762643</v>
       </c>
       <c r="B12" t="n">
-        <v>98830</v>
+        <v>91905</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>1108</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr"/>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1718,10 +1835,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>473562</v>
+        <v>473253</v>
       </c>
       <c r="R12" t="n">
-        <v>6991360</v>
+        <v>6991258</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1748,12 +1865,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Flera fruktkroppar i en stående döende gran.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1765,6 +1887,31 @@
       <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1781,10 +1928,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129733681</v>
+        <v>129762647</v>
       </c>
       <c r="B13" t="n">
-        <v>91638</v>
+        <v>91905</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1792,34 +1939,41 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>473323</v>
+        <v>473379</v>
       </c>
       <c r="R13" t="n">
-        <v>6991104</v>
+        <v>6991478</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1846,12 +2000,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Flera fruktkroppar i en stående död gran med full längd.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1860,8 +2019,34 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -1878,10 +2063,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129733687</v>
+        <v>129733681</v>
       </c>
       <c r="B14" t="n">
-        <v>91634</v>
+        <v>91909</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1889,21 +2074,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1913,10 +2098,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>473216</v>
+        <v>473323</v>
       </c>
       <c r="R14" t="n">
-        <v>6991223</v>
+        <v>6991104</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1975,10 +2160,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129733691</v>
+        <v>129762556</v>
       </c>
       <c r="B15" t="n">
-        <v>91634</v>
+        <v>91909</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1986,34 +2171,41 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>473347</v>
+        <v>473292</v>
       </c>
       <c r="R15" t="n">
-        <v>6991168</v>
+        <v>6991191</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2040,12 +2232,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Växer i en död granstam av en rotvälta.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2054,8 +2251,34 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2072,10 +2295,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129733683</v>
+        <v>129487778</v>
       </c>
       <c r="B16" t="n">
-        <v>92356</v>
+        <v>92632</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2103,14 +2326,14 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Haraån, Jmt</t>
+          <t>Lillutloppet, Lillutloppet, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>473498</v>
+        <v>473224</v>
       </c>
       <c r="R16" t="n">
-        <v>6991416</v>
+        <v>6991067</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2137,12 +2360,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2157,57 +2390,73 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Maria Noro-Larsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129733682</v>
+        <v>129733684</v>
       </c>
       <c r="B17" t="n">
-        <v>92356</v>
+        <v>57953</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>473410</v>
+        <v>473270</v>
       </c>
       <c r="R17" t="n">
-        <v>6991458</v>
+        <v>6991065</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2240,6 +2489,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Observation av en födosökande individ av tretåig hackspett. Var dock svårt att se om det var en hona eller hane. I skogen omkring fyndplatsen finns höga livsmiljövärden för tretåig hackspett baserat på volymen stående död ved.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2266,10 +2520,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129733688</v>
+        <v>129762593</v>
       </c>
       <c r="B18" t="n">
-        <v>91634</v>
+        <v>57953</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2277,34 +2531,46 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>473410</v>
+        <v>473284</v>
       </c>
       <c r="R18" t="n">
-        <v>6991534</v>
+        <v>6991191</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2331,12 +2597,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på stambasen av en gran i granskog.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2347,6 +2618,31 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2363,52 +2659,57 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129762562</v>
+        <v>129762594</v>
       </c>
       <c r="B19" t="n">
-        <v>92357</v>
+        <v>57953</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>3298</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>473408</v>
+        <v>473355</v>
       </c>
       <c r="R19" t="n">
-        <v>6991459</v>
+        <v>6991512</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2445,7 +2746,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Rikligt med fruktkroppar i stambasen av en hyfsat grov stående död gran med full längd.</t>
+          <t>Ringhack, färska, på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2454,13 +2755,12 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
@@ -2475,12 +2775,12 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2498,10 +2798,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129762650</v>
+        <v>129762595</v>
       </c>
       <c r="B20" t="n">
-        <v>91635</v>
+        <v>57953</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2509,41 +2809,46 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>473464</v>
+        <v>473369</v>
       </c>
       <c r="R20" t="n">
-        <v>6991416</v>
+        <v>6991519</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2580,7 +2885,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i stambasen av en stående döende grov gran.</t>
+          <t>Ringhack (savhack), färska, på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2589,13 +2894,12 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
@@ -2610,12 +2914,12 @@
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2633,10 +2937,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129762639</v>
+        <v>129762597</v>
       </c>
       <c r="B21" t="n">
-        <v>91635</v>
+        <v>57953</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2644,41 +2948,46 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>473289</v>
+        <v>473383</v>
       </c>
       <c r="R21" t="n">
-        <v>6991144</v>
+        <v>6991525</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2715,7 +3024,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>I två stående döda granar.</t>
+          <t>Savhack (ringhack), färska, på en gran vid hyggeskanten.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2724,7 +3033,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2745,12 +3053,12 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -2768,10 +3076,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129762642</v>
+        <v>129762600</v>
       </c>
       <c r="B22" t="n">
-        <v>91635</v>
+        <v>58114</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2779,37 +3087,50 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1108</v>
+        <v>103021</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>473243</v>
+        <v>473307</v>
       </c>
       <c r="R22" t="n">
-        <v>6991220</v>
+        <v>6991179</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2846,7 +3167,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>I stambasen av en döende gran.</t>
+          <t>Minst 1 talltita med lockläte. Ev. fans fler individer på fyndplatsen där det är flerskiktad barrskog.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2855,33 +3176,12 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -2899,52 +3199,65 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129762643</v>
+        <v>129762627</v>
       </c>
       <c r="B23" t="n">
-        <v>91635</v>
+        <v>99118</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1108</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>473253</v>
+        <v>473137</v>
       </c>
       <c r="R23" t="n">
-        <v>6991258</v>
+        <v>6991201</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2981,7 +3294,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en stående döende gran.</t>
+          <t>Minst 18 plantor och 1 vinterståndare inom ca 0,5 m2 yta söder om ett dike i barrblandskog.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2996,27 +3309,7 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3034,10 +3327,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129762654</v>
+        <v>129733688</v>
       </c>
       <c r="B24" t="n">
-        <v>91635</v>
+        <v>91905</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3063,19 +3356,16 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>473668</v>
+        <v>473410</v>
       </c>
       <c r="R24" t="n">
-        <v>6991289</v>
+        <v>6991534</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3102,17 +3392,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Flera fruktkroppar i en granstubbe.</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3121,34 +3406,8 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AH24" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Stump # Picea abies</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3165,10 +3424,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129762652</v>
+        <v>129733689</v>
       </c>
       <c r="B25" t="n">
-        <v>91635</v>
+        <v>91905</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3194,23 +3453,16 @@
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>473621</v>
+        <v>473505</v>
       </c>
       <c r="R25" t="n">
-        <v>6991345</v>
+        <v>6991422</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3237,17 +3489,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Flera fruktkroppar i en stående död gran med full längd och 35 cm i brösthöjdsdiameter.</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3256,34 +3503,8 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
-      </c>
-      <c r="AH25" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
@@ -3300,10 +3521,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129762641</v>
+        <v>129733690</v>
       </c>
       <c r="B26" t="n">
-        <v>91635</v>
+        <v>91905</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3329,23 +3550,16 @@
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>473229</v>
+        <v>473509</v>
       </c>
       <c r="R26" t="n">
-        <v>6991116</v>
+        <v>6991413</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3372,17 +3586,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Gott om fruktkroppar i en stående död gran med full längd.</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3391,34 +3600,8 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AH26" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3435,10 +3618,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129762649</v>
+        <v>129762644</v>
       </c>
       <c r="B27" t="n">
-        <v>91635</v>
+        <v>91905</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3477,10 +3660,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>473475</v>
+        <v>473430</v>
       </c>
       <c r="R27" t="n">
-        <v>6991471</v>
+        <v>6991442</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3517,7 +3700,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i stambasen av en stående död gran (24 cm BHD) med full längd. På fyndplatsen finns stående död ved i en volym som indikerar minst högt livsmiljövärde för tretåig hackspett.</t>
+          <t>I en granhögstubbe.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3532,7 +3715,7 @@
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ27" t="inlineStr">
@@ -3570,10 +3753,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129762662</v>
+        <v>129762645</v>
       </c>
       <c r="B28" t="n">
-        <v>79095</v>
+        <v>91905</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3581,26 +3764,30 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3608,10 +3795,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>473631</v>
+        <v>473460</v>
       </c>
       <c r="R28" t="n">
-        <v>6991321</v>
+        <v>6991507</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3638,17 +3825,17 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>På gran i granskog.</t>
+          <t>Rikligt med fruktkroppar i en stående död gran med full längd.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3678,12 +3865,12 @@
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3701,65 +3888,52 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129762632</v>
+        <v>129762646</v>
       </c>
       <c r="B29" t="n">
-        <v>98831</v>
+        <v>91905</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>1108</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr"/>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>473644</v>
+        <v>473393</v>
       </c>
       <c r="R29" t="n">
-        <v>6991272</v>
+        <v>6991465</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3786,17 +3960,17 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Minst 54 plantor inom ca 2 m2 yta strax norr om ett dike.</t>
+          <t>I en stående död gran.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3811,7 +3985,27 @@
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -3829,10 +4023,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129762647</v>
+        <v>129762648</v>
       </c>
       <c r="B30" t="n">
-        <v>91635</v>
+        <v>91905</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3871,10 +4065,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>473379</v>
+        <v>473481</v>
       </c>
       <c r="R30" t="n">
-        <v>6991478</v>
+        <v>6991527</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3911,7 +4105,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en stående död gran med full längd.</t>
+          <t>Flera fruktkroppar i en stående döende gran med full längd.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3926,7 +4120,7 @@
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ30" t="inlineStr">
@@ -3941,12 +4135,12 @@
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -3964,10 +4158,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129762663</v>
+        <v>129762649</v>
       </c>
       <c r="B31" t="n">
-        <v>79095</v>
+        <v>91905</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3975,26 +4169,30 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -4002,10 +4200,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>473588</v>
+        <v>473475</v>
       </c>
       <c r="R31" t="n">
-        <v>6991409</v>
+        <v>6991471</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4032,17 +4230,17 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Flera fruktkroppar i stambasen av en stående död gran (24 cm BHD) med full längd. På fyndplatsen finns stående död ved i en volym som indikerar minst högt livsmiljövärde för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4057,7 +4255,7 @@
       </c>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ31" t="inlineStr">
@@ -4072,12 +4270,12 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4095,10 +4293,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129762640</v>
+        <v>129762650</v>
       </c>
       <c r="B32" t="n">
-        <v>91635</v>
+        <v>91905</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4137,10 +4335,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>473215</v>
+        <v>473464</v>
       </c>
       <c r="R32" t="n">
-        <v>6991103</v>
+        <v>6991416</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4177,7 +4375,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>I en smal stående död gran.</t>
+          <t>Flera fruktkroppar i stambasen av en stående döende grov gran.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4192,7 +4390,7 @@
       </c>
       <c r="AH32" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ32" t="inlineStr">
@@ -4230,10 +4428,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129762660</v>
+        <v>129762651</v>
       </c>
       <c r="B33" t="n">
-        <v>79095</v>
+        <v>91905</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4241,26 +4439,30 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4268,10 +4470,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>473564</v>
+        <v>473497</v>
       </c>
       <c r="R33" t="n">
-        <v>6991395</v>
+        <v>6991392</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4308,7 +4510,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>På bark av tall.</t>
+          <t>Flera fruktkroppar i en levande gran.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4328,22 +4530,22 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Pinus sylvestris</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4361,65 +4563,52 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129762630</v>
+        <v>129762652</v>
       </c>
       <c r="B34" t="n">
-        <v>98831</v>
+        <v>91905</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>1108</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr"/>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>473588</v>
+        <v>473621</v>
       </c>
       <c r="R34" t="n">
-        <v>6991340</v>
+        <v>6991345</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4456,7 +4645,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Minst 6 plantor och 1 vinterståndare inom ca 0,5 m2 yta precis intill korallrot i gammal barrblandskog.</t>
+          <t>Flera fruktkroppar i en stående död gran med full längd och 35 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4471,7 +4660,27 @@
       </c>
       <c r="AH34" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM34" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4489,10 +4698,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129762651</v>
+        <v>129762653</v>
       </c>
       <c r="B35" t="n">
-        <v>91635</v>
+        <v>91905</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4531,10 +4740,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>473497</v>
+        <v>473644</v>
       </c>
       <c r="R35" t="n">
-        <v>6991392</v>
+        <v>6991369</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4561,17 +4770,17 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en levande gran.</t>
+          <t>Flera fruktkroppar i en stående död gran med full längd.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4586,7 +4795,7 @@
       </c>
       <c r="AH35" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ35" t="inlineStr">
@@ -4601,12 +4810,12 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4624,42 +4833,37 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129762664</v>
+        <v>129762654</v>
       </c>
       <c r="B36" t="n">
-        <v>98748</v>
+        <v>91905</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>219790</v>
+        <v>1108</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4667,10 +4871,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>473659</v>
+        <v>473668</v>
       </c>
       <c r="R36" t="n">
-        <v>6991313</v>
+        <v>6991289</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4707,7 +4911,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Minst 1 vinterståndare.</t>
+          <t>Flera fruktkroppar i en granstubbe.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4722,7 +4926,27 @@
       </c>
       <c r="AH36" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM36" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Stump # Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4740,10 +4964,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129762593</v>
+        <v>129733680</v>
       </c>
       <c r="B37" t="n">
-        <v>57741</v>
+        <v>91909</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4751,46 +4975,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>473284</v>
+        <v>473498</v>
       </c>
       <c r="R37" t="n">
-        <v>6991191</v>
+        <v>6991415</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4817,17 +5029,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på stambasen av en gran i granskog.</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4838,31 +5045,6 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
-      </c>
-      <c r="AH37" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ37" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK37" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
@@ -4879,10 +5061,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129762644</v>
+        <v>129762557</v>
       </c>
       <c r="B38" t="n">
-        <v>91635</v>
+        <v>91909</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4890,21 +5072,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4921,10 +5103,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>473430</v>
+        <v>473560</v>
       </c>
       <c r="R38" t="n">
-        <v>6991442</v>
+        <v>6991376</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4951,17 +5133,17 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>I en granhögstubbe.</t>
+          <t>Fruktkroppar längs flera meter i en granlåga.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4976,7 +5158,7 @@
       </c>
       <c r="AH38" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ38" t="inlineStr">
@@ -4991,12 +5173,12 @@
       </c>
       <c r="AM38" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Horizontal, dead with ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5014,52 +5196,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129762645</v>
+        <v>129733682</v>
       </c>
       <c r="B39" t="n">
-        <v>91635</v>
+        <v>92632</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1108</v>
+        <v>3298</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>473460</v>
+        <v>473410</v>
       </c>
       <c r="R39" t="n">
-        <v>6991507</v>
+        <v>6991458</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5086,17 +5261,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Rikligt med fruktkroppar i en stående död gran med full längd.</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5105,34 +5275,8 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
-      </c>
-      <c r="AH39" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ39" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK39" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
@@ -5149,48 +5293,45 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129762655</v>
+        <v>129733683</v>
       </c>
       <c r="B40" t="n">
-        <v>91659</v>
+        <v>92632</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5432</v>
+        <v>3298</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr"/>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>473666</v>
+        <v>473498</v>
       </c>
       <c r="R40" t="n">
-        <v>6991307</v>
+        <v>6991416</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5217,17 +5358,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Flera fruktkroppar i en levande gran.</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5236,34 +5372,8 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
-      </c>
-      <c r="AH40" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
@@ -5280,57 +5390,52 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129762603</v>
+        <v>129762562</v>
       </c>
       <c r="B41" t="n">
-        <v>57738</v>
+        <v>92632</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>3298</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>473521</v>
+        <v>473408</v>
       </c>
       <c r="R41" t="n">
-        <v>6991419</v>
+        <v>6991459</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5367,7 +5472,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Rejäla hackspår i stambasen av en stående död gran med full längd.</t>
+          <t>Rikligt med fruktkroppar i stambasen av en hyfsat grov stående död gran med full längd.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5376,12 +5481,33 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM41" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5399,57 +5525,48 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129762597</v>
+        <v>129762658</v>
       </c>
       <c r="B42" t="n">
-        <v>57741</v>
+        <v>79327</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>473383</v>
+        <v>473495</v>
       </c>
       <c r="R42" t="n">
-        <v>6991525</v>
+        <v>6991469</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5486,7 +5603,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Savhack (ringhack), färska, på en gran vid hyggeskanten.</t>
+          <t>På flera både döda och levande granar.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5495,6 +5612,7 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5515,12 +5633,12 @@
       </c>
       <c r="AM42" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Dead branch  # Picea abies</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5538,65 +5656,48 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129762620</v>
+        <v>129762659</v>
       </c>
       <c r="B43" t="n">
-        <v>98735</v>
+        <v>79327</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220093</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Châtel.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L43" t="inlineStr"/>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>473586</v>
+        <v>473494</v>
       </c>
       <c r="R43" t="n">
-        <v>6991339</v>
+        <v>6991425</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5633,7 +5734,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>1 vinterståndare i gammal barrblandskog.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5649,6 +5750,26 @@
       <c r="AH43" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM43" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -5666,41 +5787,37 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129762648</v>
+        <v>129762660</v>
       </c>
       <c r="B44" t="n">
-        <v>91635</v>
+        <v>79327</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -5708,10 +5825,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>473481</v>
+        <v>473564</v>
       </c>
       <c r="R44" t="n">
-        <v>6991527</v>
+        <v>6991395</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5748,7 +5865,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en stående döende gran med full längd.</t>
+          <t>På bark av tall.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5763,27 +5880,27 @@
       </c>
       <c r="AH44" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK44" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM44" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -5801,14 +5918,14 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129762659</v>
+        <v>129762661</v>
       </c>
       <c r="B45" t="n">
-        <v>79095</v>
+        <v>79327</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
@@ -5839,10 +5956,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>473494</v>
+        <v>473612</v>
       </c>
       <c r="R45" t="n">
-        <v>6991425</v>
+        <v>6991344</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5932,10 +6049,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129762631</v>
+        <v>129762662</v>
       </c>
       <c r="B46" t="n">
-        <v>98831</v>
+        <v>79327</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5943,54 +6060,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr"/>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>473609</v>
+        <v>473631</v>
       </c>
       <c r="R46" t="n">
-        <v>6991306</v>
+        <v>6991321</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6017,17 +6117,17 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Minst 8 plantor och 2 vinterståndare inom ca 0,5 m2 yta i barrblandskog. Troligen finns fler plantor på fyndplatsen.</t>
+          <t>På gran i granskog.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6042,7 +6142,27 @@
       </c>
       <c r="AH46" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM46" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6060,41 +6180,37 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129762646</v>
+        <v>129762663</v>
       </c>
       <c r="B47" t="n">
-        <v>91635</v>
+        <v>79327</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K47" t="inlineStr"/>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -6102,10 +6218,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>473393</v>
+        <v>473588</v>
       </c>
       <c r="R47" t="n">
-        <v>6991465</v>
+        <v>6991409</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6132,17 +6248,17 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>I en stående död gran.</t>
+          <t>På gran.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6172,12 +6288,12 @@
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6195,37 +6311,42 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129762658</v>
+        <v>129733685</v>
       </c>
       <c r="B48" t="n">
-        <v>79095</v>
+        <v>57950</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -6233,10 +6354,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>473495</v>
+        <v>473633</v>
       </c>
       <c r="R48" t="n">
-        <v>6991469</v>
+        <v>6991388</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6263,17 +6384,17 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>På flera både döda och levande granar.</t>
+          <t>Färska hackspår.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6282,34 +6403,8 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
-      </c>
-      <c r="AH48" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ48" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK48" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>Dead branch  # Picea abies</t>
-        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
@@ -6326,27 +6421,27 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129762595</v>
+        <v>129762602</v>
       </c>
       <c r="B49" t="n">
-        <v>57741</v>
+        <v>57950</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -6354,12 +6449,16 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr"/>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -6373,10 +6472,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>473369</v>
+        <v>473458</v>
       </c>
       <c r="R49" t="n">
-        <v>6991519</v>
+        <v>6991530</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6413,7 +6512,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en gran vid hyggeskanten.</t>
+          <t>1 individ med lockläte observerades.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6428,26 +6527,6 @@
       <c r="AH49" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6465,14 +6544,14 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129762602</v>
+        <v>129762603</v>
       </c>
       <c r="B50" t="n">
-        <v>57738</v>
+        <v>57950</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
@@ -6493,16 +6572,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
       <c r="M50" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -6516,10 +6591,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>473458</v>
+        <v>473521</v>
       </c>
       <c r="R50" t="n">
-        <v>6991530</v>
+        <v>6991419</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6556,7 +6631,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>1 individ med lockläte observerades.</t>
+          <t>Rejäla hackspår i stambasen av en stående död gran med full längd.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6588,10 +6663,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129762656</v>
+        <v>129762596</v>
       </c>
       <c r="B51" t="n">
-        <v>91659</v>
+        <v>57953</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6599,37 +6674,46 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>473615</v>
+        <v>473390</v>
       </c>
       <c r="R51" t="n">
-        <v>6991356</v>
+        <v>6991531</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6656,17 +6740,17 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Rikligt med fruktkroppar i en stående döende gran med full längd.</t>
+          <t>Savhack (ringhack), färska, högt upp på en gran.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6675,7 +6759,6 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -6719,10 +6802,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129762601</v>
+        <v>129762598</v>
       </c>
       <c r="B52" t="n">
-        <v>57900</v>
+        <v>57953</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6730,33 +6813,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -6770,10 +6857,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>473628</v>
+        <v>473499</v>
       </c>
       <c r="R52" t="n">
-        <v>6991288</v>
+        <v>6991413</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6810,7 +6897,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Minst 2 individer med lockläte i flerskiktad barrblandskog med inslag av klena björkar och björkhögstubbar.</t>
+          <t>En hane av tretåig hackspett som födosökte på en döende grov gran (53 cm BHD) med trådticka. På och omkring fyndplatsen finns stående död ved främst av gran i en volym som indikerar mycket högt livsmiljövärde för tretåig hackspett. Även gott om liggande död ved på fyndplatsen.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6824,7 +6911,7 @@
       </c>
       <c r="AH52" t="inlineStr">
         <is>
-          <t>Barrträd</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -6842,10 +6929,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129762594</v>
+        <v>129762601</v>
       </c>
       <c r="B53" t="n">
-        <v>57741</v>
+        <v>58114</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6853,29 +6940,33 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -6889,10 +6980,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>473355</v>
+        <v>473628</v>
       </c>
       <c r="R53" t="n">
-        <v>6991512</v>
+        <v>6991288</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6929,7 +7020,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran vid hyggeskanten.</t>
+          <t>Minst 2 individer med lockläte i flerskiktad barrblandskog med inslag av klena björkar och björkhögstubbar.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6943,27 +7034,7 @@
       </c>
       <c r="AH53" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ53" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK53" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO53" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Barrträd</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -6981,65 +7052,53 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129762627</v>
+        <v>129762664</v>
       </c>
       <c r="B54" t="n">
-        <v>98831</v>
+        <v>99035</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="L54" t="inlineStr"/>
-      <c r="N54" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>473137</v>
+        <v>473659</v>
       </c>
       <c r="R54" t="n">
-        <v>6991201</v>
+        <v>6991313</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7066,17 +7125,17 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Minst 18 plantor och 1 vinterståndare inom ca 0,5 m2 yta söder om ett dike i barrblandskog.</t>
+          <t>Minst 1 vinterståndare.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7109,32 +7168,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129762600</v>
+        <v>129762620</v>
       </c>
       <c r="B55" t="n">
-        <v>57900</v>
+        <v>99022</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>103021</v>
+        <v>220093</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -7142,13 +7201,17 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N55" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -7160,10 +7223,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>473307</v>
+        <v>473586</v>
       </c>
       <c r="R55" t="n">
-        <v>6991179</v>
+        <v>6991339</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7200,7 +7263,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Minst 1 talltita med lockläte. Ev. fans fler individer på fyndplatsen där det är flerskiktad barrskog.</t>
+          <t>1 vinterståndare i gammal barrblandskog.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7209,6 +7272,7 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -7232,41 +7296,42 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129762653</v>
+        <v>129733686</v>
       </c>
       <c r="B56" t="n">
-        <v>91635</v>
+        <v>99118</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1108</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr">
         <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr"/>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -7274,10 +7339,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>473644</v>
+        <v>473562</v>
       </c>
       <c r="R56" t="n">
-        <v>6991369</v>
+        <v>6991360</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7304,17 +7369,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Flera fruktkroppar i en stående död gran med full längd.</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7326,31 +7386,6 @@
       <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
-      </c>
-      <c r="AH56" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ56" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK56" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM56" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO56" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
@@ -7367,52 +7402,65 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129762556</v>
+        <v>129762628</v>
       </c>
       <c r="B57" t="n">
-        <v>91639</v>
+        <v>99118</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr"/>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr"/>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>473292</v>
+        <v>473387</v>
       </c>
       <c r="R57" t="n">
-        <v>6991191</v>
+        <v>6991466</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7449,7 +7497,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Växer i en död granstam av en rotvälta.</t>
+          <t>Minst 17 plantor inom ca 0,5 m2 yta intill en gran med sockel.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7465,26 +7513,6 @@
       <c r="AH57" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ57" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK57" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM57" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO57" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
@@ -7502,42 +7530,50 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129762596</v>
+        <v>129762629</v>
       </c>
       <c r="B58" t="n">
-        <v>57741</v>
+        <v>99118</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N58" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -7549,10 +7585,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>473390</v>
+        <v>473481</v>
       </c>
       <c r="R58" t="n">
-        <v>6991531</v>
+        <v>6991561</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7589,7 +7625,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Savhack (ringhack), färska, högt upp på en gran.</t>
+          <t>Minst 28 plantor inom ca 0,5 m2 yta intill en gran.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7598,32 +7634,13 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ58" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK58" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM58" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO58" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -7641,52 +7658,65 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129762557</v>
+        <v>129762630</v>
       </c>
       <c r="B59" t="n">
-        <v>91639</v>
+        <v>99118</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr"/>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr"/>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>473560</v>
+        <v>473588</v>
       </c>
       <c r="R59" t="n">
-        <v>6991376</v>
+        <v>6991340</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7713,17 +7743,17 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Fruktkroppar längs flera meter i en granlåga.</t>
+          <t>Minst 6 plantor och 1 vinterståndare inom ca 0,5 m2 yta precis intill korallrot i gammal barrblandskog.</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7738,27 +7768,7 @@
       </c>
       <c r="AH59" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ59" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK59" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM59" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO59" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Picea abies</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -7776,48 +7786,65 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129762661</v>
+        <v>129762631</v>
       </c>
       <c r="B60" t="n">
-        <v>79095</v>
+        <v>99118</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr"/>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Haraån, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>473612</v>
+        <v>473609</v>
       </c>
       <c r="R60" t="n">
-        <v>6991344</v>
+        <v>6991306</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7854,7 +7881,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>På gran.</t>
+          <t>Minst 8 plantor och 2 vinterståndare inom ca 0,5 m2 yta i barrblandskog. Troligen finns fler plantor på fyndplatsen.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7870,26 +7897,6 @@
       <c r="AH60" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ60" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK60" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM60" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO60" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT60" t="inlineStr"/>
@@ -7907,10 +7914,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129762628</v>
+        <v>129762632</v>
       </c>
       <c r="B61" t="n">
-        <v>98831</v>
+        <v>99118</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7937,7 +7944,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>54</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -7962,10 +7969,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>473387</v>
+        <v>473644</v>
       </c>
       <c r="R61" t="n">
-        <v>6991466</v>
+        <v>6991272</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7992,17 +7999,17 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Minst 17 plantor inom ca 0,5 m2 yta intill en gran med sockel.</t>
+          <t>Minst 54 plantor inom ca 2 m2 yta strax norr om ett dike.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8032,261 +8039,6 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
-    </row>
-    <row r="62">
-      <c r="A62" t="n">
-        <v>129762598</v>
-      </c>
-      <c r="B62" t="n">
-        <v>57741</v>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E62" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N62" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
-      <c r="P62" t="inlineStr">
-        <is>
-          <t>Haraån, Jmt</t>
-        </is>
-      </c>
-      <c r="Q62" t="n">
-        <v>473499</v>
-      </c>
-      <c r="R62" t="n">
-        <v>6991413</v>
-      </c>
-      <c r="S62" t="n">
-        <v>10</v>
-      </c>
-      <c r="T62" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U62" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V62" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W62" t="inlineStr">
-        <is>
-          <t>Sunne</t>
-        </is>
-      </c>
-      <c r="Y62" t="inlineStr">
-        <is>
-          <t>2025-11-19</t>
-        </is>
-      </c>
-      <c r="AA62" t="inlineStr">
-        <is>
-          <t>2025-11-19</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>En hane av tretåig hackspett som födosökte på en döende grov gran (53 cm BHD) med trådticka. På och omkring fyndplatsen finns stående död ved främst av gran i en volym som indikerar mycket högt livsmiljövärde för tretåig hackspett. Även gott om liggande död ved på fyndplatsen.</t>
-        </is>
-      </c>
-      <c r="AD62" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE62" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG62" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH62" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AT62" t="inlineStr"/>
-      <c r="AW62" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX62" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY62" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" t="n">
-        <v>129762629</v>
-      </c>
-      <c r="B63" t="n">
-        <v>98831</v>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E63" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L63" t="inlineStr"/>
-      <c r="N63" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
-      <c r="P63" t="inlineStr">
-        <is>
-          <t>Haraån, Jmt</t>
-        </is>
-      </c>
-      <c r="Q63" t="n">
-        <v>473481</v>
-      </c>
-      <c r="R63" t="n">
-        <v>6991561</v>
-      </c>
-      <c r="S63" t="n">
-        <v>10</v>
-      </c>
-      <c r="T63" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U63" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V63" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W63" t="inlineStr">
-        <is>
-          <t>Sunne</t>
-        </is>
-      </c>
-      <c r="Y63" t="inlineStr">
-        <is>
-          <t>2025-11-19</t>
-        </is>
-      </c>
-      <c r="AA63" t="inlineStr">
-        <is>
-          <t>2025-11-19</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Minst 28 plantor inom ca 0,5 m2 yta intill en gran.</t>
-        </is>
-      </c>
-      <c r="AD63" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE63" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF63" t="inlineStr"/>
-      <c r="AG63" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH63" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AT63" t="inlineStr"/>
-      <c r="AW63" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX63" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY63" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 48959-2025 artfynd.xlsx
+++ b/artfynd/A 48959-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY61"/>
+  <dimension ref="A1:AZ61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129733687</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129733688</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129733689</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129733690</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129733691</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129733692</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129733693</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129733694</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129733695</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1680,6 +1730,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129762639</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1815,6 +1870,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129762640</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1950,6 +2010,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129762641</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2081,6 +2146,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129762642</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2216,6 +2286,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129762643</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2351,6 +2426,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129762644</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2486,6 +2566,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129762645</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2621,6 +2706,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129762646</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2756,6 +2846,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129762647</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2891,6 +2986,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129762648</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3026,6 +3126,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129762649</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3161,6 +3266,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129762650</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3296,6 +3406,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129762651</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3431,6 +3546,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129762652</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3566,6 +3686,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129762653</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3697,6 +3822,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129762654</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3794,6 +3924,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129733680</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3891,6 +4026,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129733681</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -4026,6 +4166,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129762556</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4161,6 +4306,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129762557</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4268,6 +4418,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129487778</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4365,6 +4520,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129733682</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4462,6 +4622,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129733683</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4597,6 +4762,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129762562</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4728,6 +4898,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129762658</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4859,6 +5034,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129762659</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4990,6 +5170,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129762660</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -5121,6 +5306,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129762661</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -5252,6 +5442,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129762662</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5383,6 +5578,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129762663</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5493,6 +5693,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129733685</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5616,6 +5821,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129762602</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5735,6 +5945,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129762603</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5853,6 +6068,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129733684</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5992,6 +6212,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129762593</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -6131,6 +6356,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129762594</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -6270,6 +6500,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129762595</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -6409,6 +6644,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129762596</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6548,6 +6788,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129762597</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6675,6 +6920,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129762598</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6798,6 +7048,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129762600</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6921,6 +7176,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129762601</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -7037,6 +7297,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129762664</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -7165,6 +7430,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129762620</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -7271,6 +7541,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129733686</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -7399,6 +7674,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129762627</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -7527,6 +7807,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129762628</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -7655,6 +7940,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129762629</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7783,6 +8073,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129762630</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7911,6 +8206,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129762631</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -8039,8 +8339,75 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129762632</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>